--- a/Results/Phase 2/Hydrogen/hydrogen eutrophication freshwater results.xlsx
+++ b/Results/Phase 2/Hydrogen/hydrogen eutrophication freshwater results.xlsx
@@ -886,7 +886,7 @@
         <v>1.763146422333954e-05</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0002879759713835331</v>
+        <v>1.763146422333957e-05</v>
       </c>
       <c r="O5" t="n">
         <v>1.763146422333957e-05</v>
@@ -974,7 +974,7 @@
         <v>5.188428966037571e-05</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0002879759713835331</v>
+        <v>2.990833861738766e-05</v>
       </c>
       <c r="O6" t="n">
         <v>2.990848340404848e-05</v>
@@ -1062,7 +1062,7 @@
         <v>4.514038233741741e-05</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0002879759713835331</v>
+        <v>4.514038233741741e-05</v>
       </c>
       <c r="O7" t="n">
         <v>4.513096966333651e-05</v>
@@ -1150,7 +1150,7 @@
         <v>0.000148765732176611</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0002879759713835331</v>
+        <v>0.0001076120775471628</v>
       </c>
       <c r="O8" t="n">
         <v>0.0001189214591707539</v>
@@ -1238,7 +1238,7 @@
         <v>0.0002094672271842761</v>
       </c>
       <c r="N9" t="n">
-        <v>0.0002879759713835331</v>
+        <v>0.0002094672271842761</v>
       </c>
       <c r="O9" t="n">
         <v>0.0002236357059671936</v>
@@ -1898,7 +1898,7 @@
         <v>8.222018023921233e-06</v>
       </c>
       <c r="F5" t="n">
-        <v>8.222018023921218e-06</v>
+        <v>8.222018023921216e-06</v>
       </c>
       <c r="G5" t="n">
         <v>8.222018023921233e-06</v>
@@ -1922,16 +1922,16 @@
         <v>8.222018023921233e-06</v>
       </c>
       <c r="N5" t="n">
-        <v>7.505071325843371e-05</v>
+        <v>8.222018023921216e-06</v>
       </c>
       <c r="O5" t="n">
-        <v>8.222018023921218e-06</v>
+        <v>8.222018023921216e-06</v>
       </c>
       <c r="P5" t="n">
-        <v>8.222018023921218e-06</v>
+        <v>8.222018023921216e-06</v>
       </c>
       <c r="Q5" t="n">
-        <v>8.222018023921218e-06</v>
+        <v>8.222018023921216e-06</v>
       </c>
       <c r="R5" t="n">
         <v>8.222018023921233e-06</v>
@@ -1949,10 +1949,10 @@
         <v>7.658100568920588e-06</v>
       </c>
       <c r="W5" t="n">
-        <v>8.222018023921218e-06</v>
+        <v>8.222018023921216e-06</v>
       </c>
       <c r="X5" t="n">
-        <v>8.222018023921218e-06</v>
+        <v>8.222018023921216e-06</v>
       </c>
       <c r="Y5" t="n">
         <v>8.18849468540769e-06</v>
@@ -1964,7 +1964,7 @@
         <v>8.222018023921233e-06</v>
       </c>
       <c r="AB5" t="n">
-        <v>8.222018023921218e-06</v>
+        <v>8.222018023921216e-06</v>
       </c>
     </row>
     <row r="6">
@@ -2010,7 +2010,7 @@
         <v>1.093655117819038e-05</v>
       </c>
       <c r="N6" t="n">
-        <v>7.505071325843371e-05</v>
+        <v>1.103611340173179e-05</v>
       </c>
       <c r="O6" t="n">
         <v>2.117653111763413e-05</v>
@@ -2098,7 +2098,7 @@
         <v>2.279552831649993e-05</v>
       </c>
       <c r="N7" t="n">
-        <v>7.505071325843371e-05</v>
+        <v>2.279552831649993e-05</v>
       </c>
       <c r="O7" t="n">
         <v>2.278741654861403e-05</v>
@@ -2186,7 +2186,7 @@
         <v>9.31539551686324e-05</v>
       </c>
       <c r="N8" t="n">
-        <v>7.505071325843371e-05</v>
+        <v>6.673192130689879e-05</v>
       </c>
       <c r="O8" t="n">
         <v>7.399292563103965e-05</v>
@@ -2274,7 +2274,7 @@
         <v>8.860659697764269e-05</v>
       </c>
       <c r="N9" t="n">
-        <v>7.505071325843371e-05</v>
+        <v>8.860659697764269e-05</v>
       </c>
       <c r="O9" t="n">
         <v>9.457873946072234e-05</v>
@@ -2371,7 +2371,7 @@
         <v>9.904384611914532e-06</v>
       </c>
       <c r="Q10" t="n">
-        <v>9.160749563427981e-06</v>
+        <v>9.160749563427979e-06</v>
       </c>
       <c r="R10" t="n">
         <v>1.049754869992781e-05</v>
@@ -2480,7 +2480,7 @@
         <v>1.065609869691325e-05</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.977553298145903e-06</v>
+        <v>-2.977553298145904e-06</v>
       </c>
       <c r="Y11" t="n">
         <v>2.528888402999593e-06</v>
@@ -2958,7 +2958,7 @@
         <v>1.445095029244415e-05</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0004600167935857036</v>
+        <v>1.445095029244412e-05</v>
       </c>
       <c r="O5" t="n">
         <v>1.445095029244412e-05</v>
@@ -3046,7 +3046,7 @@
         <v>4.30646755372961e-05</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0004600167935857036</v>
+        <v>2.359128973232753e-05</v>
       </c>
       <c r="O6" t="n">
         <v>2.358442861505023e-05</v>
@@ -3134,7 +3134,7 @@
         <v>3.850186705856514e-05</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0004600167935857036</v>
+        <v>3.850186705856514e-05</v>
       </c>
       <c r="O7" t="n">
         <v>3.849310113443104e-05</v>
@@ -3222,7 +3222,7 @@
         <v>0.0001327731218102102</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0004600167935857036</v>
+        <v>9.56521355167405e-05</v>
       </c>
       <c r="O8" t="n">
         <v>0.0001058533048661583</v>
@@ -3310,7 +3310,7 @@
         <v>0.0001654122383185598</v>
       </c>
       <c r="N9" t="n">
-        <v>0.0004600167935857036</v>
+        <v>0.0001654122383185598</v>
       </c>
       <c r="O9" t="n">
         <v>0.00017660465150011</v>
@@ -3694,85 +3694,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.304085209688199e-05</v>
+        <v>4.304085209688189e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>2.228299958720186e-05</v>
+        <v>2.228299958720181e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>2.825727353276623e-05</v>
+        <v>2.82572735327662e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>1.983655618113785e-05</v>
+        <v>1.983655618113782e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>2.607610672314522e-05</v>
+        <v>2.607610672314517e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>2.629282221528318e-05</v>
+        <v>2.629282221528313e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>2.213363874315196e-05</v>
+        <v>2.21336387431519e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>2.911404757029924e-05</v>
+        <v>2.911404757029917e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>3.042926224875873e-05</v>
+        <v>3.042926224875857e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>3.346515578102998e-05</v>
+        <v>3.346515578102993e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>6.317524543684353e-05</v>
+        <v>6.317524543684337e-05</v>
       </c>
       <c r="M2" t="n">
-        <v>3.624079340520485e-05</v>
+        <v>3.624079340520471e-05</v>
       </c>
       <c r="N2" t="n">
-        <v>2.414442198060827e-05</v>
+        <v>2.414442198060825e-05</v>
       </c>
       <c r="O2" t="n">
-        <v>2.581226023207634e-05</v>
+        <v>2.581226023207623e-05</v>
       </c>
       <c r="P2" t="n">
-        <v>3.569429611599917e-05</v>
+        <v>3.569429611599914e-05</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.719864462450892e-05</v>
+        <v>2.719864462450887e-05</v>
       </c>
       <c r="R2" t="n">
-        <v>2.253431722433464e-05</v>
+        <v>2.253431722433459e-05</v>
       </c>
       <c r="S2" t="n">
-        <v>3.516080352642426e-05</v>
+        <v>3.516080352642414e-05</v>
       </c>
       <c r="T2" t="n">
-        <v>2.80043946901298e-05</v>
+        <v>2.800439469012965e-05</v>
       </c>
       <c r="U2" t="n">
-        <v>5.01763781757003e-05</v>
+        <v>5.017637817570033e-05</v>
       </c>
       <c r="V2" t="n">
-        <v>2.955492468007434e-05</v>
+        <v>2.955492468007439e-05</v>
       </c>
       <c r="W2" t="n">
-        <v>2.740918019728019e-05</v>
+        <v>2.740918019728013e-05</v>
       </c>
       <c r="X2" t="n">
         <v>4.426435290162738e-05</v>
       </c>
       <c r="Y2" t="n">
-        <v>3.051907247811078e-05</v>
+        <v>3.051907247811077e-05</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.354399997835794e-05</v>
+        <v>3.354399997835788e-05</v>
       </c>
       <c r="AA2" t="n">
-        <v>3.07343608622063e-05</v>
+        <v>3.073436086220624e-05</v>
       </c>
       <c r="AB2" t="n">
-        <v>4.089685596351153e-05</v>
+        <v>4.089685596351149e-05</v>
       </c>
     </row>
     <row r="3">
@@ -3782,85 +3782,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.214867747089098e-05</v>
+        <v>2.214867747089095e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>2.214867747089098e-05</v>
+        <v>2.214867747089095e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>2.214867747089098e-05</v>
+        <v>2.214867747089095e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>1.451631147773939e-05</v>
+        <v>1.451631147773935e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>2.214867747089098e-05</v>
+        <v>2.214867747089095e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>2.214867747089098e-05</v>
+        <v>2.214867747089095e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>2.214867747089098e-05</v>
+        <v>2.214867747089095e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>2.214867747089098e-05</v>
+        <v>2.214867747089095e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>2.212632994259739e-05</v>
+        <v>2.212632994259736e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>2.214867747089098e-05</v>
+        <v>2.214867747089095e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>2.214867747089098e-05</v>
+        <v>2.214867747089095e-05</v>
       </c>
       <c r="M3" t="n">
-        <v>2.214867747089098e-05</v>
+        <v>2.214867747089095e-05</v>
       </c>
       <c r="N3" t="n">
-        <v>2.214867747089098e-05</v>
+        <v>2.214867747089095e-05</v>
       </c>
       <c r="O3" t="n">
-        <v>2.214867747089098e-05</v>
+        <v>2.214867747089095e-05</v>
       </c>
       <c r="P3" t="n">
-        <v>2.214867747089098e-05</v>
+        <v>2.214867747089095e-05</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.214867747089098e-05</v>
+        <v>2.214867747089095e-05</v>
       </c>
       <c r="R3" t="n">
-        <v>2.214867747089098e-05</v>
+        <v>2.214867747089095e-05</v>
       </c>
       <c r="S3" t="n">
-        <v>2.214867747089098e-05</v>
+        <v>2.214867747089095e-05</v>
       </c>
       <c r="T3" t="n">
-        <v>2.214867747089098e-05</v>
+        <v>2.214867747089095e-05</v>
       </c>
       <c r="U3" t="n">
-        <v>2.214867747089098e-05</v>
+        <v>2.214867747089095e-05</v>
       </c>
       <c r="V3" t="n">
-        <v>2.335885397383143e-05</v>
+        <v>2.335885397383145e-05</v>
       </c>
       <c r="W3" t="n">
-        <v>2.214867747089098e-05</v>
+        <v>2.214867747089095e-05</v>
       </c>
       <c r="X3" t="n">
-        <v>2.214867747089098e-05</v>
+        <v>2.214867747089095e-05</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.214867747089098e-05</v>
+        <v>2.214867747089095e-05</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.214867747089098e-05</v>
+        <v>2.214867747089095e-05</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.214867747089098e-05</v>
+        <v>2.214867747089095e-05</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.214867747089098e-05</v>
+        <v>2.214867747089095e-05</v>
       </c>
     </row>
     <row r="4">
@@ -3870,85 +3870,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.005032187723763301</v>
+        <v>0.005032187723763306</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0001257493891103886</v>
+        <v>0.0001257493891103883</v>
       </c>
       <c r="D4" t="n">
         <v>0.00168591559654674</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001373802677753827</v>
+        <v>0.001373802677753823</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001107928151022546</v>
+        <v>0.001107928151022547</v>
       </c>
       <c r="G4" t="n">
-        <v>0.001056063407223933</v>
+        <v>0.001056063407223936</v>
       </c>
       <c r="H4" t="n">
-        <v>7.995600150503566e-05</v>
+        <v>7.995600150503619e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>0.001941473954973273</v>
+        <v>0.001941473954973268</v>
       </c>
       <c r="J4" t="n">
-        <v>0.002117748337846609</v>
+        <v>0.002117748337846607</v>
       </c>
       <c r="K4" t="n">
-        <v>0.002723915510476495</v>
+        <v>0.002723915510476491</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01035012442252217</v>
+        <v>0.01035012442252215</v>
       </c>
       <c r="M4" t="n">
-        <v>0.003842060811202326</v>
+        <v>0.003842060811202315</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0005951910464915298</v>
+        <v>0.0005951910464915296</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0009055159558275617</v>
+        <v>0.0009055159558275642</v>
       </c>
       <c r="P4" t="n">
         <v>0.003267922216739402</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.00135694566630285</v>
+        <v>0.001356945666302848</v>
       </c>
       <c r="R4" t="n">
-        <v>0.0001867117060880104</v>
+        <v>0.0001867117060880103</v>
       </c>
       <c r="S4" t="n">
-        <v>0.003164524941038469</v>
+        <v>0.00316452494103846</v>
       </c>
       <c r="T4" t="n">
         <v>0.001635146630230124</v>
       </c>
       <c r="U4" t="n">
-        <v>0.006886322884947138</v>
+        <v>0.006886322884947168</v>
       </c>
       <c r="V4" t="n">
-        <v>0.001477058288435635</v>
+        <v>0.001477058288435639</v>
       </c>
       <c r="W4" t="n">
-        <v>0.001413162317643665</v>
+        <v>0.001413162317643663</v>
       </c>
       <c r="X4" t="n">
-        <v>0.005806172860094727</v>
+        <v>0.005806172860094733</v>
       </c>
       <c r="Y4" t="n">
         <v>0.002182937216894575</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.002634526652626531</v>
+        <v>0.002634526652626525</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.002257893528739796</v>
+        <v>0.002257893528739794</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.005317901869601431</v>
+        <v>0.005317901869601417</v>
       </c>
     </row>
     <row r="5">
@@ -3958,85 +3958,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.667173511348227e-05</v>
+        <v>1.667173511348218e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>1.66717351134823e-05</v>
+        <v>1.667173511348215e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>1.66717351134823e-05</v>
+        <v>1.667173511348215e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>1.66717351134823e-05</v>
+        <v>1.667173511348215e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>1.667173511348228e-05</v>
+        <v>1.667173511348217e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>1.66717351134823e-05</v>
+        <v>1.667173511348215e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>1.66717351134823e-05</v>
+        <v>1.667173511348215e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>1.66717351134823e-05</v>
+        <v>1.667173511348215e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>1.657968486122126e-05</v>
+        <v>1.657968486122118e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>1.66717351134823e-05</v>
+        <v>1.667173511348215e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>1.66717351134823e-05</v>
+        <v>1.667173511348217e-05</v>
       </c>
       <c r="M5" t="n">
-        <v>1.66717351134823e-05</v>
+        <v>1.667173511348215e-05</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0005951910464915297</v>
+        <v>1.667173511348217e-05</v>
       </c>
       <c r="O5" t="n">
-        <v>1.667173511348228e-05</v>
+        <v>1.667173511348217e-05</v>
       </c>
       <c r="P5" t="n">
-        <v>1.667173511348228e-05</v>
+        <v>1.667173511348217e-05</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.667173511348228e-05</v>
+        <v>1.667173511348217e-05</v>
       </c>
       <c r="R5" t="n">
-        <v>1.66717351134823e-05</v>
+        <v>1.667173511348215e-05</v>
       </c>
       <c r="S5" t="n">
-        <v>1.66717351134823e-05</v>
+        <v>1.667173511348215e-05</v>
       </c>
       <c r="T5" t="n">
-        <v>1.66717351134823e-05</v>
+        <v>1.667173511348215e-05</v>
       </c>
       <c r="U5" t="n">
-        <v>1.681729395933163e-05</v>
+        <v>1.681729395933154e-05</v>
       </c>
       <c r="V5" t="n">
-        <v>1.607987126909246e-05</v>
+        <v>1.607987126909243e-05</v>
       </c>
       <c r="W5" t="n">
-        <v>1.667173511348228e-05</v>
+        <v>1.667173511348217e-05</v>
       </c>
       <c r="X5" t="n">
-        <v>1.667173511348227e-05</v>
+        <v>1.667173511348218e-05</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.681729395933163e-05</v>
+        <v>1.681729395933154e-05</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.66717351134823e-05</v>
+        <v>1.667173511348215e-05</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.66717351134823e-05</v>
+        <v>1.667173511348215e-05</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.667173511348228e-05</v>
+        <v>1.667173511348217e-05</v>
       </c>
     </row>
     <row r="6">
@@ -4046,85 +4046,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.543659178292394e-05</v>
+        <v>4.543659178292372e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>2.667626628592833e-05</v>
+        <v>2.667626628592817e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>4.543659178292395e-05</v>
+        <v>4.543659178292369e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>4.543659178292395e-05</v>
+        <v>4.543659178292369e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>2.667626628592833e-05</v>
+        <v>2.667626628592817e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>2.667626628592833e-05</v>
+        <v>2.667626628592817e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>2.667626628592833e-05</v>
+        <v>2.667626628592817e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>2.667626628592833e-05</v>
+        <v>2.667626628592817e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>4.534454153066286e-05</v>
+        <v>4.534454153066274e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>4.543659178292395e-05</v>
+        <v>4.543659178292369e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>4.543659178292394e-05</v>
+        <v>4.543659178292372e-05</v>
       </c>
       <c r="M6" t="n">
-        <v>2.667626628592833e-05</v>
+        <v>2.667626628592817e-05</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0005951910464915298</v>
+        <v>2.71824113579891e-05</v>
       </c>
       <c r="O6" t="n">
-        <v>4.54096669493026e-05</v>
+        <v>4.540966694930235e-05</v>
       </c>
       <c r="P6" t="n">
-        <v>4.54200260173321e-05</v>
+        <v>4.542002601733181e-05</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.543659178292395e-05</v>
+        <v>4.543659178292369e-05</v>
       </c>
       <c r="R6" t="n">
-        <v>2.667626628592833e-05</v>
+        <v>2.667626628592817e-05</v>
       </c>
       <c r="S6" t="n">
-        <v>4.543659178292395e-05</v>
+        <v>4.543659178292369e-05</v>
       </c>
       <c r="T6" t="n">
-        <v>2.667626628592833e-05</v>
+        <v>2.667626628592817e-05</v>
       </c>
       <c r="U6" t="n">
-        <v>2.667626628592833e-05</v>
+        <v>2.667626628592817e-05</v>
       </c>
       <c r="V6" t="n">
-        <v>4.484472793853405e-05</v>
+        <v>4.484472793853407e-05</v>
       </c>
       <c r="W6" t="n">
-        <v>4.540836877831479e-05</v>
+        <v>4.540836877831454e-05</v>
       </c>
       <c r="X6" t="n">
-        <v>2.667626628592833e-05</v>
+        <v>2.667626628592817e-05</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.779578077401133e-05</v>
+        <v>2.779578077401319e-05</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.543659178292395e-05</v>
+        <v>4.543659178292369e-05</v>
       </c>
       <c r="AA6" t="n">
-        <v>4.543659178292395e-05</v>
+        <v>4.543659178292369e-05</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.779903080577255e-05</v>
+        <v>2.77990308057725e-05</v>
       </c>
     </row>
     <row r="7">
@@ -4134,85 +4134,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.97127272893084e-05</v>
+        <v>3.971272728930835e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>3.971272728930837e-05</v>
+        <v>3.971272728930832e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>3.971272728930837e-05</v>
+        <v>3.971272728930832e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>3.971272728930837e-05</v>
+        <v>3.971272728930832e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>3.971272728930837e-05</v>
+        <v>3.971272728930832e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>3.971272728930837e-05</v>
+        <v>3.971272728930832e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>3.971272728930837e-05</v>
+        <v>3.971272728930832e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>3.971272728930837e-05</v>
+        <v>3.971272728930832e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>3.962067703704759e-05</v>
+        <v>3.962067703704743e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>3.971272728930837e-05</v>
+        <v>3.971272728930832e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>3.97127272893084e-05</v>
+        <v>3.971272728930835e-05</v>
       </c>
       <c r="M7" t="n">
-        <v>3.971272728930837e-05</v>
+        <v>3.971272728930832e-05</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0005951910464915298</v>
+        <v>3.971272728930832e-05</v>
       </c>
       <c r="O7" t="n">
-        <v>3.970447318635015e-05</v>
+        <v>3.970447318635e-05</v>
       </c>
       <c r="P7" t="n">
-        <v>3.970447318635015e-05</v>
+        <v>3.970447318635e-05</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.971272728930837e-05</v>
+        <v>3.971272728930832e-05</v>
       </c>
       <c r="R7" t="n">
-        <v>3.971272728930837e-05</v>
+        <v>3.971272728930832e-05</v>
       </c>
       <c r="S7" t="n">
-        <v>3.971272728930837e-05</v>
+        <v>3.971272728930832e-05</v>
       </c>
       <c r="T7" t="n">
-        <v>3.971272728930837e-05</v>
+        <v>3.971272728930832e-05</v>
       </c>
       <c r="U7" t="n">
-        <v>3.972132137948054e-05</v>
+        <v>3.972132137948052e-05</v>
       </c>
       <c r="V7" t="n">
-        <v>3.912086344491868e-05</v>
+        <v>3.91208634449187e-05</v>
       </c>
       <c r="W7" t="n">
-        <v>3.971272728930837e-05</v>
+        <v>3.971272728930832e-05</v>
       </c>
       <c r="X7" t="n">
-        <v>3.97127272893084e-05</v>
+        <v>3.971272728930835e-05</v>
       </c>
       <c r="Y7" t="n">
-        <v>3.971272728930837e-05</v>
+        <v>3.971272728930832e-05</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.971272728930837e-05</v>
+        <v>3.971272728930832e-05</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.971272728930837e-05</v>
+        <v>3.971272728930832e-05</v>
       </c>
       <c r="AB7" t="n">
-        <v>3.971272728930837e-05</v>
+        <v>3.971272728930832e-05</v>
       </c>
     </row>
     <row r="8">
@@ -4222,82 +4222,82 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8.311981998516405e-05</v>
+        <v>8.311981998516408e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0001284129444879369</v>
+        <v>0.0001284129444879366</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0001284129444879369</v>
+        <v>0.0001284129444879366</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0001042956917543492</v>
+        <v>0.000104295691754349</v>
       </c>
       <c r="F8" t="n">
-        <v>9.017595943049176e-05</v>
+        <v>9.01759594304917e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0001378047689106897</v>
+        <v>0.0001378047689106896</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0001284129444879369</v>
+        <v>0.0001284129444879366</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0001284129444879369</v>
+        <v>0.0001284129444879366</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0001283208942356756</v>
+        <v>0.0001283208942356755</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0001284129444879369</v>
+        <v>0.0001284129444879366</v>
       </c>
       <c r="L8" t="n">
-        <v>0.000128412944487937</v>
+        <v>0.0001284129444879366</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0001284129444879335</v>
+        <v>0.0001284129444879333</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0005951910464915298</v>
+        <v>9.330319562300741e-05</v>
       </c>
       <c r="O8" t="n">
-        <v>0.0001029516594626676</v>
+        <v>0.0001029516594626675</v>
       </c>
       <c r="P8" t="n">
         <v>0.0001005865878361827</v>
       </c>
       <c r="Q8" t="n">
-        <v>7.421868725600237e-05</v>
+        <v>7.42186872560023e-05</v>
       </c>
       <c r="R8" t="n">
-        <v>0.0001284129444879369</v>
+        <v>0.0001284129444879366</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0001284129444879369</v>
+        <v>0.0001284129444879366</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0001284129444879369</v>
+        <v>0.0001284129444879366</v>
       </c>
       <c r="U8" t="n">
         <v>0.000106319031873353</v>
       </c>
       <c r="V8" t="n">
-        <v>0.0001154561881962012</v>
+        <v>0.0001154561881962011</v>
       </c>
       <c r="W8" t="n">
         <v>0.0001284218458822297</v>
       </c>
       <c r="X8" t="n">
-        <v>7.836989211396387e-05</v>
+        <v>7.83698921139639e-05</v>
       </c>
       <c r="Y8" t="n">
         <v>0.0001734692038608609</v>
       </c>
       <c r="Z8" t="n">
-        <v>8.227847694425087e-05</v>
+        <v>8.22784769442508e-05</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.0001284129444879369</v>
+        <v>0.0001284129444879366</v>
       </c>
       <c r="AB8" t="n">
         <v>0.000175725400378179</v>
@@ -4310,85 +4310,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.0001217200952227189</v>
+        <v>0.0001217200952227188</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0001521091819631256</v>
+        <v>0.0001521091819631253</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0001521091819631256</v>
+        <v>0.0001521091819631253</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0001450955115434043</v>
+        <v>0.0001450955115434042</v>
       </c>
       <c r="F9" t="n">
-        <v>8.205403144209757e-05</v>
+        <v>8.205403144209747e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0001521091908621428</v>
+        <v>0.0001521091908621426</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0001521091819631256</v>
+        <v>0.0001521091819631253</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0001521091819631256</v>
+        <v>0.0001521091819631253</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0001520171317108646</v>
+        <v>0.0001520171317108645</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0001521091819631256</v>
+        <v>0.0001521091819631253</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0001521091819631256</v>
+        <v>0.0001521091819631254</v>
       </c>
       <c r="M9" t="n">
-        <v>0.0001521091819631256</v>
+        <v>0.0001521091819631253</v>
       </c>
       <c r="N9" t="n">
-        <v>0.0005951910464915298</v>
+        <v>0.0001521091819631253</v>
       </c>
       <c r="O9" t="n">
-        <v>0.0001621800973660456</v>
+        <v>0.0001621800973660455</v>
       </c>
       <c r="P9" t="n">
         <v>0.000164370346742887</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.0001521091908621428</v>
+        <v>0.0001521091908621426</v>
       </c>
       <c r="R9" t="n">
-        <v>0.0001521091819631256</v>
+        <v>0.0001521091819631253</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0001521091819631256</v>
+        <v>0.0001521091819631253</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0001521091819631256</v>
+        <v>0.0001521091819631253</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0001521091819631256</v>
+        <v>0.0001521091819631253</v>
       </c>
       <c r="V9" t="n">
         <v>0.0001865856301661527</v>
       </c>
       <c r="W9" t="n">
-        <v>0.0001521091819631256</v>
+        <v>0.0001521091819631253</v>
       </c>
       <c r="X9" t="n">
-        <v>0.0001521091819631256</v>
+        <v>0.0001521091819631254</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.0001521091819631256</v>
+        <v>0.0001521091819631253</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.0001337872684953964</v>
+        <v>0.0001337872684953962</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.0001521091819631256</v>
+        <v>0.0001521091819631253</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.0001521091819631256</v>
+        <v>0.0001521091819631253</v>
       </c>
     </row>
     <row r="10">
@@ -4398,85 +4398,85 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-0.0001030815422521872</v>
+        <v>-0.0001030815422521875</v>
       </c>
       <c r="C10" t="n">
-        <v>2.043600400102554e-05</v>
+        <v>2.04360040010255e-05</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.455645827235936e-05</v>
+        <v>-1.455645827235944e-05</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.727124498237737e-05</v>
+        <v>-1.727124498237734e-05</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.663197367975486e-06</v>
+        <v>-1.66319736797556e-06</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.430351796662194e-06</v>
+        <v>-3.430351796662362e-06</v>
       </c>
       <c r="H10" t="n">
-        <v>2.13189050841093e-05</v>
+        <v>2.131890508410926e-05</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.949684553571105e-05</v>
+        <v>-1.949684553571104e-05</v>
       </c>
       <c r="J10" t="n">
-        <v>-2.784196921839656e-05</v>
+        <v>-2.784196921839655e-05</v>
       </c>
       <c r="K10" t="n">
-        <v>-4.515714562595932e-05</v>
+        <v>-4.515714562595941e-05</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.0002213266447396586</v>
+        <v>-0.0002213266447396581</v>
       </c>
       <c r="M10" t="n">
         <v>-6.100323596796693e-05</v>
       </c>
       <c r="N10" t="n">
-        <v>9.481131611122797e-06</v>
+        <v>9.481131611122753e-06</v>
       </c>
       <c r="O10" t="n">
-        <v>-6.104734145222011e-07</v>
+        <v>-6.104734145223155e-07</v>
       </c>
       <c r="P10" t="n">
-        <v>-5.953697676683307e-05</v>
+        <v>-5.953697676683314e-05</v>
       </c>
       <c r="Q10" t="n">
-        <v>-8.433630794623123e-06</v>
+        <v>-8.433630794623104e-06</v>
       </c>
       <c r="R10" t="n">
-        <v>1.897867148854856e-05</v>
+        <v>1.897867148854848e-05</v>
       </c>
       <c r="S10" t="n">
-        <v>-5.595971563289481e-05</v>
+        <v>-5.595971563289486e-05</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.30528162498605e-05</v>
+        <v>-1.305281624986058e-05</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.000144645831693094</v>
+        <v>-0.0001446458316930944</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.449987307113634e-05</v>
+        <v>-1.449987307113631e-05</v>
       </c>
       <c r="W10" t="n">
-        <v>-9.829900138411796e-06</v>
+        <v>-9.829900138411759e-06</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.0001084440081463479</v>
+        <v>-0.0001084440081463478</v>
       </c>
       <c r="Y10" t="n">
-        <v>-2.81030492970518e-05</v>
+        <v>-2.810304929705194e-05</v>
       </c>
       <c r="Z10" t="n">
-        <v>-4.650692961930925e-05</v>
+        <v>-4.650692961930915e-05</v>
       </c>
       <c r="AA10" t="n">
-        <v>-2.941304875784268e-05</v>
+        <v>-2.941304875784262e-05</v>
       </c>
       <c r="AB10" t="n">
-        <v>-8.856791298111223e-05</v>
+        <v>-8.856791298111219e-05</v>
       </c>
     </row>
     <row r="11">
@@ -4486,85 +4486,85 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-1.393929696214949e-05</v>
+        <v>-1.393929696214967e-05</v>
       </c>
       <c r="C11" t="n">
-        <v>2.150372770044655e-05</v>
+        <v>2.150372770044653e-05</v>
       </c>
       <c r="D11" t="n">
-        <v>1.15563197972602e-05</v>
+        <v>1.155631979726014e-05</v>
       </c>
       <c r="E11" t="n">
-        <v>5.37311669085287e-06</v>
+        <v>5.373116690852847e-06</v>
       </c>
       <c r="F11" t="n">
-        <v>1.524162778751838e-05</v>
+        <v>1.524162778751829e-05</v>
       </c>
       <c r="G11" t="n">
-        <v>1.465428238301684e-05</v>
+        <v>1.465428238301676e-05</v>
       </c>
       <c r="H11" t="n">
-        <v>2.175608966283859e-05</v>
+        <v>2.175608966283853e-05</v>
       </c>
       <c r="I11" t="n">
-        <v>1.016520188588812e-05</v>
+        <v>1.016520188588806e-05</v>
       </c>
       <c r="J11" t="n">
-        <v>7.693526890985363e-06</v>
+        <v>7.693526890985331e-06</v>
       </c>
       <c r="K11" t="n">
-        <v>2.840791781031474e-06</v>
+        <v>2.840791781031435e-06</v>
       </c>
       <c r="L11" t="n">
-        <v>-4.760680207877055e-05</v>
+        <v>-4.760680207877045e-05</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.593592198900758e-06</v>
+        <v>-1.593592198900854e-06</v>
       </c>
       <c r="N11" t="n">
-        <v>1.838064824534031e-05</v>
+        <v>1.838064824534026e-05</v>
       </c>
       <c r="O11" t="n">
-        <v>1.545677405010286e-05</v>
+        <v>1.545677405010283e-05</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.472936878899658e-06</v>
+        <v>-1.472936878899785e-06</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.328359690366627e-05</v>
+        <v>1.328359690366624e-05</v>
       </c>
       <c r="R11" t="n">
-        <v>2.109195440015914e-05</v>
+        <v>2.109195440015908e-05</v>
       </c>
       <c r="S11" t="n">
-        <v>-3.787642524778939e-07</v>
+        <v>-3.787642524779684e-07</v>
       </c>
       <c r="T11" t="n">
-        <v>1.198760286668346e-05</v>
+        <v>1.198760286668335e-05</v>
       </c>
       <c r="U11" t="n">
-        <v>-2.571565503647502e-05</v>
+        <v>-2.571565503647505e-05</v>
       </c>
       <c r="V11" t="n">
-        <v>1.232908322600949e-05</v>
+        <v>1.232908322600953e-05</v>
       </c>
       <c r="W11" t="n">
-        <v>1.28588254753673e-05</v>
+        <v>1.285882547536722e-05</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.51557352284121e-05</v>
+        <v>-1.515573522841217e-05</v>
       </c>
       <c r="Y11" t="n">
-        <v>7.654376655945516e-06</v>
+        <v>7.654376655945403e-06</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.305479959878899e-06</v>
+        <v>2.305479959878909e-06</v>
       </c>
       <c r="AA11" t="n">
-        <v>7.273611110660617e-06</v>
+        <v>7.273611110660598e-06</v>
       </c>
       <c r="AB11" t="n">
-        <v>-9.479545524988699e-06</v>
+        <v>-9.47954552498875e-06</v>
       </c>
     </row>
   </sheetData>
@@ -4730,85 +4730,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.215143268673831e-05</v>
+        <v>4.215143268673842e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>2.479107852098311e-05</v>
+        <v>2.479107852098306e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>2.982809755095223e-05</v>
+        <v>2.98280975509523e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>1.83154972857024e-05</v>
+        <v>1.831549728570245e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>2.894453225290402e-05</v>
+        <v>2.894453225290396e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>2.839859097145924e-05</v>
+        <v>2.839859097145933e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>2.437918814856142e-05</v>
+        <v>2.437918814856138e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>3.214371553255962e-05</v>
+        <v>3.214371553255966e-05</v>
       </c>
       <c r="J2" t="n">
         <v>3.303930236155744e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>3.759026989846472e-05</v>
+        <v>3.759026989846479e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>5.804516689337226e-05</v>
+        <v>5.804516689337229e-05</v>
       </c>
       <c r="M2" t="n">
-        <v>3.693044957356874e-05</v>
+        <v>3.693044957356871e-05</v>
       </c>
       <c r="N2" t="n">
-        <v>2.606504722512852e-05</v>
+        <v>2.606504722512858e-05</v>
       </c>
       <c r="O2" t="n">
-        <v>2.682481886517166e-05</v>
+        <v>2.68248188651716e-05</v>
       </c>
       <c r="P2" t="n">
-        <v>3.683711449470132e-05</v>
+        <v>3.683711449470128e-05</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.101568239606937e-05</v>
+        <v>3.101568239606935e-05</v>
       </c>
       <c r="R2" t="n">
-        <v>2.594275438569588e-05</v>
+        <v>2.594275438569582e-05</v>
       </c>
       <c r="S2" t="n">
-        <v>3.656811864648269e-05</v>
+        <v>3.656811864648278e-05</v>
       </c>
       <c r="T2" t="n">
-        <v>3.037628165023271e-05</v>
+        <v>3.037628165023268e-05</v>
       </c>
       <c r="U2" t="n">
-        <v>5.592307602392652e-05</v>
+        <v>5.592307602392659e-05</v>
       </c>
       <c r="V2" t="n">
-        <v>4.029570332275698e-05</v>
+        <v>4.029570332275701e-05</v>
       </c>
       <c r="W2" t="n">
-        <v>3.069751757034187e-05</v>
+        <v>3.069751757034182e-05</v>
       </c>
       <c r="X2" t="n">
-        <v>4.939592515855727e-05</v>
+        <v>4.939592515855728e-05</v>
       </c>
       <c r="Y2" t="n">
-        <v>3.803123970009911e-05</v>
+        <v>3.803123970009907e-05</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.546327031111371e-05</v>
+        <v>3.546327031111366e-05</v>
       </c>
       <c r="AA2" t="n">
-        <v>3.354271516533051e-05</v>
+        <v>3.354271516533053e-05</v>
       </c>
       <c r="AB2" t="n">
-        <v>4.214550549765687e-05</v>
+        <v>4.214550549765693e-05</v>
       </c>
     </row>
     <row r="3">
@@ -4818,85 +4818,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.437419557101792e-05</v>
+        <v>2.437419557101797e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>2.437419557101792e-05</v>
+        <v>2.437419557101797e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>2.437419557101792e-05</v>
+        <v>2.437419557101797e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>1.440960169901316e-05</v>
+        <v>1.440960169901322e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>2.437419557101792e-05</v>
+        <v>2.437419557101797e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>2.437419557101792e-05</v>
+        <v>2.437419557101797e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>2.437419557101792e-05</v>
+        <v>2.437419557101797e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>2.437419557101792e-05</v>
+        <v>2.437419557101797e-05</v>
       </c>
       <c r="J3" t="n">
         <v>2.458853939301637e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>2.437419557101792e-05</v>
+        <v>2.437419557101797e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>2.437419557101792e-05</v>
+        <v>2.437419557101797e-05</v>
       </c>
       <c r="M3" t="n">
-        <v>2.437419557101792e-05</v>
+        <v>2.437419557101797e-05</v>
       </c>
       <c r="N3" t="n">
-        <v>2.437419557101792e-05</v>
+        <v>2.437419557101797e-05</v>
       </c>
       <c r="O3" t="n">
-        <v>2.437419557101792e-05</v>
+        <v>2.437419557101797e-05</v>
       </c>
       <c r="P3" t="n">
-        <v>2.437419557101792e-05</v>
+        <v>2.437419557101797e-05</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.437419557101792e-05</v>
+        <v>2.437419557101797e-05</v>
       </c>
       <c r="R3" t="n">
-        <v>2.437419557101792e-05</v>
+        <v>2.437419557101797e-05</v>
       </c>
       <c r="S3" t="n">
-        <v>2.437419557101792e-05</v>
+        <v>2.437419557101797e-05</v>
       </c>
       <c r="T3" t="n">
-        <v>2.437419557101792e-05</v>
+        <v>2.437419557101797e-05</v>
       </c>
       <c r="U3" t="n">
-        <v>2.437419557101792e-05</v>
+        <v>2.437419557101797e-05</v>
       </c>
       <c r="V3" t="n">
-        <v>2.891320775068855e-05</v>
+        <v>2.891320775068844e-05</v>
       </c>
       <c r="W3" t="n">
-        <v>2.437419557101792e-05</v>
+        <v>2.437419557101797e-05</v>
       </c>
       <c r="X3" t="n">
-        <v>2.437419557101792e-05</v>
+        <v>2.437419557101797e-05</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.437419557101792e-05</v>
+        <v>2.437419557101797e-05</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.437419557101792e-05</v>
+        <v>2.437419557101797e-05</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.437419557101792e-05</v>
+        <v>2.437419557101797e-05</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.437419557101792e-05</v>
+        <v>2.437419557101797e-05</v>
       </c>
     </row>
     <row r="4">
@@ -4906,34 +4906,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.00415881291039549</v>
+        <v>0.004158812910395501</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0002031433672749259</v>
+        <v>0.0002031433672749257</v>
       </c>
       <c r="D4" t="n">
         <v>0.001465298023295416</v>
       </c>
       <c r="E4" t="n">
-        <v>0.000962600985606608</v>
+        <v>0.0009626009856066099</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001272854405811688</v>
+        <v>0.001272854405811686</v>
       </c>
       <c r="G4" t="n">
-        <v>0.001007088498027098</v>
+        <v>0.001007088498027096</v>
       </c>
       <c r="H4" t="n">
-        <v>9.279728732822543e-05</v>
+        <v>9.279728732822687e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>0.002126369287277978</v>
+        <v>0.002126369287277977</v>
       </c>
       <c r="J4" t="n">
-        <v>0.002101800641476616</v>
+        <v>0.002101800641476611</v>
       </c>
       <c r="K4" t="n">
-        <v>0.003177465219967902</v>
+        <v>0.003177465219967909</v>
       </c>
       <c r="L4" t="n">
         <v>0.008166506963937961</v>
@@ -4942,49 +4942,49 @@
         <v>0.003296891449572734</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0005253442406829216</v>
+        <v>0.0005253442406829208</v>
       </c>
       <c r="O4" t="n">
-        <v>0.000642983991579147</v>
+        <v>0.000642983991579146</v>
       </c>
       <c r="P4" t="n">
-        <v>0.002915835721525768</v>
+        <v>0.002915835721525767</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.00172269988976571</v>
+        <v>0.001722699889765714</v>
       </c>
       <c r="R4" t="n">
-        <v>0.0005157250645330891</v>
+        <v>0.0005157250645330892</v>
       </c>
       <c r="S4" t="n">
-        <v>0.002937160491751646</v>
+        <v>0.00293716049175165</v>
       </c>
       <c r="T4" t="n">
-        <v>0.001683798825184264</v>
+        <v>0.001683798825184267</v>
       </c>
       <c r="U4" t="n">
-        <v>0.00745897667112206</v>
+        <v>0.007458976671122068</v>
       </c>
       <c r="V4" t="n">
-        <v>0.002625050427372949</v>
+        <v>0.002625050427372943</v>
       </c>
       <c r="W4" t="n">
-        <v>0.001693208402809576</v>
+        <v>0.001693208402809574</v>
       </c>
       <c r="X4" t="n">
-        <v>0.006355129122323125</v>
+        <v>0.006355129122323123</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.003588821264127751</v>
+        <v>0.00358882126412775</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.00243350080790101</v>
+        <v>0.002433500807901012</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.002427111898712938</v>
+        <v>0.002427111898712937</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.004978720696248792</v>
+        <v>0.004978720696248781</v>
       </c>
     </row>
     <row r="5">
@@ -4994,85 +4994,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.182212585185995e-05</v>
+        <v>2.182212585186021e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>2.182212585185994e-05</v>
+        <v>2.182212585186027e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>2.182212585185994e-05</v>
+        <v>2.182212585186027e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>2.182212585185994e-05</v>
+        <v>2.182212585186027e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>2.182212585185992e-05</v>
+        <v>2.182212585185999e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>2.182212585185994e-05</v>
+        <v>2.182212585186027e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>2.182212585185994e-05</v>
+        <v>2.182212585186027e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>2.182212585185994e-05</v>
+        <v>2.182212585186027e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>2.177904723224619e-05</v>
+        <v>2.177904723224635e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>2.182212585185994e-05</v>
+        <v>2.182212585186027e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>2.182212585185996e-05</v>
+        <v>2.182212585186028e-05</v>
       </c>
       <c r="M5" t="n">
-        <v>2.182212585185994e-05</v>
+        <v>2.182212585186027e-05</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0005253442406829216</v>
+        <v>2.182212585185999e-05</v>
       </c>
       <c r="O5" t="n">
-        <v>2.182212585185992e-05</v>
+        <v>2.182212585185999e-05</v>
       </c>
       <c r="P5" t="n">
-        <v>2.182212585185992e-05</v>
+        <v>2.182212585185999e-05</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.182212585185992e-05</v>
+        <v>2.182212585185999e-05</v>
       </c>
       <c r="R5" t="n">
-        <v>2.182212585185994e-05</v>
+        <v>2.182212585186027e-05</v>
       </c>
       <c r="S5" t="n">
-        <v>2.182212585185994e-05</v>
+        <v>2.182212585186027e-05</v>
       </c>
       <c r="T5" t="n">
-        <v>2.182212585185994e-05</v>
+        <v>2.182212585186027e-05</v>
       </c>
       <c r="U5" t="n">
-        <v>2.318080271867326e-05</v>
+        <v>2.318080271867347e-05</v>
       </c>
       <c r="V5" t="n">
-        <v>2.154324547719724e-05</v>
+        <v>2.154324547719713e-05</v>
       </c>
       <c r="W5" t="n">
-        <v>2.182212585185992e-05</v>
+        <v>2.182212585185999e-05</v>
       </c>
       <c r="X5" t="n">
-        <v>2.182212585185996e-05</v>
+        <v>2.182212585185999e-05</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.318080271867326e-05</v>
+        <v>2.318080271867347e-05</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.182212585185994e-05</v>
+        <v>2.182212585186027e-05</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.182212585185994e-05</v>
+        <v>2.182212585186027e-05</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.182212585185992e-05</v>
+        <v>2.182212585185999e-05</v>
       </c>
     </row>
     <row r="6">
@@ -5082,85 +5082,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.498056233697078e-05</v>
+        <v>3.498056233697091e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>3.498056233697078e-05</v>
+        <v>3.498056233697091e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>5.417465842612538e-05</v>
+        <v>5.417465842612584e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>5.417465842612538e-05</v>
+        <v>5.417465842612584e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>3.498056233697078e-05</v>
+        <v>3.498056233697091e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>3.498056233697078e-05</v>
+        <v>3.498056233697091e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>5.417465842612538e-05</v>
+        <v>5.417465842612584e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>3.498056233697078e-05</v>
+        <v>3.498056233697091e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>5.413157980651159e-05</v>
+        <v>5.413157980651157e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>5.417465842612538e-05</v>
+        <v>5.417465842612584e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>3.498056233697078e-05</v>
+        <v>3.498056233697091e-05</v>
       </c>
       <c r="M6" t="n">
-        <v>3.498056233697078e-05</v>
+        <v>3.498056233697091e-05</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0005253442406829216</v>
+        <v>3.585049145720495e-05</v>
       </c>
       <c r="O6" t="n">
-        <v>3.584428897447287e-05</v>
+        <v>3.584428897447475e-05</v>
       </c>
       <c r="P6" t="n">
-        <v>5.436003771988649e-05</v>
+        <v>5.436003771988677e-05</v>
       </c>
       <c r="Q6" t="n">
-        <v>5.417465842612538e-05</v>
+        <v>5.417465842612584e-05</v>
       </c>
       <c r="R6" t="n">
-        <v>5.417465842612538e-05</v>
+        <v>5.417465842612584e-05</v>
       </c>
       <c r="S6" t="n">
-        <v>3.498056233697078e-05</v>
+        <v>3.498056233697091e-05</v>
       </c>
       <c r="T6" t="n">
-        <v>5.417465842612538e-05</v>
+        <v>5.417465842612584e-05</v>
       </c>
       <c r="U6" t="n">
-        <v>5.417465842612538e-05</v>
+        <v>5.417465842612584e-05</v>
       </c>
       <c r="V6" t="n">
-        <v>3.470168196230815e-05</v>
+        <v>3.47016819623078e-05</v>
       </c>
       <c r="W6" t="n">
-        <v>3.608799545602594e-05</v>
+        <v>3.608799545602599e-05</v>
       </c>
       <c r="X6" t="n">
-        <v>3.498056233697078e-05</v>
+        <v>3.498056233697091e-05</v>
       </c>
       <c r="Y6" t="n">
-        <v>3.683768748891244e-05</v>
+        <v>3.683768748891246e-05</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.498056233697078e-05</v>
+        <v>3.498056233697091e-05</v>
       </c>
       <c r="AA6" t="n">
-        <v>5.417465842612538e-05</v>
+        <v>5.417465842612584e-05</v>
       </c>
       <c r="AB6" t="n">
-        <v>3.613839503981968e-05</v>
+        <v>3.613839503982004e-05</v>
       </c>
     </row>
     <row r="7">
@@ -5170,85 +5170,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.612949858805678e-05</v>
+        <v>4.612949858805684e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>4.612949858805671e-05</v>
+        <v>4.612949858805684e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>4.612949858805671e-05</v>
+        <v>4.612949858805684e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>4.612949858805671e-05</v>
+        <v>4.612949858805684e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>4.612949858805671e-05</v>
+        <v>4.612949858805684e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>4.612949858805671e-05</v>
+        <v>4.612949858805684e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>4.612949858805671e-05</v>
+        <v>4.612949858805684e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>4.612949858805671e-05</v>
+        <v>4.612949858805684e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>4.608641996844281e-05</v>
+        <v>4.608641996844289e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>4.612949858805671e-05</v>
+        <v>4.612949858805684e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>4.612949858805678e-05</v>
+        <v>4.612949858805684e-05</v>
       </c>
       <c r="M7" t="n">
-        <v>4.612949858805671e-05</v>
+        <v>4.612949858805684e-05</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0005253442406829216</v>
+        <v>4.612949858805684e-05</v>
       </c>
       <c r="O7" t="n">
-        <v>4.612108226810108e-05</v>
+        <v>4.612108226810124e-05</v>
       </c>
       <c r="P7" t="n">
-        <v>4.612108226810108e-05</v>
+        <v>4.612108226810124e-05</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.612949858805671e-05</v>
+        <v>4.612949858805684e-05</v>
       </c>
       <c r="R7" t="n">
-        <v>4.612949858805671e-05</v>
+        <v>4.612949858805684e-05</v>
       </c>
       <c r="S7" t="n">
-        <v>4.612949858805671e-05</v>
+        <v>4.612949858805684e-05</v>
       </c>
       <c r="T7" t="n">
-        <v>4.612949858805671e-05</v>
+        <v>4.612949858805684e-05</v>
       </c>
       <c r="U7" t="n">
-        <v>4.625400729220614e-05</v>
+        <v>4.625400729220606e-05</v>
       </c>
       <c r="V7" t="n">
-        <v>4.585061821339399e-05</v>
+        <v>4.585061821339365e-05</v>
       </c>
       <c r="W7" t="n">
-        <v>4.612949858805671e-05</v>
+        <v>4.612949858805684e-05</v>
       </c>
       <c r="X7" t="n">
-        <v>4.612949858805678e-05</v>
+        <v>4.612949858805684e-05</v>
       </c>
       <c r="Y7" t="n">
-        <v>4.612949858805671e-05</v>
+        <v>4.612949858805684e-05</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.612949858805671e-05</v>
+        <v>4.612949858805684e-05</v>
       </c>
       <c r="AA7" t="n">
-        <v>4.612949858805671e-05</v>
+        <v>4.612949858805684e-05</v>
       </c>
       <c r="AB7" t="n">
-        <v>4.612949858805671e-05</v>
+        <v>4.612949858805684e-05</v>
       </c>
     </row>
     <row r="8">
@@ -5258,34 +5258,34 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8.963862976742281e-05</v>
+        <v>8.963862976742277e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0001359926344103975</v>
+        <v>0.0001359926344103976</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0001359926344103975</v>
+        <v>0.0001359926344103976</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0001113104942965033</v>
+        <v>0.0001113104942965034</v>
       </c>
       <c r="F8" t="n">
-        <v>9.686004193960561e-05</v>
+        <v>9.686004193960556e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>0.000145604439241058</v>
+        <v>0.0001456044392410577</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0001359926344103975</v>
+        <v>0.0001359926344103976</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0001359926344103975</v>
+        <v>0.0001359926344103976</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0001359495557907837</v>
+        <v>0.0001359495557907836</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0001359926344103975</v>
+        <v>0.0001359926344103976</v>
       </c>
       <c r="L8" t="n">
         <v>0.0001359926344103976</v>
@@ -5294,46 +5294,46 @@
         <v>0.0001359926344103879</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0005253442406829216</v>
+        <v>0.000100060525954951</v>
       </c>
       <c r="O8" t="n">
         <v>0.0001099349813495688</v>
       </c>
       <c r="P8" t="n">
-        <v>0.0001075145137323424</v>
+        <v>0.0001075145137323426</v>
       </c>
       <c r="Q8" t="n">
-        <v>8.052900987779174e-05</v>
+        <v>8.052900987779197e-05</v>
       </c>
       <c r="R8" t="n">
-        <v>0.0001359926344103975</v>
+        <v>0.0001359926344103976</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0001359926344103975</v>
+        <v>0.0001359926344103976</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0001359926344103975</v>
+        <v>0.0001359926344103976</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0001134708770522474</v>
+        <v>0.0001134708770522473</v>
       </c>
       <c r="V8" t="n">
-        <v>0.0001231581266502504</v>
+        <v>0.0001231581266502502</v>
       </c>
       <c r="W8" t="n">
         <v>0.0001360017442962053</v>
       </c>
       <c r="X8" t="n">
-        <v>8.477744650749383e-05</v>
+        <v>8.4777446507494e-05</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.0001822575924908476</v>
+        <v>0.0001822575924908475</v>
       </c>
       <c r="Z8" t="n">
-        <v>8.877758033340174e-05</v>
+        <v>8.877758033340196e-05</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.0001359926344103975</v>
+        <v>0.0001359926344103976</v>
       </c>
       <c r="AB8" t="n">
         <v>0.0001844132683147284</v>
@@ -5346,85 +5346,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.0001264603994702234</v>
+        <v>0.0001264603994702233</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0001568193871121603</v>
+        <v>0.0001568193871121606</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0001568193871121603</v>
+        <v>0.0001568193871121606</v>
       </c>
       <c r="E9" t="n">
         <v>0.0001498126605328812</v>
       </c>
       <c r="F9" t="n">
-        <v>8.683362816376329e-05</v>
+        <v>8.683362816376341e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0001568193922297198</v>
+        <v>0.0001568193922297197</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0001568193871121603</v>
+        <v>0.0001568193871121606</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0001568193871121603</v>
+        <v>0.0001568193871121606</v>
       </c>
       <c r="J9" t="n">
-        <v>0.000156776308492547</v>
+        <v>0.0001567763084925468</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0001568193871121603</v>
+        <v>0.0001568193871121606</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0001568193871121602</v>
+        <v>0.0001568193871121607</v>
       </c>
       <c r="M9" t="n">
-        <v>0.0001568193871121603</v>
+        <v>0.0001568193871121606</v>
       </c>
       <c r="N9" t="n">
-        <v>0.0005253442406829216</v>
+        <v>0.0001568193871121606</v>
       </c>
       <c r="O9" t="n">
         <v>0.0001668803226786305</v>
       </c>
       <c r="P9" t="n">
-        <v>0.0001690684024346716</v>
+        <v>0.0001690684024346713</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.0001568193922297198</v>
+        <v>0.0001568193922297197</v>
       </c>
       <c r="R9" t="n">
-        <v>0.0001568193871121603</v>
+        <v>0.0001568193871121606</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0001568193871121603</v>
+        <v>0.0001568193871121606</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0001568193871121603</v>
+        <v>0.0001568193871121606</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0001568193871121603</v>
+        <v>0.0001568193871121606</v>
       </c>
       <c r="V9" t="n">
-        <v>0.0001915740991507644</v>
+        <v>0.0001915740991507637</v>
       </c>
       <c r="W9" t="n">
-        <v>0.0001568193871121603</v>
+        <v>0.0001568193871121606</v>
       </c>
       <c r="X9" t="n">
-        <v>0.0001568193871121602</v>
+        <v>0.0001568193871121607</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.0001568193871121603</v>
+        <v>0.0001568193871121606</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.000138515619222717</v>
+        <v>0.0001385156192227172</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.0001568193871121603</v>
+        <v>0.0001568193871121606</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.0001568193871121603</v>
+        <v>0.0001568193871121606</v>
       </c>
     </row>
     <row r="10">
@@ -5434,85 +5434,85 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-8.239044615522818e-05</v>
+        <v>-8.239044615522816e-05</v>
       </c>
       <c r="C10" t="n">
-        <v>2.093970782172137e-05</v>
+        <v>2.093970782172138e-05</v>
       </c>
       <c r="D10" t="n">
-        <v>-8.560759586127696e-06</v>
+        <v>-8.560759586127418e-06</v>
       </c>
       <c r="E10" t="n">
-        <v>-8.868035240644054e-06</v>
+        <v>-8.86803524064402e-06</v>
       </c>
       <c r="F10" t="n">
-        <v>-3.249547681731153e-06</v>
+        <v>-3.249547681730965e-06</v>
       </c>
       <c r="G10" t="n">
-        <v>-5.585086995542362e-07</v>
+        <v>-5.585086995540842e-07</v>
       </c>
       <c r="H10" t="n">
-        <v>2.336360717715919e-05</v>
+        <v>2.336360717715915e-05</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.203743246335664e-05</v>
+        <v>-2.20374324633566e-05</v>
       </c>
       <c r="J10" t="n">
-        <v>-2.628864200121025e-05</v>
+        <v>-2.628864200121009e-05</v>
       </c>
       <c r="K10" t="n">
-        <v>-5.413914882805535e-05</v>
+        <v>-5.413914882805539e-05</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.0001756813350883593</v>
+        <v>-0.0001756813350883594</v>
       </c>
       <c r="M10" t="n">
-        <v>-4.98799633120998e-05</v>
+        <v>-4.98799633120997e-05</v>
       </c>
       <c r="N10" t="n">
-        <v>1.343513990887184e-05</v>
+        <v>1.343513990887189e-05</v>
       </c>
       <c r="O10" t="n">
-        <v>8.773211488178912e-06</v>
+        <v>8.773211488178985e-06</v>
       </c>
       <c r="P10" t="n">
-        <v>-5.092340368502455e-05</v>
+        <v>-5.092340368502443e-05</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.561920297369389e-05</v>
+        <v>-1.56192029736939e-05</v>
       </c>
       <c r="R10" t="n">
-        <v>1.423805092097086e-05</v>
+        <v>1.423805092097089e-05</v>
       </c>
       <c r="S10" t="n">
-        <v>-4.894711657011943e-05</v>
+        <v>-4.894711657011937e-05</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.174878344918116e-05</v>
+        <v>-1.17487834491811e-05</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0001633231207311281</v>
+        <v>-0.0001633231207311284</v>
       </c>
       <c r="V10" t="n">
-        <v>-4.005748417875231e-05</v>
+        <v>-4.005748417875235e-05</v>
       </c>
       <c r="W10" t="n">
-        <v>-1.394231759286861e-05</v>
+        <v>-1.394231759286855e-05</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.0001233219445441118</v>
+        <v>-0.0001233219445441119</v>
       </c>
       <c r="Y10" t="n">
-        <v>-5.709391429979313e-05</v>
+        <v>-5.709391429979301e-05</v>
       </c>
       <c r="Z10" t="n">
         <v>-4.252716091985061e-05</v>
       </c>
       <c r="AA10" t="n">
-        <v>-3.068976937582442e-05</v>
+        <v>-3.068976937582439e-05</v>
       </c>
       <c r="AB10" t="n">
-        <v>-8.068636023751987e-05</v>
+        <v>-8.068636023751989e-05</v>
       </c>
     </row>
     <row r="11">
@@ -5522,85 +5522,85 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-6.426819537429235e-06</v>
+        <v>-6.426819537429209e-06</v>
       </c>
       <c r="C11" t="n">
         <v>2.322837564999013e-05</v>
       </c>
       <c r="D11" t="n">
-        <v>1.484258799697645e-05</v>
+        <v>1.48425879969766e-05</v>
       </c>
       <c r="E11" t="n">
-        <v>7.72409829673095e-06</v>
+        <v>7.724098296730994e-06</v>
       </c>
       <c r="F11" t="n">
-        <v>1.637564104125662e-05</v>
+        <v>1.637564104125677e-05</v>
       </c>
       <c r="G11" t="n">
-        <v>1.705413107253499e-05</v>
+        <v>1.705413107253501e-05</v>
       </c>
       <c r="H11" t="n">
-        <v>2.391936720880148e-05</v>
+        <v>2.391936720880149e-05</v>
       </c>
       <c r="I11" t="n">
-        <v>1.102627687183646e-05</v>
+        <v>1.102627687183644e-05</v>
       </c>
       <c r="J11" t="n">
-        <v>9.890022691227417e-06</v>
+        <v>9.890022691227444e-06</v>
       </c>
       <c r="K11" t="n">
-        <v>1.866447989703571e-06</v>
+        <v>1.866447989703618e-06</v>
       </c>
       <c r="L11" t="n">
-        <v>-3.298073709579267e-05</v>
+        <v>-3.298073709579286e-05</v>
       </c>
       <c r="M11" t="n">
-        <v>3.14457064778621e-06</v>
+        <v>3.144570647786256e-06</v>
       </c>
       <c r="N11" t="n">
-        <v>2.108774203815009e-05</v>
+        <v>2.108774203815014e-05</v>
       </c>
       <c r="O11" t="n">
-        <v>1.972632139009359e-05</v>
+        <v>1.972632139009354e-05</v>
       </c>
       <c r="P11" t="n">
-        <v>2.576466873990898e-06</v>
+        <v>2.576466873990881e-06</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.281855860682656e-05</v>
+        <v>1.281855860682658e-05</v>
       </c>
       <c r="R11" t="n">
-        <v>2.1330776267948e-05</v>
+        <v>2.133077626794807e-05</v>
       </c>
       <c r="S11" t="n">
-        <v>3.206687961107563e-06</v>
+        <v>3.206687961107712e-06</v>
       </c>
       <c r="T11" t="n">
-        <v>1.394021107893841e-05</v>
+        <v>1.394021107893839e-05</v>
       </c>
       <c r="U11" t="n">
-        <v>-2.947980104940601e-05</v>
+        <v>-2.9479801049406e-05</v>
       </c>
       <c r="V11" t="n">
-        <v>8.913818698307662e-06</v>
+        <v>8.913818698307709e-06</v>
       </c>
       <c r="W11" t="n">
-        <v>1.32633819732912e-05</v>
+        <v>1.326338197329115e-05</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.780628927349804e-05</v>
+        <v>-1.780628927349796e-05</v>
       </c>
       <c r="Y11" t="n">
-        <v>9.629900854183918e-07</v>
+        <v>9.62990085418465e-07</v>
       </c>
       <c r="Z11" t="n">
-        <v>5.022939905795526e-06</v>
+        <v>5.022939905795573e-06</v>
       </c>
       <c r="AA11" t="n">
-        <v>8.488435636072775e-06</v>
+        <v>8.488435636072823e-06</v>
       </c>
       <c r="AB11" t="n">
-        <v>-5.657382203353641e-06</v>
+        <v>-5.657382203353533e-06</v>
       </c>
     </row>
   </sheetData>
@@ -6066,7 +6066,7 @@
         <v>8.82082053651527e-06</v>
       </c>
       <c r="N5" t="n">
-        <v>8.194305666918485e-05</v>
+        <v>8.820820536515302e-06</v>
       </c>
       <c r="O5" t="n">
         <v>8.820820536515302e-06</v>
@@ -6154,7 +6154,7 @@
         <v>2.487733903412699e-05</v>
       </c>
       <c r="N6" t="n">
-        <v>8.194305666918485e-05</v>
+        <v>1.294510263563718e-05</v>
       </c>
       <c r="O6" t="n">
         <v>2.486314902805393e-05</v>
@@ -6242,7 +6242,7 @@
         <v>2.538831887241505e-05</v>
       </c>
       <c r="N7" t="n">
-        <v>8.194305666918485e-05</v>
+        <v>2.538831887241505e-05</v>
       </c>
       <c r="O7" t="n">
         <v>2.537961098107083e-05</v>
@@ -6330,7 +6330,7 @@
         <v>0.0001031182276817824</v>
       </c>
       <c r="N8" t="n">
-        <v>8.194305666918485e-05</v>
+        <v>7.378820568292174e-05</v>
       </c>
       <c r="O8" t="n">
         <v>8.184835039715777e-05</v>
@@ -6418,7 +6418,7 @@
         <v>0.0001139362850372975</v>
       </c>
       <c r="N9" t="n">
-        <v>8.194305666918485e-05</v>
+        <v>0.0001139362850372975</v>
       </c>
       <c r="O9" t="n">
         <v>0.0001217047977710434</v>
@@ -6826,7 +6826,7 @@
         <v>1.131355389128328e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>1.13736995613428e-05</v>
+        <v>1.137369956134281e-05</v>
       </c>
       <c r="K2" t="n">
         <v>1.172374737022375e-05</v>
@@ -6981,7 +6981,7 @@
         <v>7.007653850462774e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>7.262681632500274e-05</v>
+        <v>7.262681632500273e-05</v>
       </c>
       <c r="D4" t="n">
         <v>6.790540533013665e-05</v>
@@ -7017,7 +7017,7 @@
         <v>5.900048756693414e-05</v>
       </c>
       <c r="O4" t="n">
-        <v>7.771333661312918e-05</v>
+        <v>7.771333661312917e-05</v>
       </c>
       <c r="P4" t="n">
         <v>4.819038163953485e-05</v>
@@ -7102,7 +7102,7 @@
         <v>7.586742432416335e-06</v>
       </c>
       <c r="N5" t="n">
-        <v>5.900048756693414e-05</v>
+        <v>7.586742432416289e-06</v>
       </c>
       <c r="O5" t="n">
         <v>7.586742432416289e-06</v>
@@ -7190,7 +7190,7 @@
         <v>1.979642557511365e-05</v>
       </c>
       <c r="N6" t="n">
-        <v>5.900048756693414e-05</v>
+        <v>1.020792665638782e-05</v>
       </c>
       <c r="O6" t="n">
         <v>1.980196727244267e-05</v>
@@ -7278,7 +7278,7 @@
         <v>2.128468354970565e-05</v>
       </c>
       <c r="N7" t="n">
-        <v>5.900048756693414e-05</v>
+        <v>2.128468354970565e-05</v>
       </c>
       <c r="O7" t="n">
         <v>2.12765847834035e-05</v>
@@ -7299,7 +7299,7 @@
         <v>2.128468354970565e-05</v>
       </c>
       <c r="U7" t="n">
-        <v>2.130516281477722e-05</v>
+        <v>2.130516281477723e-05</v>
       </c>
       <c r="V7" t="n">
         <v>2.072476972865493e-05</v>
@@ -7366,7 +7366,7 @@
         <v>8.969146987241149e-05</v>
       </c>
       <c r="N8" t="n">
-        <v>5.900048756693414e-05</v>
+        <v>6.421139479370283e-05</v>
       </c>
       <c r="O8" t="n">
         <v>7.121354066545414e-05</v>
@@ -7454,7 +7454,7 @@
         <v>8.946431300209669e-05</v>
       </c>
       <c r="N9" t="n">
-        <v>5.900048756693414e-05</v>
+        <v>8.946431300209669e-05</v>
       </c>
       <c r="O9" t="n">
         <v>9.552207536692732e-05</v>
@@ -7539,7 +7539,7 @@
         <v>8.478935797169819e-06</v>
       </c>
       <c r="M10" t="n">
-        <v>8.120612224527707e-06</v>
+        <v>8.120612224527705e-06</v>
       </c>
       <c r="N10" t="n">
         <v>1.037232126818869e-05</v>
@@ -7554,10 +7554,10 @@
         <v>1.028750150236431e-05</v>
       </c>
       <c r="R10" t="n">
-        <v>9.998080401766309e-06</v>
+        <v>9.998080401766311e-06</v>
       </c>
       <c r="S10" t="n">
-        <v>6.296489066502348e-06</v>
+        <v>6.296489066502349e-06</v>
       </c>
       <c r="T10" t="n">
         <v>1.038331686242366e-05</v>
@@ -7603,7 +7603,7 @@
         <v>1.074739711311491e-05</v>
       </c>
       <c r="E11" t="n">
-        <v>7.207481053968143e-06</v>
+        <v>7.207481053968142e-06</v>
       </c>
       <c r="F11" t="n">
         <v>1.058789612589814e-05</v>
@@ -7660,7 +7660,7 @@
         <v>9.470888592180637e-06</v>
       </c>
       <c r="X11" t="n">
-        <v>3.588960106772307e-06</v>
+        <v>3.588960106772308e-06</v>
       </c>
       <c r="Y11" t="n">
         <v>7.526310423286603e-06</v>
@@ -8050,7 +8050,7 @@
         <v>0.0001618201752147636</v>
       </c>
       <c r="N4" t="n">
-        <v>5.547092294784046e-05</v>
+        <v>5.547092294784045e-05</v>
       </c>
       <c r="O4" t="n">
         <v>7.735930071512082e-05</v>
@@ -8138,7 +8138,7 @@
         <v>7.753887591689924e-06</v>
       </c>
       <c r="N5" t="n">
-        <v>5.547092294784045e-05</v>
+        <v>7.753887591689961e-06</v>
       </c>
       <c r="O5" t="n">
         <v>7.753887591689961e-06</v>
@@ -8226,7 +8226,7 @@
         <v>2.003854903474416e-05</v>
       </c>
       <c r="N6" t="n">
-        <v>5.547092294784046e-05</v>
+        <v>1.03835704987825e-05</v>
       </c>
       <c r="O6" t="n">
         <v>1.037826054165161e-05</v>
@@ -8314,7 +8314,7 @@
         <v>2.137429710914274e-05</v>
       </c>
       <c r="N7" t="n">
-        <v>5.547092294784046e-05</v>
+        <v>2.137429710914274e-05</v>
       </c>
       <c r="O7" t="n">
         <v>2.136619674410174e-05</v>
@@ -8402,7 +8402,7 @@
         <v>8.948686460313014e-05</v>
       </c>
       <c r="N8" t="n">
-        <v>5.547092294784046e-05</v>
+        <v>6.411364702734457e-05</v>
       </c>
       <c r="O8" t="n">
         <v>7.108642752923161e-05</v>
@@ -8490,7 +8490,7 @@
         <v>8.442136726200965e-05</v>
       </c>
       <c r="N9" t="n">
-        <v>5.547092294784046e-05</v>
+        <v>8.442136726200965e-05</v>
       </c>
       <c r="O9" t="n">
         <v>9.01062874783618e-05</v>
@@ -9174,7 +9174,7 @@
         <v>1.24172661496009e-05</v>
       </c>
       <c r="N5" t="n">
-        <v>0.000153882214599664</v>
+        <v>1.241726614960093e-05</v>
       </c>
       <c r="O5" t="n">
         <v>1.241726614960093e-05</v>
@@ -9262,7 +9262,7 @@
         <v>1.944789491362229e-05</v>
       </c>
       <c r="N6" t="n">
-        <v>0.000153882214599664</v>
+        <v>1.97301942777174e-05</v>
       </c>
       <c r="O6" t="n">
         <v>3.686174500739465e-05</v>
@@ -9350,7 +9350,7 @@
         <v>3.359980757610958e-05</v>
       </c>
       <c r="N7" t="n">
-        <v>0.000153882214599664</v>
+        <v>3.359980757610958e-05</v>
       </c>
       <c r="O7" t="n">
         <v>3.35910645786403e-05</v>
@@ -9438,7 +9438,7 @@
         <v>0.0001217140706394431</v>
       </c>
       <c r="N8" t="n">
-        <v>0.000153882214599664</v>
+        <v>8.751923019985796e-05</v>
       </c>
       <c r="O8" t="n">
         <v>9.69162692615863e-05</v>
@@ -9526,7 +9526,7 @@
         <v>0.0001478367466384704</v>
       </c>
       <c r="N9" t="n">
-        <v>0.000153882214599664</v>
+        <v>0.0001478367466384704</v>
       </c>
       <c r="O9" t="n">
         <v>0.0001578637436358306</v>
@@ -10210,7 +10210,7 @@
         <v>8.609101492692919e-06</v>
       </c>
       <c r="N5" t="n">
-        <v>5.516302837961751e-05</v>
+        <v>8.609101492692929e-06</v>
       </c>
       <c r="O5" t="n">
         <v>8.609101492692929e-06</v>
@@ -10298,7 +10298,7 @@
         <v>1.137781835165553e-05</v>
       </c>
       <c r="N6" t="n">
-        <v>5.516302837961751e-05</v>
+        <v>1.147407713377862e-05</v>
       </c>
       <c r="O6" t="n">
         <v>2.405150087230807e-05</v>
@@ -10386,7 +10386,7 @@
         <v>2.41447132056404e-05</v>
       </c>
       <c r="N7" t="n">
-        <v>5.516302837961751e-05</v>
+        <v>2.41447132056404e-05</v>
       </c>
       <c r="O7" t="n">
         <v>2.413660698090972e-05</v>
@@ -10474,7 +10474,7 @@
         <v>9.714960472536993e-05</v>
       </c>
       <c r="N8" t="n">
-        <v>5.516302837961751e-05</v>
+        <v>6.954222201766854e-05</v>
       </c>
       <c r="O8" t="n">
         <v>7.712897049685e-05</v>
@@ -10562,7 +10562,7 @@
         <v>0.0001017635637784478</v>
       </c>
       <c r="N9" t="n">
-        <v>5.516302837961751e-05</v>
+        <v>0.0001017635637784478</v>
       </c>
       <c r="O9" t="n">
         <v>0.0001086760095189331</v>

--- a/Results/Phase 2/Hydrogen/hydrogen eutrophication freshwater results.xlsx
+++ b/Results/Phase 2/Hydrogen/hydrogen eutrophication freshwater results.xlsx
@@ -586,85 +586,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.349211428742349e-05</v>
+        <v>5.349211428742364e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>2.362099281000732e-05</v>
+        <v>2.362099281000733e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>2.508650283921904e-05</v>
+        <v>2.508650283921902e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>2.428619493632367e-05</v>
+        <v>2.428619493632376e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>2.550876065078337e-05</v>
+        <v>2.55087606507834e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>2.727251686205099e-05</v>
+        <v>2.727251686205101e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>2.599569030868984e-05</v>
+        <v>2.599569030868964e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>2.551098368435614e-05</v>
+        <v>2.551098368435616e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>3.167335691619601e-05</v>
+        <v>3.167335691619609e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>2.483638338381783e-05</v>
+        <v>2.483638338381793e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>6.810780761705853e-05</v>
+        <v>6.810780761705867e-05</v>
       </c>
       <c r="M2" t="n">
-        <v>3.935461564764043e-05</v>
+        <v>3.93546156476404e-05</v>
       </c>
       <c r="N2" t="n">
-        <v>2.377513160100949e-05</v>
+        <v>2.377513160100964e-05</v>
       </c>
       <c r="O2" t="n">
-        <v>2.701428741159581e-05</v>
+        <v>2.701428741159585e-05</v>
       </c>
       <c r="P2" t="n">
-        <v>3.357626684942023e-05</v>
+        <v>3.35762668494202e-05</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.833376418608446e-05</v>
+        <v>2.833376418608452e-05</v>
       </c>
       <c r="R2" t="n">
-        <v>2.507335978034045e-05</v>
+        <v>2.50733597803405e-05</v>
       </c>
       <c r="S2" t="n">
-        <v>3.607345068857785e-05</v>
+        <v>3.607345068857787e-05</v>
       </c>
       <c r="T2" t="n">
-        <v>2.692429669204666e-05</v>
+        <v>2.692429669204674e-05</v>
       </c>
       <c r="U2" t="n">
-        <v>5.056530971612104e-05</v>
+        <v>5.056530971612109e-05</v>
       </c>
       <c r="V2" t="n">
-        <v>3.052832680335617e-05</v>
+        <v>3.05283268033561e-05</v>
       </c>
       <c r="W2" t="n">
-        <v>2.854360587600235e-05</v>
+        <v>2.854360587600242e-05</v>
       </c>
       <c r="X2" t="n">
-        <v>3.76141684994483e-05</v>
+        <v>3.761416849944842e-05</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.781281199565366e-05</v>
+        <v>2.781281199565375e-05</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.655610761000232e-05</v>
+        <v>3.65561076100024e-05</v>
       </c>
       <c r="AA2" t="n">
-        <v>3.356792200741937e-05</v>
+        <v>3.356792200741943e-05</v>
       </c>
       <c r="AB2" t="n">
-        <v>4.324270115470952e-05</v>
+        <v>4.324270115470955e-05</v>
       </c>
     </row>
     <row r="3">
@@ -674,85 +674,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.312003600267949e-05</v>
+        <v>2.312003600267966e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>2.312003600267949e-05</v>
+        <v>2.312003600267966e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>2.312003600267949e-05</v>
+        <v>2.312003600267966e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>1.625574864077643e-05</v>
+        <v>1.625574864077647e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>2.312003600267949e-05</v>
+        <v>2.312003600267966e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>2.312003600267949e-05</v>
+        <v>2.312003600267966e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>2.312003600267949e-05</v>
+        <v>2.312003600267966e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>2.312003600267949e-05</v>
+        <v>2.312003600267966e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>2.309291707265329e-05</v>
+        <v>2.309291707265332e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>2.312003600267949e-05</v>
+        <v>2.312003600267966e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>2.312003600267949e-05</v>
+        <v>2.312003600267966e-05</v>
       </c>
       <c r="M3" t="n">
-        <v>2.312003600267949e-05</v>
+        <v>2.312003600267966e-05</v>
       </c>
       <c r="N3" t="n">
-        <v>2.312003600267949e-05</v>
+        <v>2.312003600267966e-05</v>
       </c>
       <c r="O3" t="n">
-        <v>2.312003600267949e-05</v>
+        <v>2.312003600267966e-05</v>
       </c>
       <c r="P3" t="n">
-        <v>2.312003600267949e-05</v>
+        <v>2.312003600267966e-05</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.312003600267949e-05</v>
+        <v>2.312003600267966e-05</v>
       </c>
       <c r="R3" t="n">
-        <v>2.312003600267949e-05</v>
+        <v>2.312003600267966e-05</v>
       </c>
       <c r="S3" t="n">
-        <v>2.312003600267949e-05</v>
+        <v>2.312003600267966e-05</v>
       </c>
       <c r="T3" t="n">
-        <v>2.312003600267949e-05</v>
+        <v>2.312003600267966e-05</v>
       </c>
       <c r="U3" t="n">
-        <v>2.312003600267949e-05</v>
+        <v>2.312003600267966e-05</v>
       </c>
       <c r="V3" t="n">
-        <v>2.402027176565511e-05</v>
+        <v>2.402027176565509e-05</v>
       </c>
       <c r="W3" t="n">
-        <v>2.312003600267949e-05</v>
+        <v>2.312003600267966e-05</v>
       </c>
       <c r="X3" t="n">
-        <v>2.312003600267949e-05</v>
+        <v>2.312003600267966e-05</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.312003600267949e-05</v>
+        <v>2.312003600267966e-05</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.312003600267949e-05</v>
+        <v>2.312003600267966e-05</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.312003600267949e-05</v>
+        <v>2.312003600267966e-05</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.312003600267949e-05</v>
+        <v>2.312003600267966e-05</v>
       </c>
     </row>
     <row r="4">
@@ -762,67 +762,67 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.008256526036868985</v>
+        <v>0.008256526036868996</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0002468931419199012</v>
+        <v>0.000246893141919902</v>
       </c>
       <c r="D4" t="n">
-        <v>0.000693638284740139</v>
+        <v>0.0006936382847401392</v>
       </c>
       <c r="E4" t="n">
-        <v>0.002365047696265178</v>
+        <v>0.002365047696265175</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0008400461968765913</v>
+        <v>0.0008400461968765896</v>
       </c>
       <c r="G4" t="n">
-        <v>0.001242480103494393</v>
+        <v>0.001242480103494391</v>
       </c>
       <c r="H4" t="n">
         <v>0.001008797076095332</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0008314636015752225</v>
+        <v>0.0008314636015752223</v>
       </c>
       <c r="J4" t="n">
-        <v>0.002531061600078394</v>
+        <v>0.002531061600078395</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0006130984442299467</v>
+        <v>0.0006130984442299449</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01308218125675879</v>
+        <v>0.01308218125675877</v>
       </c>
       <c r="M4" t="n">
-        <v>0.005083255567813367</v>
+        <v>0.005083255567813372</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0002879759713835327</v>
+        <v>0.0002879759713835332</v>
       </c>
       <c r="O4" t="n">
-        <v>0.001118915400049231</v>
+        <v>0.001118915400049228</v>
       </c>
       <c r="P4" t="n">
-        <v>0.002960536883601253</v>
+        <v>0.002960536883601252</v>
       </c>
       <c r="Q4" t="n">
         <v>0.00164818815513245</v>
       </c>
       <c r="R4" t="n">
-        <v>0.0007051060146179934</v>
+        <v>0.0007051060146179936</v>
       </c>
       <c r="S4" t="n">
-        <v>0.003685586209283265</v>
+        <v>0.003685586209283268</v>
       </c>
       <c r="T4" t="n">
-        <v>0.001257361518935676</v>
+        <v>0.001257361518935678</v>
       </c>
       <c r="U4" t="n">
         <v>0.007856729229093607</v>
       </c>
       <c r="V4" t="n">
-        <v>0.00186339075456124</v>
+        <v>0.001863390754561234</v>
       </c>
       <c r="W4" t="n">
         <v>0.001670193936038148</v>
@@ -831,16 +831,16 @@
         <v>0.004444601469566455</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.001458324422648717</v>
+        <v>0.00145832442264872</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.003813393114958634</v>
+        <v>0.003813393114958635</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.003152075249482387</v>
+        <v>0.003152075249482382</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.006511841344607638</v>
+        <v>0.006511841344607632</v>
       </c>
     </row>
     <row r="5">
@@ -850,61 +850,61 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9.567570267833009e-05</v>
+        <v>9.567570267832997e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0001487657321766098</v>
+        <v>0.0001487657321766104</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0001487657321766098</v>
+        <v>0.0001487657321766104</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0001204968575266807</v>
+        <v>0.0001204968575266802</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0001039465087980147</v>
+        <v>0.0001039465087980146</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0001597742956424456</v>
+        <v>0.0001597742956424458</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0001487657321766098</v>
+        <v>0.0001487657321766104</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0001487657321766098</v>
+        <v>0.0001487657321766104</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0001486717995693206</v>
+        <v>0.0001486717995693209</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0001487657321766098</v>
+        <v>0.0001487657321766104</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0001487657321766098</v>
+        <v>0.0001487657321766104</v>
       </c>
       <c r="M5" t="n">
-        <v>0.000148765732176611</v>
+        <v>0.0001487657321766118</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0002879759713835327</v>
+        <v>0.0001076120775471631</v>
       </c>
       <c r="O5" t="n">
-        <v>0.000118921459170754</v>
+        <v>0.0001189214591707537</v>
       </c>
       <c r="P5" t="n">
-        <v>0.0001161492564618084</v>
+        <v>0.0001161492564618083</v>
       </c>
       <c r="Q5" t="n">
-        <v>8.524230016120689e-05</v>
+        <v>8.524230016120735e-05</v>
       </c>
       <c r="R5" t="n">
-        <v>0.0001487657321766098</v>
+        <v>0.0001487657321766104</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0001487657321766098</v>
+        <v>0.0001487657321766104</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0001487657321766098</v>
+        <v>0.0001487657321766104</v>
       </c>
       <c r="U5" t="n">
         <v>0.0001228461613071417</v>
@@ -913,22 +913,22 @@
         <v>0.0001336438579892903</v>
       </c>
       <c r="W5" t="n">
-        <v>0.0001487761658890055</v>
+        <v>0.0001487761658890056</v>
       </c>
       <c r="X5" t="n">
-        <v>9.010810685640083e-05</v>
+        <v>9.010810685640069e-05</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.0002015399034542699</v>
+        <v>0.0002015399034542702</v>
       </c>
       <c r="Z5" t="n">
-        <v>9.468952812403246e-05</v>
+        <v>9.468952812403244e-05</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.0001487657321766098</v>
+        <v>0.0001487657321766104</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.0002042227073037574</v>
+        <v>0.0002042227073037576</v>
       </c>
     </row>
     <row r="6">
@@ -938,85 +938,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.000166713696203362</v>
+        <v>0.0001667136962033613</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0002094672271842764</v>
+        <v>0.0002094672271842762</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0002094672271842764</v>
+        <v>0.0002094672271842762</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0001995998950554344</v>
+        <v>0.0001995998950554347</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0001109086554172683</v>
+        <v>0.0001109086554172684</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0002094672381476903</v>
+        <v>0.00020946723814769</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0002094672271842764</v>
+        <v>0.0002094672271842762</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0002094672271842764</v>
+        <v>0.0002094672271842762</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0002093732945769872</v>
+        <v>0.0002093732945769873</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0002094672271842764</v>
+        <v>0.0002094672271842762</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0002094672271842764</v>
+        <v>0.0002094672271842762</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0002094672271842764</v>
+        <v>0.0002094672271842762</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0002879759713835327</v>
+        <v>0.0002094672271842762</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0002236357059671939</v>
+        <v>0.0002236357059671937</v>
       </c>
       <c r="P6" t="n">
-        <v>0.0002267171046278521</v>
+        <v>0.0002267171046278525</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.0002094672381476903</v>
+        <v>0.00020946723814769</v>
       </c>
       <c r="R6" t="n">
-        <v>0.0002094672271842764</v>
+        <v>0.0002094672271842762</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0002094672271842764</v>
+        <v>0.0002094672271842762</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0002094672271842764</v>
+        <v>0.0002094672271842762</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0002094672271842764</v>
+        <v>0.0002094672271842762</v>
       </c>
       <c r="V6" t="n">
-        <v>0.0002582000203455051</v>
+        <v>0.0002582000203455048</v>
       </c>
       <c r="W6" t="n">
-        <v>0.0002094672271842764</v>
+        <v>0.0002094672271842762</v>
       </c>
       <c r="X6" t="n">
-        <v>0.0002094672271842764</v>
+        <v>0.0002094672271842762</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.0002094672271842764</v>
+        <v>0.0002094672271842762</v>
       </c>
       <c r="Z6" t="n">
         <v>0.0001836906541485518</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.0002094672271842764</v>
+        <v>0.0002094672271842762</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.0002094672271842764</v>
+        <v>0.0002094672271842762</v>
       </c>
     </row>
     <row r="7">
@@ -1026,85 +1026,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.0001585858956155242</v>
+        <v>-0.0001585858956155244</v>
       </c>
       <c r="C7" t="n">
-        <v>1.918029540105827e-05</v>
+        <v>1.918029540105814e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>1.060063998582317e-05</v>
+        <v>1.060063998582333e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>-3.170022675877231e-05</v>
+        <v>-3.170022675877214e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>8.200655433607063e-06</v>
+        <v>8.200655433607127e-06</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.586636781531572e-06</v>
+        <v>-2.586636781531364e-06</v>
       </c>
       <c r="H7" t="n">
-        <v>5.395730483977963e-06</v>
+        <v>5.395730483978216e-06</v>
       </c>
       <c r="I7" t="n">
-        <v>8.142410722864154e-06</v>
+        <v>8.142410722864372e-06</v>
       </c>
       <c r="J7" t="n">
-        <v>-2.868961696165788e-05</v>
+        <v>-2.868961696165767e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>1.20499845216051e-05</v>
+        <v>1.204998452160529e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.0002438509137849897</v>
+        <v>-0.0002438509137849889</v>
       </c>
       <c r="M7" t="n">
-        <v>-7.261042084396052e-05</v>
+        <v>-7.261042084396033e-05</v>
       </c>
       <c r="N7" t="n">
-        <v>1.826136688366251e-05</v>
+        <v>1.826136688366258e-05</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.091104173411957e-06</v>
+        <v>-1.091104173411952e-06</v>
       </c>
       <c r="P7" t="n">
-        <v>-4.022823309145708e-05</v>
+        <v>-4.022823309145688e-05</v>
       </c>
       <c r="Q7" t="n">
-        <v>-8.50107071499486e-06</v>
+        <v>-8.50107071499478e-06</v>
       </c>
       <c r="R7" t="n">
-        <v>1.072684586628223e-05</v>
+        <v>1.072684586628221e-05</v>
       </c>
       <c r="S7" t="n">
-        <v>-5.471803079984691e-05</v>
+        <v>-5.471803079984701e-05</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.494795228658189e-07</v>
+        <v>-1.494795228657118e-07</v>
       </c>
       <c r="U7" t="n">
         <v>-0.0001403055280968974</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.574201868920269e-05</v>
+        <v>-1.574201868920262e-05</v>
       </c>
       <c r="W7" t="n">
-        <v>-9.898458918608226e-06</v>
+        <v>-9.898458918608219e-06</v>
       </c>
       <c r="X7" t="n">
-        <v>-6.286325600507128e-05</v>
+        <v>-6.286325600507118e-05</v>
       </c>
       <c r="Y7" t="n">
-        <v>-5.538898575798214e-06</v>
+        <v>-5.538898575798093e-06</v>
       </c>
       <c r="Z7" t="n">
-        <v>-5.774092718317737e-05</v>
+        <v>-5.774092718317741e-05</v>
       </c>
       <c r="AA7" t="n">
-        <v>-3.950086730991535e-05</v>
+        <v>-3.950086730991509e-05</v>
       </c>
       <c r="AB7" t="n">
-        <v>-9.572270833582416e-05</v>
+        <v>-9.572270833582397e-05</v>
       </c>
     </row>
     <row r="8">
@@ -1114,85 +1114,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-2.918466366130511e-05</v>
+        <v>-2.918466366130509e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>2.182839828106131e-05</v>
+        <v>2.182839828106151e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>1.939013775460161e-05</v>
+        <v>1.939013775460181e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>2.466073302903184e-06</v>
+        <v>2.466073302903432e-06</v>
       </c>
       <c r="F8" t="n">
-        <v>1.872039494661059e-05</v>
+        <v>1.87203949466109e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>1.557589882292958e-05</v>
+        <v>1.55758988229296e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>1.793107481367037e-05</v>
+        <v>1.793107481367047e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>1.869611645118045e-05</v>
+        <v>1.869611645118034e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>8.112138909439842e-06</v>
+        <v>8.112138909440096e-06</v>
       </c>
       <c r="K8" t="n">
-        <v>1.979947468176815e-05</v>
+        <v>1.979947468176839e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>-5.336482532226747e-05</v>
+        <v>-5.336482532226748e-05</v>
       </c>
       <c r="M8" t="n">
-        <v>-4.203047292445396e-06</v>
+        <v>-4.203047292445374e-06</v>
       </c>
       <c r="N8" t="n">
-        <v>2.1564421668197e-05</v>
+        <v>2.156442166819726e-05</v>
       </c>
       <c r="O8" t="n">
-        <v>1.599814147514846e-05</v>
+        <v>1.599814147514877e-05</v>
       </c>
       <c r="P8" t="n">
-        <v>4.75260253263276e-06</v>
+        <v>4.752602532632813e-06</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.394605985905464e-05</v>
+        <v>1.394605985905478e-05</v>
       </c>
       <c r="R8" t="n">
-        <v>1.943441877352612e-05</v>
+        <v>1.943441877352638e-05</v>
       </c>
       <c r="S8" t="n">
-        <v>6.568822382275683e-07</v>
+        <v>6.568822382277008e-07</v>
       </c>
       <c r="T8" t="n">
-        <v>1.633659297237755e-05</v>
+        <v>1.633659297237753e-05</v>
       </c>
       <c r="U8" t="n">
-        <v>-2.379384275555767e-05</v>
+        <v>-2.379384275555742e-05</v>
       </c>
       <c r="V8" t="n">
-        <v>1.24363579314947e-05</v>
+        <v>1.243635793149467e-05</v>
       </c>
       <c r="W8" t="n">
-        <v>1.352008546311644e-05</v>
+        <v>1.352008546311646e-05</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.508503376571767e-06</v>
+        <v>-1.508503376571815e-06</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.47729054318408e-05</v>
+        <v>1.477290543184103e-05</v>
       </c>
       <c r="Z8" t="n">
-        <v>-2.358883281625725e-07</v>
+        <v>-2.358883281623014e-07</v>
       </c>
       <c r="AA8" t="n">
-        <v>5.075211439210681e-06</v>
+        <v>5.075211439210799e-06</v>
       </c>
       <c r="AB8" t="n">
-        <v>-1.08311262486643e-05</v>
+        <v>-1.083112624866422e-05</v>
       </c>
     </row>
   </sheetData>
@@ -1358,85 +1358,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.177394696925496e-05</v>
+        <v>1.177394696925493e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>1.174257365191295e-05</v>
+        <v>1.174257365191294e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>1.202080390276684e-05</v>
+        <v>1.202080390276679e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>8.066145861718403e-06</v>
+        <v>8.066145861718344e-06</v>
       </c>
       <c r="F2" t="n">
-        <v>1.213328940736095e-05</v>
+        <v>1.213328940736093e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>1.26535352999397e-05</v>
+        <v>1.265353529993966e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>1.176479990822101e-05</v>
+        <v>1.176479990822095e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>1.214486015237128e-05</v>
+        <v>1.214486015237125e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>1.252957935741486e-05</v>
+        <v>1.25295793574148e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>1.418231943355322e-05</v>
+        <v>1.418231943355318e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>1.329147496924775e-05</v>
+        <v>1.329147496924776e-05</v>
       </c>
       <c r="M2" t="n">
-        <v>1.25983830076018e-05</v>
+        <v>1.259838300760175e-05</v>
       </c>
       <c r="N2" t="n">
-        <v>1.181895027634162e-05</v>
+        <v>1.181895027634158e-05</v>
       </c>
       <c r="O2" t="n">
-        <v>1.19002650629874e-05</v>
+        <v>1.190026506298734e-05</v>
       </c>
       <c r="P2" t="n">
-        <v>1.19431294064847e-05</v>
+        <v>1.194312940648467e-05</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.207440063029702e-05</v>
+        <v>1.207440063029697e-05</v>
       </c>
       <c r="R2" t="n">
-        <v>1.184814652086871e-05</v>
+        <v>1.184814652086865e-05</v>
       </c>
       <c r="S2" t="n">
-        <v>1.33395776915785e-05</v>
+        <v>1.333957769157848e-05</v>
       </c>
       <c r="T2" t="n">
-        <v>1.191346704694754e-05</v>
+        <v>1.191346704694752e-05</v>
       </c>
       <c r="U2" t="n">
-        <v>1.477057539645445e-05</v>
+        <v>1.477057539645439e-05</v>
       </c>
       <c r="V2" t="n">
-        <v>1.388058216339979e-05</v>
+        <v>1.388058216339971e-05</v>
       </c>
       <c r="W2" t="n">
-        <v>1.222737565465445e-05</v>
+        <v>1.222737565465442e-05</v>
       </c>
       <c r="X2" t="n">
-        <v>2.040847796546201e-05</v>
+        <v>2.040847796546199e-05</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.706341851881516e-05</v>
+        <v>1.70634185188151e-05</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.191259252298949e-05</v>
+        <v>1.191259252298947e-05</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.264544176300221e-05</v>
+        <v>1.264544176300217e-05</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.266668816141692e-05</v>
+        <v>1.266668816141688e-05</v>
       </c>
     </row>
     <row r="3">
@@ -1446,85 +1446,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.169827474819234e-05</v>
+        <v>1.169827474819231e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>1.169827474819234e-05</v>
+        <v>1.169827474819231e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>1.169827474819234e-05</v>
+        <v>1.169827474819231e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>7.899444111491704e-06</v>
+        <v>7.899444111491652e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>1.169827474819234e-05</v>
+        <v>1.169827474819231e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>1.169827474819234e-05</v>
+        <v>1.169827474819231e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>1.169827474819234e-05</v>
+        <v>1.169827474819231e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>1.169827474819234e-05</v>
+        <v>1.169827474819231e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>1.16836236873225e-05</v>
+        <v>1.168362368732249e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>1.169827474819234e-05</v>
+        <v>1.169827474819231e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>1.169827474819234e-05</v>
+        <v>1.169827474819231e-05</v>
       </c>
       <c r="M3" t="n">
-        <v>1.169827474819234e-05</v>
+        <v>1.169827474819231e-05</v>
       </c>
       <c r="N3" t="n">
-        <v>1.169827474819234e-05</v>
+        <v>1.169827474819231e-05</v>
       </c>
       <c r="O3" t="n">
-        <v>1.169827474819234e-05</v>
+        <v>1.169827474819231e-05</v>
       </c>
       <c r="P3" t="n">
-        <v>1.169827474819234e-05</v>
+        <v>1.169827474819231e-05</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.169827474819234e-05</v>
+        <v>1.169827474819231e-05</v>
       </c>
       <c r="R3" t="n">
-        <v>1.169827474819234e-05</v>
+        <v>1.169827474819231e-05</v>
       </c>
       <c r="S3" t="n">
-        <v>1.169827474819234e-05</v>
+        <v>1.169827474819231e-05</v>
       </c>
       <c r="T3" t="n">
-        <v>1.169827474819234e-05</v>
+        <v>1.169827474819231e-05</v>
       </c>
       <c r="U3" t="n">
-        <v>1.169827474819234e-05</v>
+        <v>1.169827474819231e-05</v>
       </c>
       <c r="V3" t="n">
-        <v>1.331906963655514e-05</v>
+        <v>1.331906963655503e-05</v>
       </c>
       <c r="W3" t="n">
-        <v>1.169827474819234e-05</v>
+        <v>1.169827474819231e-05</v>
       </c>
       <c r="X3" t="n">
-        <v>1.169827474819234e-05</v>
+        <v>1.169827474819231e-05</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.169827474819234e-05</v>
+        <v>1.169827474819231e-05</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.169827474819234e-05</v>
+        <v>1.169827474819231e-05</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.169827474819234e-05</v>
+        <v>1.169827474819231e-05</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.169827474819234e-05</v>
+        <v>1.169827474819231e-05</v>
       </c>
     </row>
     <row r="4">
@@ -1534,82 +1534,82 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.528014955089714e-05</v>
+        <v>6.528014955089704e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>6.62987072056407e-05</v>
+        <v>6.629870720564056e-05</v>
       </c>
       <c r="D4" t="n">
         <v>0.0001339766453087228</v>
       </c>
       <c r="E4" t="n">
-        <v>6.448246714272999e-05</v>
+        <v>6.448246714272985e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0001617703481066982</v>
+        <v>0.0001617703481066978</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0002669071294672478</v>
+        <v>0.0002669071294672471</v>
       </c>
       <c r="H4" t="n">
-        <v>6.846134632635055e-05</v>
+        <v>6.846134632635035e-05</v>
       </c>
       <c r="I4" t="n">
         <v>0.0001654243121857654</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0002504277853618066</v>
+        <v>0.0002504277853618064</v>
       </c>
       <c r="K4" t="n">
         <v>0.0006271311193934944</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0004181506702919189</v>
+        <v>0.0004181506702919191</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0002817789276301549</v>
+        <v>0.0002817789276301547</v>
       </c>
       <c r="N4" t="n">
-        <v>7.505071325843369e-05</v>
+        <v>7.505071325843374e-05</v>
       </c>
       <c r="O4" t="n">
-        <v>9.625792123837e-05</v>
+        <v>9.62579212383699e-05</v>
       </c>
       <c r="P4" t="n">
         <v>0.000104777243429044</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.0001409834063997851</v>
+        <v>0.0001409834063997849</v>
       </c>
       <c r="R4" t="n">
-        <v>8.754916467735587e-05</v>
+        <v>8.754916467735565e-05</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0004203389960390093</v>
+        <v>0.0004203389960390091</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0001031911551775399</v>
+        <v>0.0001031911551775398</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0007406385488363426</v>
+        <v>0.0007406385488363408</v>
       </c>
       <c r="V4" t="n">
-        <v>0.0001857124539327636</v>
+        <v>0.0001857124539327635</v>
       </c>
       <c r="W4" t="n">
-        <v>0.0001776980090284671</v>
+        <v>0.0001776980090284669</v>
       </c>
       <c r="X4" t="n">
-        <v>0.002175133600702869</v>
+        <v>0.002175133600702873</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.001419308710250767</v>
+        <v>0.001419308710250765</v>
       </c>
       <c r="Z4" t="n">
         <v>9.999304197309091e-05</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.0002851024977966098</v>
+        <v>0.0002851024977966097</v>
       </c>
       <c r="AB4" t="n">
         <v>0.0003120312101592364</v>
@@ -1622,85 +1622,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.906836617883221e-05</v>
+        <v>5.906836617883208e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>9.315395516863717e-05</v>
+        <v>9.315395516863695e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>9.315395516863717e-05</v>
+        <v>9.315395516863695e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>7.500438449349663e-05</v>
+        <v>7.50043844934966e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>6.437850257686424e-05</v>
+        <v>6.43785025768641e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0001002218240926687</v>
+        <v>0.0001002218240926684</v>
       </c>
       <c r="H5" t="n">
-        <v>9.315395516863717e-05</v>
+        <v>9.315395516863695e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>9.315395516863717e-05</v>
+        <v>9.315395516863695e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>9.306646403725562e-05</v>
+        <v>9.306646403725545e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>9.315395516863717e-05</v>
+        <v>9.315395516863695e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>9.315395516863717e-05</v>
+        <v>9.315395516863695e-05</v>
       </c>
       <c r="M5" t="n">
-        <v>9.315395516863271e-05</v>
+        <v>9.315395516863235e-05</v>
       </c>
       <c r="N5" t="n">
-        <v>7.505071325843369e-05</v>
+        <v>6.673192130689869e-05</v>
       </c>
       <c r="O5" t="n">
-        <v>7.39929256310398e-05</v>
+        <v>7.399292563103968e-05</v>
       </c>
       <c r="P5" t="n">
-        <v>7.22130780207056e-05</v>
+        <v>7.221307802070541e-05</v>
       </c>
       <c r="Q5" t="n">
-        <v>5.236976997672965e-05</v>
+        <v>5.236976997672961e-05</v>
       </c>
       <c r="R5" t="n">
-        <v>9.315395516863717e-05</v>
+        <v>9.315395516863695e-05</v>
       </c>
       <c r="S5" t="n">
-        <v>9.315395516863717e-05</v>
+        <v>9.315395516863695e-05</v>
       </c>
       <c r="T5" t="n">
-        <v>9.315395516863717e-05</v>
+        <v>9.315395516863695e-05</v>
       </c>
       <c r="U5" t="n">
-        <v>7.654028911492782e-05</v>
+        <v>7.654028911492769e-05</v>
       </c>
       <c r="V5" t="n">
-        <v>8.329936128112064e-05</v>
+        <v>8.329936128112052e-05</v>
       </c>
       <c r="W5" t="n">
-        <v>9.316065396401453e-05</v>
+        <v>9.316065396401415e-05</v>
       </c>
       <c r="X5" t="n">
-        <v>5.549378193701583e-05</v>
+        <v>5.549378193701579e-05</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.0001270839208545819</v>
+        <v>0.0001270839208545817</v>
       </c>
       <c r="Z5" t="n">
-        <v>5.843520886382515e-05</v>
+        <v>5.843520886382507e-05</v>
       </c>
       <c r="AA5" t="n">
-        <v>9.315395516863717e-05</v>
+        <v>9.315395516863695e-05</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.0001287592030593626</v>
+        <v>0.0001287592030593623</v>
       </c>
     </row>
     <row r="6">
@@ -1710,85 +1710,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7.058557995823057e-05</v>
+        <v>7.058557995823046e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>8.860659697764298e-05</v>
+        <v>8.860659697764279e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>8.860659697764298e-05</v>
+        <v>8.860659697764279e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>8.444742035633695e-05</v>
+        <v>8.444742035633688e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>4.706323332680032e-05</v>
+        <v>4.706323332680022e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>8.860659775820388e-05</v>
+        <v>8.860659775820367e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>8.860659697764298e-05</v>
+        <v>8.860659697764279e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>8.860659697764298e-05</v>
+        <v>8.860659697764279e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>8.851910584626148e-05</v>
+        <v>8.851910584626132e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>8.860659697764298e-05</v>
+        <v>8.860659697764279e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>8.860659697764298e-05</v>
+        <v>8.860659697764279e-05</v>
       </c>
       <c r="M6" t="n">
-        <v>8.860659697764298e-05</v>
+        <v>8.860659697764279e-05</v>
       </c>
       <c r="N6" t="n">
-        <v>7.505071325843369e-05</v>
+        <v>8.860659697764279e-05</v>
       </c>
       <c r="O6" t="n">
-        <v>9.457873946072245e-05</v>
+        <v>9.457873946072236e-05</v>
       </c>
       <c r="P6" t="n">
-        <v>9.587757781622476e-05</v>
+        <v>9.587757781622475e-05</v>
       </c>
       <c r="Q6" t="n">
-        <v>8.860659775820388e-05</v>
+        <v>8.860659775820367e-05</v>
       </c>
       <c r="R6" t="n">
-        <v>8.860659697764298e-05</v>
+        <v>8.860659697764279e-05</v>
       </c>
       <c r="S6" t="n">
-        <v>8.860659697764298e-05</v>
+        <v>8.860659697764279e-05</v>
       </c>
       <c r="T6" t="n">
-        <v>8.860659697764298e-05</v>
+        <v>8.860659697764279e-05</v>
       </c>
       <c r="U6" t="n">
-        <v>8.860659697764298e-05</v>
+        <v>8.860659697764279e-05</v>
       </c>
       <c r="V6" t="n">
-        <v>0.0001088385455043055</v>
+        <v>0.0001088385455043054</v>
       </c>
       <c r="W6" t="n">
-        <v>8.860659697764298e-05</v>
+        <v>8.860659697764279e-05</v>
       </c>
       <c r="X6" t="n">
-        <v>8.860659697764298e-05</v>
+        <v>8.860659697764279e-05</v>
       </c>
       <c r="Y6" t="n">
-        <v>8.860659697764298e-05</v>
+        <v>8.860659697764279e-05</v>
       </c>
       <c r="Z6" t="n">
-        <v>7.774152651625048e-05</v>
+        <v>7.774152651625043e-05</v>
       </c>
       <c r="AA6" t="n">
-        <v>8.860659697764298e-05</v>
+        <v>8.860659697764279e-05</v>
       </c>
       <c r="AB6" t="n">
-        <v>8.860659697764298e-05</v>
+        <v>8.860659697764279e-05</v>
       </c>
     </row>
     <row r="7">
@@ -1798,85 +1798,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.091450753640953e-05</v>
+        <v>1.091450753640949e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>1.111029386876004e-05</v>
+        <v>1.111029386876001e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>9.481279016382918e-06</v>
+        <v>9.481279016382889e-06</v>
       </c>
       <c r="E7" t="n">
-        <v>6.830806917988026e-06</v>
+        <v>6.830806917987975e-06</v>
       </c>
       <c r="F7" t="n">
-        <v>8.836642770992229e-06</v>
+        <v>8.836642770992214e-06</v>
       </c>
       <c r="G7" t="n">
-        <v>5.685055993731197e-06</v>
+        <v>5.685055993731182e-06</v>
       </c>
       <c r="H7" t="n">
-        <v>1.09859783124486e-05</v>
+        <v>1.098597831244857e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>8.760207324507443e-06</v>
+        <v>8.760207324507413e-06</v>
       </c>
       <c r="J7" t="n">
-        <v>6.357293480963602e-06</v>
+        <v>6.357293480963548e-06</v>
       </c>
       <c r="K7" t="n">
-        <v>-3.201018618876881e-06</v>
+        <v>-3.20101861887691e-06</v>
       </c>
       <c r="L7" t="n">
-        <v>1.948317271536095e-06</v>
+        <v>1.948317271536075e-06</v>
       </c>
       <c r="M7" t="n">
-        <v>6.119508286431623e-06</v>
+        <v>6.119508286431601e-06</v>
       </c>
       <c r="N7" t="n">
-        <v>1.065908392925897e-05</v>
+        <v>1.065908392925892e-05</v>
       </c>
       <c r="O7" t="n">
-        <v>1.01612977950504e-05</v>
+        <v>1.016129779505039e-05</v>
       </c>
       <c r="P7" t="n">
-        <v>9.904384611914576e-06</v>
+        <v>9.904384611914547e-06</v>
       </c>
       <c r="Q7" t="n">
-        <v>9.16074956342802e-06</v>
+        <v>9.160749563428001e-06</v>
       </c>
       <c r="R7" t="n">
-        <v>1.049754869992783e-05</v>
+        <v>1.049754869992781e-05</v>
       </c>
       <c r="S7" t="n">
-        <v>1.631610210235299e-06</v>
+        <v>1.631610210235263e-06</v>
       </c>
       <c r="T7" t="n">
-        <v>1.011104532193404e-05</v>
+        <v>1.011104532193399e-05</v>
       </c>
       <c r="U7" t="n">
-        <v>-6.814392178074035e-06</v>
+        <v>-6.814392178074021e-06</v>
       </c>
       <c r="V7" t="n">
-        <v>9.494738621156304e-06</v>
+        <v>9.494738621156202e-06</v>
       </c>
       <c r="W7" t="n">
-        <v>8.2449429841796e-06</v>
+        <v>8.244942984179561e-06</v>
       </c>
       <c r="X7" t="n">
-        <v>-3.969923617369592e-05</v>
+        <v>-3.969923617369594e-05</v>
       </c>
       <c r="Y7" t="n">
-        <v>-2.02455237506424e-05</v>
+        <v>-2.024552375064246e-05</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.009151355376902e-05</v>
+        <v>1.009151355376899e-05</v>
       </c>
       <c r="AA7" t="n">
-        <v>5.782381013733871e-06</v>
+        <v>5.782381013733827e-06</v>
       </c>
       <c r="AB7" t="n">
-        <v>5.699349919837371e-06</v>
+        <v>5.699349919837342e-06</v>
       </c>
     </row>
     <row r="8">
@@ -1886,85 +1886,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.141733039017589e-05</v>
+        <v>1.141733039017585e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>1.147504047798738e-05</v>
+        <v>1.147504047798735e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>1.101206377964736e-05</v>
+        <v>1.101206377964732e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>7.579912533129552e-06</v>
+        <v>7.579912533129503e-06</v>
       </c>
       <c r="F8" t="n">
-        <v>1.08312377382549e-05</v>
+        <v>1.083123773825486e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>9.91750160366874e-06</v>
+        <v>9.917501603668676e-06</v>
       </c>
       <c r="H8" t="n">
-        <v>1.144070276000357e-05</v>
+        <v>1.144070276000352e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>1.080803011152933e-05</v>
+        <v>1.080803011152928e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>1.010608213951428e-05</v>
+        <v>1.010608213951426e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>7.403093470306054e-06</v>
+        <v>7.403093470305994e-06</v>
       </c>
       <c r="L8" t="n">
-        <v>8.855213246098303e-06</v>
+        <v>8.855213246098277e-06</v>
       </c>
       <c r="M8" t="n">
-        <v>1.006002648902682e-05</v>
+        <v>1.006002648902679e-05</v>
       </c>
       <c r="N8" t="n">
-        <v>1.134611514202229e-05</v>
+        <v>1.134611514202224e-05</v>
       </c>
       <c r="O8" t="n">
-        <v>1.120093565125288e-05</v>
+        <v>1.120093565125286e-05</v>
       </c>
       <c r="P8" t="n">
-        <v>1.112690367768961e-05</v>
+        <v>1.112690367768963e-05</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.091981858461628e-05</v>
+        <v>1.091981858461626e-05</v>
       </c>
       <c r="R8" t="n">
-        <v>1.130181234242146e-05</v>
+        <v>1.130181234242143e-05</v>
       </c>
       <c r="S8" t="n">
-        <v>8.759213246251663e-06</v>
+        <v>8.759213246251614e-06</v>
       </c>
       <c r="T8" t="n">
-        <v>1.11912725998e-05</v>
+        <v>1.119127259979993e-05</v>
       </c>
       <c r="U8" t="n">
-        <v>6.347252948634264e-06</v>
+        <v>6.347252948634204e-06</v>
       </c>
       <c r="V8" t="n">
-        <v>1.214049936397349e-05</v>
+        <v>1.214049936397342e-05</v>
       </c>
       <c r="W8" t="n">
-        <v>1.06560986969133e-05</v>
+        <v>1.065609869691326e-05</v>
       </c>
       <c r="X8" t="n">
-        <v>-2.977553298145868e-06</v>
+        <v>-2.977553298145907e-06</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.528888402999642e-06</v>
+        <v>2.528888402999604e-06</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.118151105908277e-05</v>
+        <v>1.118151105908276e-05</v>
       </c>
       <c r="AA8" t="n">
-        <v>9.95369126098886e-06</v>
+        <v>9.953691260988825e-06</v>
       </c>
       <c r="AB8" t="n">
-        <v>9.937158247076328e-06</v>
+        <v>9.937158247076287e-06</v>
       </c>
     </row>
   </sheetData>
@@ -2130,85 +2130,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.644960699087046e-05</v>
+        <v>4.644960699087069e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>2.092921182348515e-05</v>
+        <v>2.092921182348521e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>2.519143515028332e-05</v>
+        <v>2.519143515028335e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>2.157606077680128e-05</v>
+        <v>2.157606077680145e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>2.322779643080074e-05</v>
+        <v>2.322779643080077e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>2.491445703075519e-05</v>
+        <v>2.491445703075521e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>2.120658168322598e-05</v>
+        <v>2.120658168322599e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>2.230445024646639e-05</v>
+        <v>2.230445024646643e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>2.857756663764593e-05</v>
+        <v>2.857756663764597e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>2.29013035162169e-05</v>
+        <v>2.290130351621693e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>6.649107799866049e-05</v>
+        <v>6.649107799866068e-05</v>
       </c>
       <c r="M2" t="n">
-        <v>3.617378108285767e-05</v>
+        <v>3.617378108285769e-05</v>
       </c>
       <c r="N2" t="n">
-        <v>2.21638797035292e-05</v>
+        <v>2.216387970352924e-05</v>
       </c>
       <c r="O2" t="n">
-        <v>2.466688062507061e-05</v>
+        <v>2.466688062507064e-05</v>
       </c>
       <c r="P2" t="n">
-        <v>3.418645639813365e-05</v>
+        <v>3.418645639813371e-05</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.574548349325154e-05</v>
+        <v>2.574548349325161e-05</v>
       </c>
       <c r="R2" t="n">
-        <v>2.130153470647057e-05</v>
+        <v>2.13015347064706e-05</v>
       </c>
       <c r="S2" t="n">
-        <v>3.419426990753657e-05</v>
+        <v>3.419426990753658e-05</v>
       </c>
       <c r="T2" t="n">
-        <v>2.581810167284857e-05</v>
+        <v>2.581810167284862e-05</v>
       </c>
       <c r="U2" t="n">
-        <v>4.764012115544436e-05</v>
+        <v>4.764012115544439e-05</v>
       </c>
       <c r="V2" t="n">
-        <v>2.44873078273634e-05</v>
+        <v>2.448730782736341e-05</v>
       </c>
       <c r="W2" t="n">
-        <v>2.461621081611072e-05</v>
+        <v>2.461621081611079e-05</v>
       </c>
       <c r="X2" t="n">
-        <v>3.668655127950565e-05</v>
+        <v>3.668655127950576e-05</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.484219048474524e-05</v>
+        <v>2.484219048474527e-05</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.186883513996712e-05</v>
+        <v>3.186883513996729e-05</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.869040450949516e-05</v>
+        <v>2.86904045094952e-05</v>
       </c>
       <c r="AB2" t="n">
-        <v>4.036638049673769e-05</v>
+        <v>4.036638049673777e-05</v>
       </c>
     </row>
     <row r="3">
@@ -2218,85 +2218,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.079061083015639e-05</v>
+        <v>2.079061083015643e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>2.079061083015639e-05</v>
+        <v>2.079061083015643e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>2.079061083015639e-05</v>
+        <v>2.079061083015643e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>1.485718967512785e-05</v>
+        <v>1.485718967512788e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>2.079061083015639e-05</v>
+        <v>2.079061083015643e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>2.079061083015639e-05</v>
+        <v>2.079061083015643e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>2.079061083015639e-05</v>
+        <v>2.079061083015643e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>2.079061083015639e-05</v>
+        <v>2.079061083015643e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>2.067386656051645e-05</v>
+        <v>2.067386656051653e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>2.079061083015639e-05</v>
+        <v>2.079061083015643e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>2.079061083015639e-05</v>
+        <v>2.079061083015643e-05</v>
       </c>
       <c r="M3" t="n">
-        <v>2.079061083015639e-05</v>
+        <v>2.079061083015643e-05</v>
       </c>
       <c r="N3" t="n">
-        <v>2.079061083015639e-05</v>
+        <v>2.079061083015643e-05</v>
       </c>
       <c r="O3" t="n">
-        <v>2.079061083015639e-05</v>
+        <v>2.079061083015643e-05</v>
       </c>
       <c r="P3" t="n">
-        <v>2.079061083015639e-05</v>
+        <v>2.079061083015643e-05</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.079061083015639e-05</v>
+        <v>2.079061083015643e-05</v>
       </c>
       <c r="R3" t="n">
-        <v>2.079061083015639e-05</v>
+        <v>2.079061083015643e-05</v>
       </c>
       <c r="S3" t="n">
-        <v>2.079061083015639e-05</v>
+        <v>2.079061083015643e-05</v>
       </c>
       <c r="T3" t="n">
-        <v>2.079061083015639e-05</v>
+        <v>2.079061083015643e-05</v>
       </c>
       <c r="U3" t="n">
-        <v>2.079061083015639e-05</v>
+        <v>2.079061083015643e-05</v>
       </c>
       <c r="V3" t="n">
-        <v>2.064819633375511e-05</v>
+        <v>2.064819633375515e-05</v>
       </c>
       <c r="W3" t="n">
-        <v>2.079061083015639e-05</v>
+        <v>2.079061083015643e-05</v>
       </c>
       <c r="X3" t="n">
-        <v>2.079061083015639e-05</v>
+        <v>2.079061083015643e-05</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.079061083015639e-05</v>
+        <v>2.079061083015643e-05</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.079061083015639e-05</v>
+        <v>2.079061083015643e-05</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.079061083015639e-05</v>
+        <v>2.079061083015643e-05</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.079061083015639e-05</v>
+        <v>2.079061083015643e-05</v>
       </c>
     </row>
     <row r="4">
@@ -2306,85 +2306,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.006488131476177946</v>
+        <v>0.006488131476177963</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0001256279597694635</v>
+        <v>0.0001256279597694637</v>
       </c>
       <c r="D4" t="n">
-        <v>0.00133390545982115</v>
+        <v>0.001333905459821148</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001848314336771747</v>
+        <v>0.001848314336771764</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0007772727748324374</v>
+        <v>0.0007772727748324394</v>
       </c>
       <c r="G4" t="n">
-        <v>0.001138231507794174</v>
+        <v>0.001138231507794172</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0002084873374273209</v>
+        <v>0.0002084873374273208</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0005172759711750451</v>
+        <v>0.0005172759711750456</v>
       </c>
       <c r="J4" t="n">
-        <v>0.002181754908361414</v>
+        <v>0.00218175490836141</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0006476500358868872</v>
+        <v>0.0006476500358868882</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0124260603372188</v>
+        <v>0.0124260603372189</v>
       </c>
       <c r="M4" t="n">
-        <v>0.004478973466340058</v>
+        <v>0.004478973466340047</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0004600167935857026</v>
+        <v>0.0004600167935857046</v>
       </c>
       <c r="O4" t="n">
-        <v>0.001026163482222651</v>
+        <v>0.00102616348222265</v>
       </c>
       <c r="P4" t="n">
-        <v>0.003508131524467768</v>
+        <v>0.003508131524467769</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.00145421580413615</v>
+        <v>0.001454215804136157</v>
       </c>
       <c r="R4" t="n">
-        <v>0.0002311981336367942</v>
+        <v>0.0002311981336367941</v>
       </c>
       <c r="S4" t="n">
         <v>0.003522111162999276</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0015101964235309</v>
+        <v>0.001510196423530904</v>
       </c>
       <c r="U4" t="n">
-        <v>0.00716872997185278</v>
+        <v>0.007168729971852779</v>
       </c>
       <c r="V4" t="n">
-        <v>0.00102394040783516</v>
+        <v>0.001023940407835159</v>
       </c>
       <c r="W4" t="n">
-        <v>0.001120025483105178</v>
+        <v>0.00112002548310518</v>
       </c>
       <c r="X4" t="n">
-        <v>0.004520657877127758</v>
+        <v>0.004520657877127773</v>
       </c>
       <c r="Y4" t="n">
         <v>0.001171274605912158</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.002926343817822136</v>
+        <v>0.002926343817822141</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.002224869398517875</v>
+        <v>0.002224869398517886</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.005926713677764568</v>
+        <v>0.005926713677764585</v>
       </c>
     </row>
     <row r="5">
@@ -2394,85 +2394,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8.488541232095419e-05</v>
+        <v>8.488541232095408e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>0.000132773121810211</v>
+        <v>0.0001327731218102111</v>
       </c>
       <c r="D5" t="n">
-        <v>0.000132773121810211</v>
+        <v>0.0001327731218102111</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0001072743291063918</v>
+        <v>0.0001072743291063919</v>
       </c>
       <c r="F5" t="n">
-        <v>9.234575778391828e-05</v>
+        <v>9.234575778391817e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0001427029503322244</v>
+        <v>0.0001427029503322243</v>
       </c>
       <c r="H5" t="n">
-        <v>0.000132773121810211</v>
+        <v>0.0001327731218102111</v>
       </c>
       <c r="I5" t="n">
-        <v>0.000132773121810211</v>
+        <v>0.0001327731218102111</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0001326611610343155</v>
+        <v>0.0001326611610343153</v>
       </c>
       <c r="K5" t="n">
-        <v>0.000132773121810211</v>
+        <v>0.0001327731218102111</v>
       </c>
       <c r="L5" t="n">
-        <v>0.000132773121810211</v>
+        <v>0.0001327731218102111</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0001327731218102103</v>
+        <v>0.0001327731218102102</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0004600167935857026</v>
+        <v>9.565213551674057e-05</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0001058533048661585</v>
+        <v>0.0001058533048661584</v>
       </c>
       <c r="P5" t="n">
-        <v>0.0001033527517638611</v>
+        <v>0.0001033527517638613</v>
       </c>
       <c r="Q5" t="n">
-        <v>7.54743844229137e-05</v>
+        <v>7.547438442291362e-05</v>
       </c>
       <c r="R5" t="n">
-        <v>0.000132773121810211</v>
+        <v>0.0001327731218102111</v>
       </c>
       <c r="S5" t="n">
-        <v>0.000132773121810211</v>
+        <v>0.0001327731218102111</v>
       </c>
       <c r="T5" t="n">
-        <v>0.000132773121810211</v>
+        <v>0.0001327731218102111</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0001093770290544266</v>
+        <v>0.0001093770290544265</v>
       </c>
       <c r="V5" t="n">
-        <v>0.000118940509397132</v>
+        <v>0.0001189405093971319</v>
       </c>
       <c r="W5" t="n">
-        <v>0.0001327825331169447</v>
+        <v>0.0001327825331169445</v>
       </c>
       <c r="X5" t="n">
-        <v>7.986338815171229e-05</v>
+        <v>7.98633881517121e-05</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.0001803478782899404</v>
+        <v>0.0001803478782899403</v>
       </c>
       <c r="Z5" t="n">
-        <v>8.399587353172583e-05</v>
+        <v>8.399587353172589e-05</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.000132773121810211</v>
+        <v>0.0001327731218102111</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.0001827958386764121</v>
+        <v>0.0001827958386764123</v>
       </c>
     </row>
     <row r="6">
@@ -2482,85 +2482,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0001316390049254728</v>
+        <v>0.0001316390049254726</v>
       </c>
       <c r="C6" t="n">
-        <v>0.00016541223831856</v>
+        <v>0.0001654122383185598</v>
       </c>
       <c r="D6" t="n">
-        <v>0.00016541223831856</v>
+        <v>0.0001654122383185598</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0001576175183493644</v>
+        <v>0.0001576175183493645</v>
       </c>
       <c r="F6" t="n">
-        <v>8.755571005444933e-05</v>
+        <v>8.755571005444917e-05</v>
       </c>
       <c r="G6" t="n">
         <v>0.0001654122442200421</v>
       </c>
       <c r="H6" t="n">
-        <v>0.00016541223831856</v>
+        <v>0.0001654122383185598</v>
       </c>
       <c r="I6" t="n">
-        <v>0.00016541223831856</v>
+        <v>0.0001654122383185598</v>
       </c>
       <c r="J6" t="n">
-        <v>0.000165300277542664</v>
+        <v>0.0001653002775426639</v>
       </c>
       <c r="K6" t="n">
-        <v>0.00016541223831856</v>
+        <v>0.0001654122383185598</v>
       </c>
       <c r="L6" t="n">
-        <v>0.00016541223831856</v>
+        <v>0.0001654122383185598</v>
       </c>
       <c r="M6" t="n">
-        <v>0.00016541223831856</v>
+        <v>0.0001654122383185598</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0004600167935857026</v>
+        <v>0.0001654122383185598</v>
       </c>
       <c r="O6" t="n">
         <v>0.00017660465150011</v>
       </c>
       <c r="P6" t="n">
-        <v>0.0001790388080540477</v>
+        <v>0.0001790388080540475</v>
       </c>
       <c r="Q6" t="n">
         <v>0.0001654122442200421</v>
       </c>
       <c r="R6" t="n">
-        <v>0.00016541223831856</v>
+        <v>0.0001654122383185598</v>
       </c>
       <c r="S6" t="n">
-        <v>0.00016541223831856</v>
+        <v>0.0001654122383185598</v>
       </c>
       <c r="T6" t="n">
-        <v>0.00016541223831856</v>
+        <v>0.0001654122383185598</v>
       </c>
       <c r="U6" t="n">
-        <v>0.00016541223831856</v>
+        <v>0.0001654122383185598</v>
       </c>
       <c r="V6" t="n">
         <v>0.000203666668519429</v>
       </c>
       <c r="W6" t="n">
-        <v>0.00016541223831856</v>
+        <v>0.0001654122383185598</v>
       </c>
       <c r="X6" t="n">
-        <v>0.00016541223831856</v>
+        <v>0.0001654122383185598</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.00016541223831856</v>
+        <v>0.0001654122383185598</v>
       </c>
       <c r="Z6" t="n">
         <v>0.0001450499841590385</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.00016541223831856</v>
+        <v>0.0001654122383185598</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.00016541223831856</v>
+        <v>0.0001654122383185598</v>
       </c>
     </row>
     <row r="7">
@@ -2570,85 +2570,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.0001327493562663869</v>
+        <v>-0.0001327493562663876</v>
       </c>
       <c r="C7" t="n">
-        <v>1.910104481447237e-05</v>
+        <v>1.910104481447246e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>-5.863053994889344e-06</v>
+        <v>-5.863053994889263e-06</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.53052841352095e-05</v>
+        <v>-2.530528413520993e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>5.713197701399931e-06</v>
+        <v>5.713197701399956e-06</v>
       </c>
       <c r="G7" t="n">
-        <v>-4.618853076385646e-06</v>
+        <v>-4.618853076385546e-06</v>
       </c>
       <c r="H7" t="n">
-        <v>1.75010295173184e-05</v>
+        <v>1.750102951731846e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>1.106587922525283e-05</v>
+        <v>1.106587922525291e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>-2.692919582197943e-05</v>
+        <v>-2.69291958219794e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>7.532629329050273e-06</v>
+        <v>7.532629329050322e-06</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.0002502674589578799</v>
+        <v>-0.0002502674589578813</v>
       </c>
       <c r="M7" t="n">
-        <v>-6.984703443893697e-05</v>
+        <v>-6.984703443893698e-05</v>
       </c>
       <c r="N7" t="n">
-        <v>1.183301001751878e-05</v>
+        <v>1.183301001751886e-05</v>
       </c>
       <c r="O7" t="n">
-        <v>-3.186276193034382e-06</v>
+        <v>-3.186276193034293e-06</v>
       </c>
       <c r="P7" t="n">
-        <v>-5.995325741836182e-05</v>
+        <v>-5.995325741836175e-05</v>
       </c>
       <c r="Q7" t="n">
-        <v>-9.184986440779126e-06</v>
+        <v>-9.184986440779091e-06</v>
       </c>
       <c r="R7" t="n">
-        <v>1.693759446185313e-05</v>
+        <v>1.69375944618532e-05</v>
       </c>
       <c r="S7" t="n">
-        <v>-5.959113981995884e-05</v>
+        <v>-5.959113981995904e-05</v>
       </c>
       <c r="T7" t="n">
-        <v>-9.514487546439726e-06</v>
+        <v>-9.514487546439799e-06</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0001389830318627032</v>
+        <v>-0.0001389830318627034</v>
       </c>
       <c r="V7" t="n">
-        <v>-3.064066587082906e-06</v>
+        <v>-3.064066587082889e-06</v>
       </c>
       <c r="W7" t="n">
-        <v>-2.670695700026596e-06</v>
+        <v>-2.670695700026554e-06</v>
       </c>
       <c r="X7" t="n">
-        <v>-7.328653787033058e-05</v>
+        <v>-7.328653787033065e-05</v>
       </c>
       <c r="Y7" t="n">
-        <v>-3.964304446436695e-06</v>
+        <v>-3.964304446436595e-06</v>
       </c>
       <c r="Z7" t="n">
-        <v>-4.593176798656583e-05</v>
+        <v>-4.593176798656594e-05</v>
       </c>
       <c r="AA7" t="n">
-        <v>-2.667783004641211e-05</v>
+        <v>-2.66778300464121e-05</v>
       </c>
       <c r="AB7" t="n">
-        <v>-9.472437977229535e-05</v>
+        <v>-9.472437977229534e-05</v>
       </c>
     </row>
     <row r="8">
@@ -2658,82 +2658,82 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-2.341156734089959e-05</v>
+        <v>-2.341156734089956e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>2.016045390202154e-05</v>
+        <v>2.01604539020216e-05</v>
       </c>
       <c r="D8" t="n">
         <v>1.306393271469757e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>3.302007202887937e-06</v>
+        <v>3.302007202887919e-06</v>
       </c>
       <c r="F8" t="n">
-        <v>1.636752540835183e-05</v>
+        <v>1.636752540835185e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>1.335306997812167e-05</v>
+        <v>1.335306997812171e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>1.970981170261108e-05</v>
+        <v>1.970981170261113e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>1.787966637535445e-05</v>
+        <v>1.787966637535449e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>6.918021551651599e-06</v>
+        <v>6.918021551651659e-06</v>
       </c>
       <c r="K8" t="n">
-        <v>1.686887968253348e-05</v>
+        <v>1.686887968253355e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>-5.68412075657114e-05</v>
+        <v>-5.684120756571142e-05</v>
       </c>
       <c r="M8" t="n">
-        <v>-5.066636359616982e-06</v>
+        <v>-5.066636359616921e-06</v>
       </c>
       <c r="N8" t="n">
-        <v>1.808814278759906e-05</v>
+        <v>1.808814278759914e-05</v>
       </c>
       <c r="O8" t="n">
-        <v>1.375732061971356e-05</v>
+        <v>1.375732061971362e-05</v>
       </c>
       <c r="P8" t="n">
-        <v>-2.552260970382644e-06</v>
+        <v>-2.552260970382595e-06</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.210649120841536e-05</v>
+        <v>1.21064912084154e-05</v>
       </c>
       <c r="R8" t="n">
-        <v>1.954839998005799e-05</v>
+        <v>1.954839998005797e-05</v>
       </c>
       <c r="S8" t="n">
-        <v>-2.379682799706095e-06</v>
+        <v>-2.379682799706032e-06</v>
       </c>
       <c r="T8" t="n">
-        <v>1.202918533487907e-05</v>
+        <v>1.202918533487908e-05</v>
       </c>
       <c r="U8" t="n">
-        <v>-2.505739543819508e-05</v>
+        <v>-2.50573954381951e-05</v>
       </c>
       <c r="V8" t="n">
-        <v>1.369815263188384e-05</v>
+        <v>1.369815263188383e-05</v>
       </c>
       <c r="W8" t="n">
-        <v>1.39412415781298e-05</v>
+        <v>1.394124157812979e-05</v>
       </c>
       <c r="X8" t="n">
-        <v>-6.118851185300068e-06</v>
+        <v>-6.118851185300107e-06</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.357862514466123e-05</v>
+        <v>1.357862514466125e-05</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.509940146753495e-06</v>
+        <v>1.509940146753615e-06</v>
       </c>
       <c r="AA8" t="n">
-        <v>7.092112637711028e-06</v>
+        <v>7.092112637711101e-06</v>
       </c>
       <c r="AB8" t="n">
         <v>-1.219330835181062e-05</v>
@@ -2902,85 +2902,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.304085209688187e-05</v>
+        <v>4.304085209688197e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>2.22829995872018e-05</v>
+        <v>2.228299958720181e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>2.82572735327661e-05</v>
+        <v>2.825727353276624e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>1.983655618113783e-05</v>
+        <v>1.983655618113785e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>2.607610672314511e-05</v>
+        <v>2.607610672314514e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>2.629282221528309e-05</v>
+        <v>2.629282221528311e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>2.213363874315186e-05</v>
+        <v>2.213363874315192e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>2.911404757029915e-05</v>
+        <v>2.911404757029918e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>3.042926224875863e-05</v>
+        <v>3.042926224875862e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>3.346515578102987e-05</v>
+        <v>3.346515578102993e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>6.317524543684335e-05</v>
+        <v>6.317524543684338e-05</v>
       </c>
       <c r="M2" t="n">
-        <v>3.62407934052048e-05</v>
+        <v>3.624079340520479e-05</v>
       </c>
       <c r="N2" t="n">
         <v>2.414442198060821e-05</v>
       </c>
       <c r="O2" t="n">
-        <v>2.581226023207627e-05</v>
+        <v>2.581226023207631e-05</v>
       </c>
       <c r="P2" t="n">
-        <v>3.569429611599906e-05</v>
+        <v>3.569429611599913e-05</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.719864462450883e-05</v>
+        <v>2.719864462450887e-05</v>
       </c>
       <c r="R2" t="n">
-        <v>2.253431722433454e-05</v>
+        <v>2.253431722433458e-05</v>
       </c>
       <c r="S2" t="n">
-        <v>3.516080352642412e-05</v>
+        <v>3.516080352642418e-05</v>
       </c>
       <c r="T2" t="n">
-        <v>2.800439469012966e-05</v>
+        <v>2.800439469012971e-05</v>
       </c>
       <c r="U2" t="n">
         <v>5.017637817570028e-05</v>
       </c>
       <c r="V2" t="n">
-        <v>2.95549246800743e-05</v>
+        <v>2.955492468007437e-05</v>
       </c>
       <c r="W2" t="n">
-        <v>2.740918019728006e-05</v>
+        <v>2.740918019728013e-05</v>
       </c>
       <c r="X2" t="n">
-        <v>4.426435290162725e-05</v>
+        <v>4.42643529016273e-05</v>
       </c>
       <c r="Y2" t="n">
-        <v>3.05190724781107e-05</v>
+        <v>3.051907247811074e-05</v>
       </c>
       <c r="Z2" t="n">
         <v>3.354399997835784e-05</v>
       </c>
       <c r="AA2" t="n">
-        <v>3.073436086220622e-05</v>
+        <v>3.073436086220625e-05</v>
       </c>
       <c r="AB2" t="n">
-        <v>4.089685596351146e-05</v>
+        <v>4.089685596351153e-05</v>
       </c>
     </row>
     <row r="3">
@@ -2990,85 +2990,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.214867747089093e-05</v>
+        <v>2.214867747089096e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>2.214867747089093e-05</v>
+        <v>2.214867747089096e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>2.214867747089093e-05</v>
+        <v>2.214867747089096e-05</v>
       </c>
       <c r="E3" t="n">
         <v>1.451631147773938e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>2.214867747089093e-05</v>
+        <v>2.214867747089096e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>2.214867747089093e-05</v>
+        <v>2.214867747089096e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>2.214867747089093e-05</v>
+        <v>2.214867747089096e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>2.214867747089093e-05</v>
+        <v>2.214867747089096e-05</v>
       </c>
       <c r="J3" t="n">
         <v>2.212632994259738e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>2.214867747089093e-05</v>
+        <v>2.214867747089096e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>2.214867747089093e-05</v>
+        <v>2.214867747089096e-05</v>
       </c>
       <c r="M3" t="n">
-        <v>2.214867747089093e-05</v>
+        <v>2.214867747089096e-05</v>
       </c>
       <c r="N3" t="n">
-        <v>2.214867747089093e-05</v>
+        <v>2.214867747089096e-05</v>
       </c>
       <c r="O3" t="n">
-        <v>2.214867747089093e-05</v>
+        <v>2.214867747089096e-05</v>
       </c>
       <c r="P3" t="n">
-        <v>2.214867747089093e-05</v>
+        <v>2.214867747089096e-05</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.214867747089093e-05</v>
+        <v>2.214867747089096e-05</v>
       </c>
       <c r="R3" t="n">
-        <v>2.214867747089093e-05</v>
+        <v>2.214867747089096e-05</v>
       </c>
       <c r="S3" t="n">
-        <v>2.214867747089093e-05</v>
+        <v>2.214867747089096e-05</v>
       </c>
       <c r="T3" t="n">
-        <v>2.214867747089093e-05</v>
+        <v>2.214867747089096e-05</v>
       </c>
       <c r="U3" t="n">
-        <v>2.214867747089093e-05</v>
+        <v>2.214867747089096e-05</v>
       </c>
       <c r="V3" t="n">
-        <v>2.335885397383139e-05</v>
+        <v>2.335885397383142e-05</v>
       </c>
       <c r="W3" t="n">
-        <v>2.214867747089093e-05</v>
+        <v>2.214867747089096e-05</v>
       </c>
       <c r="X3" t="n">
-        <v>2.214867747089093e-05</v>
+        <v>2.214867747089096e-05</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.214867747089093e-05</v>
+        <v>2.214867747089096e-05</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.214867747089093e-05</v>
+        <v>2.214867747089096e-05</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.214867747089093e-05</v>
+        <v>2.214867747089096e-05</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.214867747089093e-05</v>
+        <v>2.214867747089096e-05</v>
       </c>
     </row>
     <row r="4">
@@ -3078,85 +3078,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.005032187723763291</v>
+        <v>0.005032187723763301</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0001257493891103882</v>
+        <v>0.0001257493891103884</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001685915596546741</v>
+        <v>0.001685915596546742</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001373802677753827</v>
+        <v>0.001373802677753823</v>
       </c>
       <c r="F4" t="n">
         <v>0.001107928151022545</v>
       </c>
       <c r="G4" t="n">
-        <v>0.001056063407223933</v>
+        <v>0.001056063407223937</v>
       </c>
       <c r="H4" t="n">
-        <v>7.99560015050352e-05</v>
+        <v>7.995600150503549e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>0.001941473954973271</v>
+        <v>0.001941473954973269</v>
       </c>
       <c r="J4" t="n">
-        <v>0.002117748337846608</v>
+        <v>0.002117748337846609</v>
       </c>
       <c r="K4" t="n">
         <v>0.002723915510476491</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01035012442252216</v>
+        <v>0.01035012442252215</v>
       </c>
       <c r="M4" t="n">
-        <v>0.003842060811202319</v>
+        <v>0.003842060811202322</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0005951910464915281</v>
+        <v>0.000595191046491529</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0009055159558275604</v>
+        <v>0.0009055159558275617</v>
       </c>
       <c r="P4" t="n">
-        <v>0.003267922216739398</v>
+        <v>0.003267922216739405</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.001356945666302847</v>
+        <v>0.001356945666302846</v>
       </c>
       <c r="R4" t="n">
-        <v>0.0001867117060880096</v>
+        <v>0.0001867117060880102</v>
       </c>
       <c r="S4" t="n">
-        <v>0.00316452494103846</v>
+        <v>0.003164524941038461</v>
       </c>
       <c r="T4" t="n">
-        <v>0.001635146630230122</v>
+        <v>0.001635146630230127</v>
       </c>
       <c r="U4" t="n">
-        <v>0.006886322884947144</v>
+        <v>0.006886322884947142</v>
       </c>
       <c r="V4" t="n">
-        <v>0.001477058288435627</v>
+        <v>0.001477058288435635</v>
       </c>
       <c r="W4" t="n">
-        <v>0.001413162317643664</v>
+        <v>0.001413162317643663</v>
       </c>
       <c r="X4" t="n">
-        <v>0.005806172860094725</v>
+        <v>0.005806172860094721</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.002182937216894569</v>
+        <v>0.002182937216894574</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.002634526652626525</v>
+        <v>0.002634526652626524</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.002257893528739796</v>
+        <v>0.002257893528739797</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.005317901869601425</v>
+        <v>0.005317901869601428</v>
       </c>
     </row>
     <row r="5">
@@ -3166,85 +3166,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8.311981998516385e-05</v>
+        <v>8.311981998516404e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0001284129444879366</v>
+        <v>0.0001284129444879368</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0001284129444879366</v>
+        <v>0.0001284129444879368</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0001042956917543491</v>
+        <v>0.0001042956917543492</v>
       </c>
       <c r="F5" t="n">
-        <v>9.017595943049158e-05</v>
+        <v>9.017595943049159e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0001378047689106892</v>
+        <v>0.0001378047689106897</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0001284129444879366</v>
+        <v>0.0001284129444879368</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0001284129444879366</v>
+        <v>0.0001284129444879368</v>
       </c>
       <c r="J5" t="n">
         <v>0.0001283208942356756</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0001284129444879366</v>
+        <v>0.0001284129444879368</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0001284129444879367</v>
+        <v>0.0001284129444879368</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0001284129444879333</v>
+        <v>0.0001284129444879335</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0005951910464915281</v>
+        <v>9.330319562300739e-05</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0001029516594626674</v>
+        <v>0.0001029516594626677</v>
       </c>
       <c r="P5" t="n">
-        <v>0.0001005865878361825</v>
+        <v>0.0001005865878361826</v>
       </c>
       <c r="Q5" t="n">
-        <v>7.421868725600209e-05</v>
+        <v>7.421868725600237e-05</v>
       </c>
       <c r="R5" t="n">
-        <v>0.0001284129444879366</v>
+        <v>0.0001284129444879368</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0001284129444879366</v>
+        <v>0.0001284129444879368</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0001284129444879366</v>
+        <v>0.0001284129444879368</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0001063190318733529</v>
+        <v>0.000106319031873353</v>
       </c>
       <c r="V5" t="n">
-        <v>0.000115456188196201</v>
+        <v>0.0001154561881962012</v>
       </c>
       <c r="W5" t="n">
-        <v>0.0001284218458822294</v>
+        <v>0.0001284218458822295</v>
       </c>
       <c r="X5" t="n">
         <v>7.836989211396394e-05</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.0001734692038608603</v>
+        <v>0.0001734692038608608</v>
       </c>
       <c r="Z5" t="n">
-        <v>8.227847694425061e-05</v>
+        <v>8.227847694425086e-05</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.0001284129444879366</v>
+        <v>0.0001284129444879368</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.0001757254003781787</v>
+        <v>0.000175725400378179</v>
       </c>
     </row>
     <row r="6">
@@ -3254,85 +3254,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0001217200952227188</v>
+        <v>0.0001217200952227189</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0001521091819631254</v>
+        <v>0.0001521091819631256</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0001521091819631254</v>
+        <v>0.0001521091819631256</v>
       </c>
       <c r="E6" t="n">
         <v>0.0001450955115434043</v>
       </c>
       <c r="F6" t="n">
-        <v>8.205403144209747e-05</v>
+        <v>8.205403144209759e-05</v>
       </c>
       <c r="G6" t="n">
         <v>0.0001521091908621428</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0001521091819631254</v>
+        <v>0.0001521091819631256</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0001521091819631254</v>
+        <v>0.0001521091819631256</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0001520171317108645</v>
+        <v>0.0001520171317108646</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0001521091819631254</v>
+        <v>0.0001521091819631256</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0001521091819631254</v>
+        <v>0.0001521091819631257</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0001521091819631254</v>
+        <v>0.0001521091819631256</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0005951910464915281</v>
+        <v>0.0001521091819631256</v>
       </c>
       <c r="O6" t="n">
         <v>0.0001621800973660457</v>
       </c>
       <c r="P6" t="n">
-        <v>0.0001643703467428868</v>
+        <v>0.0001643703467428869</v>
       </c>
       <c r="Q6" t="n">
         <v>0.0001521091908621428</v>
       </c>
       <c r="R6" t="n">
-        <v>0.0001521091819631254</v>
+        <v>0.0001521091819631256</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0001521091819631254</v>
+        <v>0.0001521091819631256</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0001521091819631254</v>
+        <v>0.0001521091819631256</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0001521091819631254</v>
+        <v>0.0001521091819631256</v>
       </c>
       <c r="V6" t="n">
-        <v>0.0001865856301661526</v>
+        <v>0.0001865856301661529</v>
       </c>
       <c r="W6" t="n">
-        <v>0.0001521091819631254</v>
+        <v>0.0001521091819631256</v>
       </c>
       <c r="X6" t="n">
-        <v>0.0001521091819631254</v>
+        <v>0.0001521091819631257</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.0001521091819631254</v>
+        <v>0.0001521091819631256</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.0001337872684953962</v>
+        <v>0.0001337872684953964</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.0001521091819631254</v>
+        <v>0.0001521091819631256</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.0001521091819631254</v>
+        <v>0.0001521091819631256</v>
       </c>
     </row>
     <row r="7">
@@ -3342,85 +3342,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.0001030815422521873</v>
+        <v>-0.0001030815422521872</v>
       </c>
       <c r="C7" t="n">
-        <v>2.043600400102549e-05</v>
+        <v>2.043600400102556e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.455645827235952e-05</v>
+        <v>-1.455645827235947e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.727124498237737e-05</v>
+        <v>-1.727124498237733e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.663197367975559e-06</v>
+        <v>-1.663197367975488e-06</v>
       </c>
       <c r="G7" t="n">
-        <v>-3.430351796662315e-06</v>
+        <v>-3.430351796662294e-06</v>
       </c>
       <c r="H7" t="n">
-        <v>2.131890508410932e-05</v>
+        <v>2.131890508410928e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.949684553571105e-05</v>
+        <v>-1.949684553571104e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>-2.784196921839653e-05</v>
+        <v>-2.784196921839652e-05</v>
       </c>
       <c r="K7" t="n">
         <v>-4.51571456259594e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.0002213266447396585</v>
+        <v>-0.0002213266447396583</v>
       </c>
       <c r="M7" t="n">
-        <v>-6.100323596796695e-05</v>
+        <v>-6.100323596796697e-05</v>
       </c>
       <c r="N7" t="n">
-        <v>9.481131611122746e-06</v>
+        <v>9.481131611122792e-06</v>
       </c>
       <c r="O7" t="n">
-        <v>-6.104734145223201e-07</v>
+        <v>-6.104734145223417e-07</v>
       </c>
       <c r="P7" t="n">
-        <v>-5.953697676683315e-05</v>
+        <v>-5.953697676683314e-05</v>
       </c>
       <c r="Q7" t="n">
-        <v>-8.433630794623091e-06</v>
+        <v>-8.433630794623104e-06</v>
       </c>
       <c r="R7" t="n">
-        <v>1.897867148854844e-05</v>
+        <v>1.897867148854853e-05</v>
       </c>
       <c r="S7" t="n">
-        <v>-5.595971563289481e-05</v>
+        <v>-5.595971563289476e-05</v>
       </c>
       <c r="T7" t="n">
         <v>-1.305281624986054e-05</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0001446458316930942</v>
+        <v>-0.0001446458316930941</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.449987307113625e-05</v>
+        <v>-1.449987307113635e-05</v>
       </c>
       <c r="W7" t="n">
-        <v>-9.829900138411825e-06</v>
+        <v>-9.829900138411752e-06</v>
       </c>
       <c r="X7" t="n">
         <v>-0.0001084440081463479</v>
       </c>
       <c r="Y7" t="n">
-        <v>-2.81030492970519e-05</v>
+        <v>-2.810304929705183e-05</v>
       </c>
       <c r="Z7" t="n">
-        <v>-4.650692961930918e-05</v>
+        <v>-4.650692961930913e-05</v>
       </c>
       <c r="AA7" t="n">
-        <v>-2.941304875784268e-05</v>
+        <v>-2.941304875784264e-05</v>
       </c>
       <c r="AB7" t="n">
-        <v>-8.856791298111223e-05</v>
+        <v>-8.856791298111216e-05</v>
       </c>
     </row>
     <row r="8">
@@ -3430,85 +3430,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-1.393929696214968e-05</v>
+        <v>-1.393929696214953e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>2.150372770044645e-05</v>
+        <v>2.150372770044651e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>1.155631979726008e-05</v>
+        <v>1.155631979726013e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>5.373116690852836e-06</v>
+        <v>5.373116690852878e-06</v>
       </c>
       <c r="F8" t="n">
-        <v>1.524162778751827e-05</v>
+        <v>1.524162778751832e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>1.465428238301668e-05</v>
+        <v>1.465428238301673e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>2.175608966283856e-05</v>
+        <v>2.175608966283853e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>1.016520188588803e-05</v>
+        <v>1.016520188588807e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>7.693526890985217e-06</v>
+        <v>7.693526890985305e-06</v>
       </c>
       <c r="K8" t="n">
-        <v>2.840791781031389e-06</v>
+        <v>2.84079178103142e-06</v>
       </c>
       <c r="L8" t="n">
-        <v>-4.760680207877063e-05</v>
+        <v>-4.760680207877055e-05</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.59359219890079e-06</v>
+        <v>-1.593592198900764e-06</v>
       </c>
       <c r="N8" t="n">
-        <v>1.838064824534019e-05</v>
+        <v>1.838064824534026e-05</v>
       </c>
       <c r="O8" t="n">
-        <v>1.545677405010274e-05</v>
+        <v>1.545677405010278e-05</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.472936878899789e-06</v>
+        <v>-1.472936878899778e-06</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.328359690366614e-05</v>
+        <v>1.328359690366621e-05</v>
       </c>
       <c r="R8" t="n">
-        <v>2.109195440015906e-05</v>
+        <v>2.109195440015911e-05</v>
       </c>
       <c r="S8" t="n">
-        <v>-3.787642524780171e-07</v>
+        <v>-3.787642524779642e-07</v>
       </c>
       <c r="T8" t="n">
-        <v>1.198760286668333e-05</v>
+        <v>1.19876028666834e-05</v>
       </c>
       <c r="U8" t="n">
-        <v>-2.571565503647511e-05</v>
+        <v>-2.571565503647507e-05</v>
       </c>
       <c r="V8" t="n">
-        <v>1.232908322600952e-05</v>
+        <v>1.23290832260095e-05</v>
       </c>
       <c r="W8" t="n">
-        <v>1.285882547536721e-05</v>
+        <v>1.285882547536726e-05</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.515573522841226e-05</v>
+        <v>-1.515573522841217e-05</v>
       </c>
       <c r="Y8" t="n">
-        <v>7.654376655945362e-06</v>
+        <v>7.654376655945452e-06</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.305479959878849e-06</v>
+        <v>2.30547995987887e-06</v>
       </c>
       <c r="AA8" t="n">
-        <v>7.273611110660544e-06</v>
+        <v>7.273611110660587e-06</v>
       </c>
       <c r="AB8" t="n">
-        <v>-9.47954552498886e-06</v>
+        <v>-9.479545524988709e-06</v>
       </c>
     </row>
   </sheetData>
@@ -3674,85 +3674,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.21514326867382e-05</v>
+        <v>4.215143268673832e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>2.479107852098324e-05</v>
+        <v>2.479107852098309e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>2.982809755095244e-05</v>
+        <v>2.982809755095229e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>1.831549728570249e-05</v>
+        <v>1.831549728570243e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>2.894453225290423e-05</v>
+        <v>2.894453225290402e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>2.839859097145959e-05</v>
+        <v>2.839859097145935e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>2.437918814856148e-05</v>
+        <v>2.437918814856142e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>3.214371553255959e-05</v>
+        <v>3.21437155325596e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>3.303930236155756e-05</v>
+        <v>3.303930236155746e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>3.759026989846474e-05</v>
+        <v>3.759026989846475e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>5.804516689337221e-05</v>
+        <v>5.804516689337226e-05</v>
       </c>
       <c r="M2" t="n">
-        <v>3.693044957356873e-05</v>
+        <v>3.693044957356875e-05</v>
       </c>
       <c r="N2" t="n">
-        <v>2.606504722512881e-05</v>
+        <v>2.606504722512861e-05</v>
       </c>
       <c r="O2" t="n">
-        <v>2.682481886517201e-05</v>
+        <v>2.682481886517159e-05</v>
       </c>
       <c r="P2" t="n">
-        <v>3.683711449470155e-05</v>
+        <v>3.683711449470131e-05</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.101568239606939e-05</v>
+        <v>3.101568239606937e-05</v>
       </c>
       <c r="R2" t="n">
-        <v>2.59427543856961e-05</v>
+        <v>2.594275438569582e-05</v>
       </c>
       <c r="S2" t="n">
-        <v>3.656811864648315e-05</v>
+        <v>3.656811864648282e-05</v>
       </c>
       <c r="T2" t="n">
-        <v>3.03762816502329e-05</v>
+        <v>3.037628165023272e-05</v>
       </c>
       <c r="U2" t="n">
-        <v>5.592307602392684e-05</v>
+        <v>5.592307602392658e-05</v>
       </c>
       <c r="V2" t="n">
-        <v>4.029570332275701e-05</v>
+        <v>4.029570332275707e-05</v>
       </c>
       <c r="W2" t="n">
-        <v>3.069751757034201e-05</v>
+        <v>3.069751757034186e-05</v>
       </c>
       <c r="X2" t="n">
-        <v>4.939592515855758e-05</v>
+        <v>4.939592515855727e-05</v>
       </c>
       <c r="Y2" t="n">
-        <v>3.803123970009922e-05</v>
+        <v>3.803123970009905e-05</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.546327031111371e-05</v>
+        <v>3.546327031111368e-05</v>
       </c>
       <c r="AA2" t="n">
-        <v>3.354271516533074e-05</v>
+        <v>3.354271516533049e-05</v>
       </c>
       <c r="AB2" t="n">
-        <v>4.2145505497657e-05</v>
+        <v>4.214550549765693e-05</v>
       </c>
     </row>
     <row r="3">
@@ -3762,85 +3762,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.437419557101808e-05</v>
+        <v>2.437419557101793e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>2.437419557101808e-05</v>
+        <v>2.437419557101793e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>2.437419557101808e-05</v>
+        <v>2.437419557101793e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>1.440960169901339e-05</v>
+        <v>1.440960169901315e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>2.437419557101808e-05</v>
+        <v>2.437419557101793e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>2.437419557101808e-05</v>
+        <v>2.437419557101793e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>2.437419557101808e-05</v>
+        <v>2.437419557101793e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>2.437419557101808e-05</v>
+        <v>2.437419557101793e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>2.458853939301649e-05</v>
+        <v>2.45885393930164e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>2.437419557101808e-05</v>
+        <v>2.437419557101793e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>2.437419557101808e-05</v>
+        <v>2.437419557101793e-05</v>
       </c>
       <c r="M3" t="n">
-        <v>2.437419557101808e-05</v>
+        <v>2.437419557101793e-05</v>
       </c>
       <c r="N3" t="n">
-        <v>2.437419557101808e-05</v>
+        <v>2.437419557101793e-05</v>
       </c>
       <c r="O3" t="n">
-        <v>2.437419557101808e-05</v>
+        <v>2.437419557101793e-05</v>
       </c>
       <c r="P3" t="n">
-        <v>2.437419557101808e-05</v>
+        <v>2.437419557101793e-05</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.437419557101808e-05</v>
+        <v>2.437419557101793e-05</v>
       </c>
       <c r="R3" t="n">
-        <v>2.437419557101808e-05</v>
+        <v>2.437419557101793e-05</v>
       </c>
       <c r="S3" t="n">
-        <v>2.437419557101808e-05</v>
+        <v>2.437419557101793e-05</v>
       </c>
       <c r="T3" t="n">
-        <v>2.437419557101808e-05</v>
+        <v>2.437419557101793e-05</v>
       </c>
       <c r="U3" t="n">
-        <v>2.437419557101808e-05</v>
+        <v>2.437419557101793e-05</v>
       </c>
       <c r="V3" t="n">
-        <v>2.891320775068847e-05</v>
+        <v>2.891320775068848e-05</v>
       </c>
       <c r="W3" t="n">
-        <v>2.437419557101808e-05</v>
+        <v>2.437419557101793e-05</v>
       </c>
       <c r="X3" t="n">
-        <v>2.437419557101808e-05</v>
+        <v>2.437419557101793e-05</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.437419557101808e-05</v>
+        <v>2.437419557101793e-05</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.437419557101808e-05</v>
+        <v>2.437419557101793e-05</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.437419557101808e-05</v>
+        <v>2.437419557101793e-05</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.437419557101808e-05</v>
+        <v>2.437419557101793e-05</v>
       </c>
     </row>
     <row r="4">
@@ -3850,85 +3850,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.004158812910395502</v>
+        <v>0.0041588129103955</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0002031433672749261</v>
+        <v>0.0002031433672749258</v>
       </c>
       <c r="D4" t="n">
-        <v>0.00146529802329541</v>
+        <v>0.001465298023295415</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0009626009856066105</v>
+        <v>0.0009626009856066095</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001272854405811689</v>
+        <v>0.001272854405811691</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0010070884980271</v>
+        <v>0.001007088498027096</v>
       </c>
       <c r="H4" t="n">
-        <v>9.279728732822741e-05</v>
+        <v>9.279728732822709e-05</v>
       </c>
       <c r="I4" t="n">
         <v>0.002126369287277976</v>
       </c>
       <c r="J4" t="n">
-        <v>0.002101800641476611</v>
+        <v>0.002101800641476612</v>
       </c>
       <c r="K4" t="n">
-        <v>0.003177465219967905</v>
+        <v>0.003177465219967912</v>
       </c>
       <c r="L4" t="n">
-        <v>0.00816650696393797</v>
+        <v>0.008166506963937977</v>
       </c>
       <c r="M4" t="n">
-        <v>0.003296891449572733</v>
+        <v>0.003296891449572736</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0005253442406829228</v>
+        <v>0.0005253442406829218</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0006429839915791473</v>
+        <v>0.0006429839915791464</v>
       </c>
       <c r="P4" t="n">
-        <v>0.002915835721525775</v>
+        <v>0.002915835721525773</v>
       </c>
       <c r="Q4" t="n">
         <v>0.001722699889765712</v>
       </c>
       <c r="R4" t="n">
-        <v>0.0005157250645330903</v>
+        <v>0.0005157250645330901</v>
       </c>
       <c r="S4" t="n">
-        <v>0.00293716049175165</v>
+        <v>0.002937160491751651</v>
       </c>
       <c r="T4" t="n">
-        <v>0.001683798825184265</v>
+        <v>0.001683798825184266</v>
       </c>
       <c r="U4" t="n">
-        <v>0.007458976671122058</v>
+        <v>0.007458976671122057</v>
       </c>
       <c r="V4" t="n">
         <v>0.002625050427372946</v>
       </c>
       <c r="W4" t="n">
-        <v>0.001693208402809575</v>
+        <v>0.001693208402809577</v>
       </c>
       <c r="X4" t="n">
-        <v>0.006355129122323118</v>
+        <v>0.006355129122323111</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.003588821264127759</v>
+        <v>0.003588821264127756</v>
       </c>
       <c r="Z4" t="n">
         <v>0.002433500807901014</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.002427111898712937</v>
+        <v>0.002427111898712941</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.004978720696248784</v>
+        <v>0.004978720696248791</v>
       </c>
     </row>
     <row r="5">
@@ -3938,85 +3938,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8.963862976742314e-05</v>
+        <v>8.963862976742287e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0001359926344103981</v>
+        <v>0.0001359926344103978</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0001359926344103981</v>
+        <v>0.0001359926344103978</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0001113104942965039</v>
+        <v>0.0001113104942965036</v>
       </c>
       <c r="F5" t="n">
-        <v>9.686004193960601e-05</v>
+        <v>9.686004193960574e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0001456044392410583</v>
+        <v>0.000145604439241058</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0001359926344103981</v>
+        <v>0.0001359926344103978</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0001359926344103981</v>
+        <v>0.0001359926344103978</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0001359495557907844</v>
+        <v>0.000135949555790784</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0001359926344103981</v>
+        <v>0.0001359926344103978</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0001359926344103982</v>
+        <v>0.0001359926344103978</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0001359926344103886</v>
+        <v>0.0001359926344103882</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0005253442406829228</v>
+        <v>0.0001000605259549513</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0001099349813495695</v>
+        <v>0.000109934981349569</v>
       </c>
       <c r="P5" t="n">
-        <v>0.0001075145137323429</v>
+        <v>0.0001075145137323426</v>
       </c>
       <c r="Q5" t="n">
-        <v>8.052900987779269e-05</v>
+        <v>8.052900987779203e-05</v>
       </c>
       <c r="R5" t="n">
-        <v>0.0001359926344103981</v>
+        <v>0.0001359926344103978</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0001359926344103981</v>
+        <v>0.0001359926344103978</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0001359926344103981</v>
+        <v>0.0001359926344103978</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0001134708770522479</v>
+        <v>0.0001134708770522475</v>
       </c>
       <c r="V5" t="n">
-        <v>0.0001231581266502506</v>
+        <v>0.0001231581266502507</v>
       </c>
       <c r="W5" t="n">
-        <v>0.0001360017442962058</v>
+        <v>0.0001360017442962055</v>
       </c>
       <c r="X5" t="n">
-        <v>8.477744650749427e-05</v>
+        <v>8.477744650749415e-05</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.0001822575924908475</v>
+        <v>0.0001822575924908477</v>
       </c>
       <c r="Z5" t="n">
-        <v>8.877758033340204e-05</v>
+        <v>8.877758033340197e-05</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.0001359926344103981</v>
+        <v>0.0001359926344103978</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.0001844132683147285</v>
+        <v>0.0001844132683147286</v>
       </c>
     </row>
     <row r="6">
@@ -4026,7 +4026,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0001264603994702238</v>
+        <v>0.0001264603994702235</v>
       </c>
       <c r="C6" t="n">
         <v>0.0001568193871121604</v>
@@ -4035,13 +4035,13 @@
         <v>0.0001568193871121604</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0001498126605328816</v>
+        <v>0.0001498126605328811</v>
       </c>
       <c r="F6" t="n">
-        <v>8.683362816376355e-05</v>
+        <v>8.683362816376338e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0001568193922297192</v>
+        <v>0.0001568193922297196</v>
       </c>
       <c r="H6" t="n">
         <v>0.0001568193871121604</v>
@@ -4050,28 +4050,28 @@
         <v>0.0001568193871121604</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0001567763084925471</v>
+        <v>0.0001567763084925469</v>
       </c>
       <c r="K6" t="n">
         <v>0.0001568193871121604</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0001568193871121605</v>
+        <v>0.0001568193871121604</v>
       </c>
       <c r="M6" t="n">
         <v>0.0001568193871121604</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0005253442406829228</v>
+        <v>0.0001568193871121604</v>
       </c>
       <c r="O6" t="n">
-        <v>0.000166880322678631</v>
+        <v>0.0001668803226786304</v>
       </c>
       <c r="P6" t="n">
-        <v>0.000169068402434672</v>
+        <v>0.0001690684024346714</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.0001568193922297192</v>
+        <v>0.0001568193922297196</v>
       </c>
       <c r="R6" t="n">
         <v>0.0001568193871121604</v>
@@ -4086,19 +4086,19 @@
         <v>0.0001568193871121604</v>
       </c>
       <c r="V6" t="n">
-        <v>0.0001915740991507639</v>
+        <v>0.0001915740991507642</v>
       </c>
       <c r="W6" t="n">
         <v>0.0001568193871121604</v>
       </c>
       <c r="X6" t="n">
-        <v>0.0001568193871121605</v>
+        <v>0.0001568193871121604</v>
       </c>
       <c r="Y6" t="n">
         <v>0.0001568193871121604</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.0001385156192227175</v>
+        <v>0.0001385156192227172</v>
       </c>
       <c r="AA6" t="n">
         <v>0.0001568193871121604</v>
@@ -4114,85 +4114,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-8.239044615522815e-05</v>
+        <v>-8.239044615522834e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>2.093970782172154e-05</v>
+        <v>2.093970782172139e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>-8.560759586127537e-06</v>
+        <v>-8.560759586127657e-06</v>
       </c>
       <c r="E7" t="n">
-        <v>-8.868035240643842e-06</v>
+        <v>-8.868035240644069e-06</v>
       </c>
       <c r="F7" t="n">
-        <v>-3.249547681731032e-06</v>
+        <v>-3.249547681731118e-06</v>
       </c>
       <c r="G7" t="n">
-        <v>-5.585086995540448e-07</v>
+        <v>-5.585086995540605e-07</v>
       </c>
       <c r="H7" t="n">
-        <v>2.336360717715916e-05</v>
+        <v>2.336360717715914e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>-2.203743246335632e-05</v>
+        <v>-2.203743246335657e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>-2.628864200121004e-05</v>
+        <v>-2.628864200121016e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>-5.413914882805533e-05</v>
+        <v>-5.413914882805544e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.0001756813350883594</v>
+        <v>-0.0001756813350883596</v>
       </c>
       <c r="M7" t="n">
-        <v>-4.987996331209965e-05</v>
+        <v>-4.987996331209986e-05</v>
       </c>
       <c r="N7" t="n">
-        <v>1.343513990887224e-05</v>
+        <v>1.343513990887185e-05</v>
       </c>
       <c r="O7" t="n">
-        <v>8.773211488178997e-06</v>
+        <v>8.7732114881789e-06</v>
       </c>
       <c r="P7" t="n">
-        <v>-5.092340368502451e-05</v>
+        <v>-5.09234036850246e-05</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.561920297369389e-05</v>
+        <v>-1.561920297369387e-05</v>
       </c>
       <c r="R7" t="n">
-        <v>1.4238050920971e-05</v>
+        <v>1.423805092097087e-05</v>
       </c>
       <c r="S7" t="n">
-        <v>-4.894711657011957e-05</v>
+        <v>-4.894711657011941e-05</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.174878344918123e-05</v>
+        <v>-1.174878344918112e-05</v>
       </c>
       <c r="U7" t="n">
         <v>-0.0001633231207311281</v>
       </c>
       <c r="V7" t="n">
-        <v>-4.005748417875242e-05</v>
+        <v>-4.005748417875239e-05</v>
       </c>
       <c r="W7" t="n">
-        <v>-1.394231759286856e-05</v>
+        <v>-1.394231759286863e-05</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.0001233219445441116</v>
+        <v>-0.0001233219445441118</v>
       </c>
       <c r="Y7" t="n">
-        <v>-5.70939142997933e-05</v>
+        <v>-5.709391429979315e-05</v>
       </c>
       <c r="Z7" t="n">
-        <v>-4.252716091985053e-05</v>
+        <v>-4.252716091985066e-05</v>
       </c>
       <c r="AA7" t="n">
-        <v>-3.068976937582442e-05</v>
+        <v>-3.068976937582443e-05</v>
       </c>
       <c r="AB7" t="n">
-        <v>-8.068636023751968e-05</v>
+        <v>-8.068636023751979e-05</v>
       </c>
     </row>
     <row r="8">
@@ -4202,85 +4202,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-6.42681953742895e-06</v>
+        <v>-6.426819537429226e-06</v>
       </c>
       <c r="C8" t="n">
-        <v>2.322837564999015e-05</v>
+        <v>2.322837564999012e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>1.484258799697662e-05</v>
+        <v>1.484258799697652e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>7.724098296730921e-06</v>
+        <v>7.724098296730973e-06</v>
       </c>
       <c r="F8" t="n">
-        <v>1.637564104125685e-05</v>
+        <v>1.63756410412567e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>1.705413107253521e-05</v>
+        <v>1.705413107253505e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>2.391936720880163e-05</v>
+        <v>2.391936720880149e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>1.102627687183664e-05</v>
+        <v>1.10262768718364e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>9.890022691227541e-06</v>
+        <v>9.890022691227436e-06</v>
       </c>
       <c r="K8" t="n">
-        <v>1.866447989703673e-06</v>
+        <v>1.866447989703555e-06</v>
       </c>
       <c r="L8" t="n">
-        <v>-3.298073709579273e-05</v>
+        <v>-3.29807370957929e-05</v>
       </c>
       <c r="M8" t="n">
-        <v>3.144570647786464e-06</v>
+        <v>3.144570647786306e-06</v>
       </c>
       <c r="N8" t="n">
-        <v>2.108774203814993e-05</v>
+        <v>2.108774203815014e-05</v>
       </c>
       <c r="O8" t="n">
-        <v>1.972632139009365e-05</v>
+        <v>1.972632139009354e-05</v>
       </c>
       <c r="P8" t="n">
-        <v>2.576466873990975e-06</v>
+        <v>2.576466873990837e-06</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.281855860682639e-05</v>
+        <v>1.281855860682648e-05</v>
       </c>
       <c r="R8" t="n">
-        <v>2.133077626794813e-05</v>
+        <v>2.1330776267948e-05</v>
       </c>
       <c r="S8" t="n">
-        <v>3.20668796110767e-06</v>
+        <v>3.206687961107585e-06</v>
       </c>
       <c r="T8" t="n">
-        <v>1.394021107893864e-05</v>
+        <v>1.394021107893835e-05</v>
       </c>
       <c r="U8" t="n">
-        <v>-2.947980104940572e-05</v>
+        <v>-2.947980104940603e-05</v>
       </c>
       <c r="V8" t="n">
-        <v>8.913818698307702e-06</v>
+        <v>8.913818698307753e-06</v>
       </c>
       <c r="W8" t="n">
-        <v>1.326338197329129e-05</v>
+        <v>1.326338197329113e-05</v>
       </c>
       <c r="X8" t="n">
         <v>-1.7806289273498e-05</v>
       </c>
       <c r="Y8" t="n">
-        <v>9.629900854184985e-07</v>
+        <v>9.629900854183842e-07</v>
       </c>
       <c r="Z8" t="n">
-        <v>5.022939905795555e-06</v>
+        <v>5.022939905795499e-06</v>
       </c>
       <c r="AA8" t="n">
-        <v>8.488435636072804e-06</v>
+        <v>8.488435636072779e-06</v>
       </c>
       <c r="AB8" t="n">
-        <v>-5.65738220335337e-06</v>
+        <v>-5.657382203353549e-06</v>
       </c>
     </row>
   </sheetData>
@@ -4446,19 +4446,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.51539035389727e-05</v>
+        <v>1.515390353897271e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>1.28150148356902e-05</v>
+        <v>1.281501483569021e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>1.314393623483555e-05</v>
+        <v>1.314393623483557e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>9.261115912406448e-06</v>
+        <v>9.261115912406469e-06</v>
       </c>
       <c r="F2" t="n">
-        <v>1.298921042876513e-05</v>
+        <v>1.298921042876515e-05</v>
       </c>
       <c r="G2" t="n">
         <v>1.435267375596581e-05</v>
@@ -4467,16 +4467,16 @@
         <v>1.3095599950147e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>1.322352234354836e-05</v>
+        <v>1.322352234354838e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>1.475429721555306e-05</v>
+        <v>1.475429721555308e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>1.403046468080569e-05</v>
+        <v>1.403046468080568e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>2.264745050181607e-05</v>
+        <v>2.26474505018161e-05</v>
       </c>
       <c r="M2" t="n">
         <v>1.763560183594264e-05</v>
@@ -4491,40 +4491,40 @@
         <v>1.541005640468742e-05</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.339778890122745e-05</v>
+        <v>1.339778890122746e-05</v>
       </c>
       <c r="R2" t="n">
-        <v>1.287679625528539e-05</v>
+        <v>1.28767962552854e-05</v>
       </c>
       <c r="S2" t="n">
         <v>1.436647328137949e-05</v>
       </c>
       <c r="T2" t="n">
-        <v>1.323820201151268e-05</v>
+        <v>1.323820201151269e-05</v>
       </c>
       <c r="U2" t="n">
-        <v>2.414119372926147e-05</v>
+        <v>2.41411937292615e-05</v>
       </c>
       <c r="V2" t="n">
-        <v>1.474128247447308e-05</v>
+        <v>1.474128247447306e-05</v>
       </c>
       <c r="W2" t="n">
-        <v>1.546393944607872e-05</v>
+        <v>1.546393944607874e-05</v>
       </c>
       <c r="X2" t="n">
-        <v>1.52148065527904e-05</v>
+        <v>1.521480655279042e-05</v>
       </c>
       <c r="Y2" t="n">
         <v>1.332534564680117e-05</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.47847585611633e-05</v>
+        <v>1.478475856116331e-05</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.655619827072438e-05</v>
+        <v>1.655619827072439e-05</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.912927840242005e-05</v>
+        <v>1.912927840242006e-05</v>
       </c>
     </row>
     <row r="3">
@@ -4543,7 +4543,7 @@
         <v>1.28241241745048e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>8.551929260935667e-06</v>
+        <v>8.551929260935692e-06</v>
       </c>
       <c r="F3" t="n">
         <v>1.28241241745048e-05</v>
@@ -4558,7 +4558,7 @@
         <v>1.28241241745048e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>1.278151131475053e-05</v>
+        <v>1.278151131475052e-05</v>
       </c>
       <c r="K3" t="n">
         <v>1.28241241745048e-05</v>
@@ -4594,7 +4594,7 @@
         <v>1.28241241745048e-05</v>
       </c>
       <c r="V3" t="n">
-        <v>1.398435885755706e-05</v>
+        <v>1.398435885755704e-05</v>
       </c>
       <c r="W3" t="n">
         <v>1.28241241745048e-05</v>
@@ -4622,85 +4622,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0006298824806138692</v>
+        <v>0.0006298824806138685</v>
       </c>
       <c r="C4" t="n">
-        <v>5.639833537673236e-05</v>
+        <v>5.639833537673228e-05</v>
       </c>
       <c r="D4" t="n">
         <v>0.0001441290715460245</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0002093317585245958</v>
+        <v>0.0002093317585245957</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0001039803861943011</v>
+        <v>0.0001039803861943009</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0004216254157052689</v>
+        <v>0.0004216254157052687</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0001356850342840274</v>
+        <v>0.0001356850342840279</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0001678106836958256</v>
+        <v>0.0001678106836958254</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0005495147940492497</v>
+        <v>0.0005495147940492502</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0003739320997059525</v>
+        <v>0.0003739320997059523</v>
       </c>
       <c r="L4" t="n">
         <v>0.002385118615112228</v>
       </c>
       <c r="M4" t="n">
-        <v>0.001300792937832964</v>
+        <v>0.001300792937832963</v>
       </c>
       <c r="N4" t="n">
-        <v>8.194305666918485e-05</v>
+        <v>8.194305666918428e-05</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0001401444758478411</v>
+        <v>0.0001401444758478422</v>
       </c>
       <c r="P4" t="n">
-        <v>0.0007058604344981483</v>
+        <v>0.0007058604344981459</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.0002079985028280351</v>
+        <v>0.0002079985028280342</v>
       </c>
       <c r="R4" t="n">
-        <v>6.787993223447296e-05</v>
+        <v>6.787993223447259e-05</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0004084596378370483</v>
+        <v>0.000408459637837048</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0001734853120814562</v>
+        <v>0.000173485312081456</v>
       </c>
       <c r="U4" t="n">
-        <v>0.00295450047933882</v>
+        <v>0.002954500479338828</v>
       </c>
       <c r="V4" t="n">
         <v>0.0002499444853396635</v>
       </c>
       <c r="W4" t="n">
-        <v>0.000768728581351386</v>
+        <v>0.0007687285813513872</v>
       </c>
       <c r="X4" t="n">
-        <v>0.0007141575874072554</v>
+        <v>0.0007141575874072563</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.0001892197197036123</v>
+        <v>0.0001892197197036128</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.0005283325715325805</v>
+        <v>0.0005283325715325812</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.001063741344343563</v>
+        <v>0.001063741344343561</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.001860694897466302</v>
+        <v>0.001860694897466298</v>
       </c>
     </row>
     <row r="5">
@@ -4710,85 +4710,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.528120574195169e-05</v>
+        <v>6.528120574195167e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0001031182276817835</v>
+        <v>0.0001031182276817834</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0001031182276817835</v>
+        <v>0.0001031182276817834</v>
       </c>
       <c r="E5" t="n">
         <v>8.297112962097285e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>7.117577154977365e-05</v>
+        <v>7.11757715497737e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0001109639806663832</v>
+        <v>0.0001109639806663831</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0001031182276817835</v>
+        <v>0.0001031182276817834</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0001031182276817835</v>
+        <v>0.0001031182276817834</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0001030244646807192</v>
+        <v>0.0001030244646807191</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0001031182276817835</v>
+        <v>0.0001031182276817834</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0001031182276817835</v>
+        <v>0.0001031182276817834</v>
       </c>
       <c r="M5" t="n">
         <v>0.0001031182276817823</v>
       </c>
       <c r="N5" t="n">
-        <v>8.194305666918485e-05</v>
+        <v>7.378820568292182e-05</v>
       </c>
       <c r="O5" t="n">
-        <v>8.184835039715783e-05</v>
+        <v>8.184835039715771e-05</v>
       </c>
       <c r="P5" t="n">
-        <v>7.987261416723517e-05</v>
+        <v>7.987261416723511e-05</v>
       </c>
       <c r="Q5" t="n">
-        <v>5.784536734272277e-05</v>
+        <v>5.784536734272278e-05</v>
       </c>
       <c r="R5" t="n">
-        <v>0.0001031182276817835</v>
+        <v>0.0001031182276817834</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0001031182276817835</v>
+        <v>0.0001031182276817834</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0001031182276817835</v>
+        <v>0.0001031182276817834</v>
       </c>
       <c r="U5" t="n">
-        <v>8.466605659171884e-05</v>
+        <v>8.466605659171885e-05</v>
       </c>
       <c r="V5" t="n">
-        <v>9.218999826720488e-05</v>
+        <v>9.21899982672048e-05</v>
       </c>
       <c r="W5" t="n">
-        <v>0.0001031256637419621</v>
+        <v>0.000103125663741962</v>
       </c>
       <c r="X5" t="n">
-        <v>6.131320558751832e-05</v>
+        <v>6.131320558751838e-05</v>
       </c>
       <c r="Y5" t="n">
         <v>0.0001407653604885729</v>
       </c>
       <c r="Z5" t="n">
-        <v>6.457836363386727e-05</v>
+        <v>6.457836363386715e-05</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.0001031182276817835</v>
+        <v>0.0001031182276817834</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.0001426421609791963</v>
+        <v>0.0001426421609791962</v>
       </c>
     </row>
     <row r="6">
@@ -4798,85 +4798,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9.049466926414748e-05</v>
+        <v>9.049466926414752e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0001139362850372974</v>
+        <v>0.0001139362850372975</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0001139362850372974</v>
+        <v>0.0001139362850372975</v>
       </c>
       <c r="E6" t="n">
         <v>0.0001085260510887282</v>
       </c>
       <c r="F6" t="n">
-        <v>5.989697073783733e-05</v>
+        <v>5.989697073783737e-05</v>
       </c>
       <c r="G6" t="n">
         <v>0.0001139362789989674</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0001139362850372974</v>
+        <v>0.0001139362850372975</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0001139362850372974</v>
+        <v>0.0001139362850372975</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0001138425220362328</v>
+        <v>0.0001138425220362329</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0001139362850372974</v>
+        <v>0.0001139362850372975</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0001139362850372974</v>
+        <v>0.0001139362850372975</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0001139362850372974</v>
+        <v>0.0001139362850372975</v>
       </c>
       <c r="N6" t="n">
-        <v>8.194305666918485e-05</v>
+        <v>0.0001139362850372975</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0001217047977710432</v>
+        <v>0.0001217047977710435</v>
       </c>
       <c r="P6" t="n">
-        <v>0.0001233943173185272</v>
+        <v>0.0001233943173185274</v>
       </c>
       <c r="Q6" t="n">
         <v>0.0001139362789989674</v>
       </c>
       <c r="R6" t="n">
-        <v>0.0001139362850372974</v>
+        <v>0.0001139362850372975</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0001139362850372974</v>
+        <v>0.0001139362850372975</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0001139362850372974</v>
+        <v>0.0001139362850372975</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0001139362850372974</v>
+        <v>0.0001139362850372975</v>
       </c>
       <c r="V6" t="n">
-        <v>0.0001403834017717231</v>
+        <v>0.0001403834017717232</v>
       </c>
       <c r="W6" t="n">
-        <v>0.0001139362850372974</v>
+        <v>0.0001139362850372975</v>
       </c>
       <c r="X6" t="n">
-        <v>0.0001139362850372974</v>
+        <v>0.0001139362850372975</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.0001139362850372974</v>
+        <v>0.0001139362850372975</v>
       </c>
       <c r="Z6" t="n">
-        <v>9.980307283814381e-05</v>
+        <v>9.980307283814393e-05</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.0001139362850372974</v>
+        <v>0.0001139362850372975</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.0001139362850372974</v>
+        <v>0.0001139362850372975</v>
       </c>
     </row>
     <row r="7">
@@ -4886,85 +4886,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-1.446460645448508e-06</v>
+        <v>-1.446460645448482e-06</v>
       </c>
       <c r="C7" t="n">
-        <v>1.247370748729435e-05</v>
+        <v>1.247370748729433e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>1.054749317985643e-05</v>
+        <v>1.054749317985644e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>4.242833129188058e-06</v>
+        <v>4.242833129188076e-06</v>
       </c>
       <c r="F7" t="n">
-        <v>1.146071232507092e-05</v>
+        <v>1.14607123250709e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>3.325505160406086e-06</v>
+        <v>3.325505160406087e-06</v>
       </c>
       <c r="H7" t="n">
-        <v>1.084438233994705e-05</v>
+        <v>1.084438233994707e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>1.00865320498044e-05</v>
+        <v>1.008653204980441e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>7.152299622387828e-07</v>
+        <v>7.152299622387794e-07</v>
       </c>
       <c r="K7" t="n">
-        <v>5.343975240571309e-06</v>
+        <v>5.343975240571324e-06</v>
       </c>
       <c r="L7" t="n">
-        <v>-4.565727171773983e-05</v>
+        <v>-4.565727171773992e-05</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.565392762786706e-05</v>
+        <v>-1.565392762786708e-05</v>
       </c>
       <c r="N7" t="n">
-        <v>1.181217791375752e-05</v>
+        <v>1.18121779137575e-05</v>
       </c>
       <c r="O7" t="n">
-        <v>1.041202936322643e-05</v>
+        <v>1.041202936322642e-05</v>
       </c>
       <c r="P7" t="n">
-        <v>-3.001690748576882e-06</v>
+        <v>-3.001690748576844e-06</v>
       </c>
       <c r="Q7" t="n">
-        <v>9.050804618007121e-06</v>
+        <v>9.05080461800712e-06</v>
       </c>
       <c r="R7" t="n">
-        <v>1.211525468239302e-05</v>
+        <v>1.211525468239305e-05</v>
       </c>
       <c r="S7" t="n">
-        <v>3.267831187570961e-06</v>
+        <v>3.267831187570938e-06</v>
       </c>
       <c r="T7" t="n">
-        <v>9.997153801941908e-06</v>
+        <v>9.997153801941897e-06</v>
       </c>
       <c r="U7" t="n">
-        <v>-5.455528449720986e-05</v>
+        <v>-5.455528449720997e-05</v>
       </c>
       <c r="V7" t="n">
-        <v>8.957426228473857e-06</v>
+        <v>8.957426228473839e-06</v>
       </c>
       <c r="W7" t="n">
-        <v>-3.162720432248241e-06</v>
+        <v>-3.162720432248274e-06</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.596603478794931e-06</v>
+        <v>-1.596603478794936e-06</v>
       </c>
       <c r="Y7" t="n">
-        <v>9.464712141984356e-06</v>
+        <v>9.464712141984427e-06</v>
       </c>
       <c r="Z7" t="n">
-        <v>7.630735571765031e-07</v>
+        <v>7.630735571764768e-07</v>
       </c>
       <c r="AA7" t="n">
-        <v>-9.590930621288725e-06</v>
+        <v>-9.590930621288694e-06</v>
       </c>
       <c r="AB7" t="n">
-        <v>-2.450331665326072e-05</v>
+        <v>-2.450331665326076e-05</v>
       </c>
     </row>
     <row r="8">
@@ -4974,85 +4974,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8.660741968238509e-06</v>
+        <v>8.660741968238521e-06</v>
       </c>
       <c r="C8" t="n">
         <v>1.265557412629774e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>1.210806187707808e-05</v>
+        <v>1.210806187707807e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>7.300463440186695e-06</v>
+        <v>7.300463440186723e-06</v>
       </c>
       <c r="F8" t="n">
-        <v>1.236885369233701e-05</v>
+        <v>1.236885369233699e-05</v>
       </c>
       <c r="G8" t="n">
         <v>1.003077183424816e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>1.219481110636037e-05</v>
+        <v>1.219481110636039e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>1.197790920262125e-05</v>
+        <v>1.197790920262126e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>9.264100747203153e-06</v>
+        <v>9.264100747203148e-06</v>
       </c>
       <c r="K8" t="n">
-        <v>1.062697307804569e-05</v>
+        <v>1.062697307804573e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>-3.96177099830591e-06</v>
+        <v>-3.961770998305865e-06</v>
       </c>
       <c r="M8" t="n">
-        <v>4.677997511697163e-06</v>
+        <v>4.677997511697154e-06</v>
       </c>
       <c r="N8" t="n">
-        <v>1.246683078577056e-05</v>
+        <v>1.246683078577055e-05</v>
       </c>
       <c r="O8" t="n">
-        <v>1.206264274263186e-05</v>
+        <v>1.206264274263189e-05</v>
       </c>
       <c r="P8" t="n">
-        <v>8.209260180805556e-06</v>
+        <v>8.209260180805571e-06</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.168091647816506e-05</v>
+        <v>1.168091647816509e-05</v>
       </c>
       <c r="R8" t="n">
-        <v>1.255425837734151e-05</v>
+        <v>1.255425837734153e-05</v>
       </c>
       <c r="S8" t="n">
-        <v>1.001832951822582e-05</v>
+        <v>1.001832951822583e-05</v>
       </c>
       <c r="T8" t="n">
-        <v>1.195192148297659e-05</v>
+        <v>1.195192148297655e-05</v>
       </c>
       <c r="U8" t="n">
-        <v>-6.516651941803604e-06</v>
+        <v>-6.516651941803566e-06</v>
       </c>
       <c r="V8" t="n">
-        <v>1.245401210835644e-05</v>
+        <v>1.245401210835642e-05</v>
       </c>
       <c r="W8" t="n">
-        <v>8.18987420295521e-06</v>
+        <v>8.18987420295522e-06</v>
       </c>
       <c r="X8" t="n">
-        <v>8.653329514406799e-06</v>
+        <v>8.65332951440679e-06</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.179680246619346e-05</v>
+        <v>1.179680246619347e-05</v>
       </c>
       <c r="Z8" t="n">
         <v>9.296942093991186e-06</v>
       </c>
       <c r="AA8" t="n">
-        <v>6.357276906097121e-06</v>
+        <v>6.3572769060971e-06</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.145173870290934e-06</v>
+        <v>2.145173870290947e-06</v>
       </c>
     </row>
   </sheetData>
@@ -5218,31 +5218,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.108225524344104e-05</v>
+        <v>1.108225524344102e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>1.104963480773268e-05</v>
+        <v>1.104963480773266e-05</v>
       </c>
       <c r="D2" t="n">
         <v>1.102525773692314e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>7.689836440306573e-06</v>
+        <v>7.689836440306546e-06</v>
       </c>
       <c r="F2" t="n">
-        <v>1.112267708107364e-05</v>
+        <v>1.112267708107361e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>1.139221079934211e-05</v>
+        <v>1.139221079934207e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>1.104193645965787e-05</v>
+        <v>1.104193645965786e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>1.131355389128329e-05</v>
+        <v>1.131355389128328e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>1.137369956134282e-05</v>
+        <v>1.13736995613428e-05</v>
       </c>
       <c r="K2" t="n">
         <v>1.172374737022376e-05</v>
@@ -5254,49 +5254,49 @@
         <v>1.140934839009149e-05</v>
       </c>
       <c r="N2" t="n">
-        <v>1.102259392678554e-05</v>
+        <v>1.102259392678553e-05</v>
       </c>
       <c r="O2" t="n">
-        <v>1.10949779941783e-05</v>
+        <v>1.109497799417829e-05</v>
       </c>
       <c r="P2" t="n">
-        <v>1.098723471114825e-05</v>
+        <v>1.098723471114826e-05</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.10372186503355e-05</v>
+        <v>1.103721865033549e-05</v>
       </c>
       <c r="R2" t="n">
-        <v>1.108763103861468e-05</v>
+        <v>1.108763103861469e-05</v>
       </c>
       <c r="S2" t="n">
-        <v>1.170893328735187e-05</v>
+        <v>1.170893328735188e-05</v>
       </c>
       <c r="T2" t="n">
         <v>1.102124595177374e-05</v>
       </c>
       <c r="U2" t="n">
-        <v>1.145112365454442e-05</v>
+        <v>1.145112365454441e-05</v>
       </c>
       <c r="V2" t="n">
-        <v>1.275937924360009e-05</v>
+        <v>1.27593792436001e-05</v>
       </c>
       <c r="W2" t="n">
-        <v>1.178130159646769e-05</v>
+        <v>1.178130159646768e-05</v>
       </c>
       <c r="X2" t="n">
-        <v>1.531733190541329e-05</v>
+        <v>1.531733190541327e-05</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.29402825936406e-05</v>
+        <v>1.294028259364058e-05</v>
       </c>
       <c r="Z2" t="n">
         <v>1.123817679561672e-05</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.173633900129191e-05</v>
+        <v>1.17363390012919e-05</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.134157403011192e-05</v>
+        <v>1.134157403011189e-05</v>
       </c>
     </row>
     <row r="3">
@@ -5306,85 +5306,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.097009461386289e-05</v>
+        <v>1.097009461386286e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>1.097009461386289e-05</v>
+        <v>1.097009461386286e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>1.097009461386289e-05</v>
+        <v>1.097009461386286e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>7.523118238049935e-06</v>
+        <v>7.523118238049947e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>1.097009461386289e-05</v>
+        <v>1.097009461386286e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>1.097009461386289e-05</v>
+        <v>1.097009461386286e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>1.097009461386289e-05</v>
+        <v>1.097009461386286e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>1.097009461386289e-05</v>
+        <v>1.097009461386286e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>1.09592311389048e-05</v>
+        <v>1.095923113890482e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>1.097009461386289e-05</v>
+        <v>1.097009461386286e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>1.097009461386289e-05</v>
+        <v>1.097009461386286e-05</v>
       </c>
       <c r="M3" t="n">
-        <v>1.097009461386289e-05</v>
+        <v>1.097009461386286e-05</v>
       </c>
       <c r="N3" t="n">
-        <v>1.097009461386289e-05</v>
+        <v>1.097009461386286e-05</v>
       </c>
       <c r="O3" t="n">
-        <v>1.097009461386289e-05</v>
+        <v>1.097009461386286e-05</v>
       </c>
       <c r="P3" t="n">
-        <v>1.097009461386289e-05</v>
+        <v>1.097009461386286e-05</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.097009461386289e-05</v>
+        <v>1.097009461386286e-05</v>
       </c>
       <c r="R3" t="n">
-        <v>1.097009461386289e-05</v>
+        <v>1.097009461386286e-05</v>
       </c>
       <c r="S3" t="n">
-        <v>1.097009461386289e-05</v>
+        <v>1.097009461386286e-05</v>
       </c>
       <c r="T3" t="n">
-        <v>1.097009461386289e-05</v>
+        <v>1.097009461386286e-05</v>
       </c>
       <c r="U3" t="n">
-        <v>1.097009461386289e-05</v>
+        <v>1.097009461386286e-05</v>
       </c>
       <c r="V3" t="n">
-        <v>1.244451104623681e-05</v>
+        <v>1.244451104623672e-05</v>
       </c>
       <c r="W3" t="n">
-        <v>1.097009461386289e-05</v>
+        <v>1.097009461386286e-05</v>
       </c>
       <c r="X3" t="n">
-        <v>1.097009461386289e-05</v>
+        <v>1.097009461386286e-05</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.097009461386289e-05</v>
+        <v>1.097009461386286e-05</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.097009461386289e-05</v>
+        <v>1.097009461386286e-05</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.097009461386289e-05</v>
+        <v>1.097009461386286e-05</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.097009461386289e-05</v>
+        <v>1.097009461386286e-05</v>
       </c>
     </row>
     <row r="4">
@@ -5394,82 +5394,82 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.007653850462778e-05</v>
+        <v>7.007653850462782e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>7.262681632500288e-05</v>
+        <v>7.262681632500277e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>6.790540533013669e-05</v>
+        <v>6.790540533013653e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>5.715670770242383e-05</v>
+        <v>5.715670770242376e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>8.831641423440794e-05</v>
+        <v>8.83164142344079e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0001497410578792536</v>
+        <v>0.0001497410578792538</v>
       </c>
       <c r="H4" t="n">
-        <v>6.740650609741769e-05</v>
+        <v>6.740650609741766e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0001370593570192365</v>
+        <v>0.0001370593570192362</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0001486830221512862</v>
+        <v>0.0001486830221512865</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0002333831555158423</v>
+        <v>0.0002333831555158421</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0001453174942131596</v>
+        <v>0.0001453174942131592</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0001674231161525558</v>
+        <v>0.0001674231161525556</v>
       </c>
       <c r="N4" t="n">
-        <v>5.900048756693419e-05</v>
+        <v>5.900048756693411e-05</v>
       </c>
       <c r="O4" t="n">
-        <v>7.77133366131292e-05</v>
+        <v>7.771333661312921e-05</v>
       </c>
       <c r="P4" t="n">
-        <v>4.819038163953496e-05</v>
+        <v>4.819038163953491e-05</v>
       </c>
       <c r="Q4" t="n">
-        <v>6.922458952034148e-05</v>
+        <v>6.922458952034138e-05</v>
       </c>
       <c r="R4" t="n">
-        <v>7.871225342148756e-05</v>
+        <v>7.871225342148734e-05</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0002095461094464429</v>
+        <v>0.000209546109446443</v>
       </c>
       <c r="T4" t="n">
-        <v>6.791703377368073e-05</v>
+        <v>6.79170337736805e-05</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0001643027264028813</v>
+        <v>0.0001643027264028811</v>
       </c>
       <c r="V4" t="n">
-        <v>0.0001291537383044941</v>
+        <v>0.0001291537383044952</v>
       </c>
       <c r="W4" t="n">
-        <v>0.0002428486092715681</v>
+        <v>0.0002428486092715676</v>
       </c>
       <c r="X4" t="n">
-        <v>0.001098560449378367</v>
+        <v>0.001098560449378368</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.0005412358074018655</v>
+        <v>0.0005412358074018654</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.000108879389402093</v>
+        <v>0.0001088793894020928</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.0002360620080143704</v>
+        <v>0.0002360620080143708</v>
       </c>
       <c r="AB4" t="n">
         <v>0.0001471911342518843</v>
@@ -5482,85 +5482,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.68210492564771e-05</v>
+        <v>5.682104925647688e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>8.969146987241095e-05</v>
+        <v>8.969146987241054e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>8.969146987241095e-05</v>
+        <v>8.969146987241054e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>7.218894051110124e-05</v>
+        <v>7.218894051110093e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>6.19418766238504e-05</v>
+        <v>6.194187662385015e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>9.650736571804549e-05</v>
+        <v>9.650736571804504e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>8.969146987241095e-05</v>
+        <v>8.969146987241054e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>8.969146987241095e-05</v>
+        <v>8.969146987241054e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>8.960462120585682e-05</v>
+        <v>8.960462120585641e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>8.969146987241095e-05</v>
+        <v>8.969146987241054e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>8.969146987241095e-05</v>
+        <v>8.969146987241054e-05</v>
       </c>
       <c r="M5" t="n">
-        <v>8.969146987241189e-05</v>
+        <v>8.969146987241145e-05</v>
       </c>
       <c r="N5" t="n">
-        <v>5.900048756693419e-05</v>
+        <v>6.421139479370276e-05</v>
       </c>
       <c r="O5" t="n">
-        <v>7.121354066545446e-05</v>
+        <v>7.121354066545401e-05</v>
       </c>
       <c r="P5" t="n">
-        <v>6.949714551668493e-05</v>
+        <v>6.949714551668459e-05</v>
       </c>
       <c r="Q5" t="n">
-        <v>5.036126137466022e-05</v>
+        <v>5.036126137466007e-05</v>
       </c>
       <c r="R5" t="n">
-        <v>8.969146987241095e-05</v>
+        <v>8.969146987241054e-05</v>
       </c>
       <c r="S5" t="n">
-        <v>8.969146987241095e-05</v>
+        <v>8.969146987241054e-05</v>
       </c>
       <c r="T5" t="n">
-        <v>8.969146987241095e-05</v>
+        <v>8.969146987241054e-05</v>
       </c>
       <c r="U5" t="n">
-        <v>7.367000355951876e-05</v>
+        <v>7.367000355951849e-05</v>
       </c>
       <c r="V5" t="n">
-        <v>8.017200226515739e-05</v>
+        <v>8.017200226515699e-05</v>
       </c>
       <c r="W5" t="n">
-        <v>8.969792985253981e-05</v>
+        <v>8.969792985253948e-05</v>
       </c>
       <c r="X5" t="n">
-        <v>5.337390073899125e-05</v>
+        <v>5.337390073899103e-05</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.0001224116684517898</v>
+        <v>0.0001224116684517892</v>
       </c>
       <c r="Z5" t="n">
-        <v>5.621046431787023e-05</v>
+        <v>5.621046431786993e-05</v>
       </c>
       <c r="AA5" t="n">
-        <v>8.969146987241095e-05</v>
+        <v>8.969146987241054e-05</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.0001240273727860447</v>
+        <v>0.0001240273727860441</v>
       </c>
     </row>
     <row r="6">
@@ -5570,85 +5570,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7.118494015622571e-05</v>
+        <v>7.118494015622564e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>8.946431300209669e-05</v>
+        <v>8.946431300209666e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>8.946431300209669e-05</v>
+        <v>8.946431300209666e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>8.524550954488341e-05</v>
+        <v>8.524550954488324e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>4.732536758168992e-05</v>
+        <v>4.732536758168982e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>8.946431460821873e-05</v>
+        <v>8.94643146082187e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>8.946431300209669e-05</v>
+        <v>8.946431300209666e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>8.946431300209669e-05</v>
+        <v>8.946431300209666e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>8.937746433554259e-05</v>
+        <v>8.93774643355423e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>8.946431300209669e-05</v>
+        <v>8.946431300209666e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>8.946431300209669e-05</v>
+        <v>8.946431300209666e-05</v>
       </c>
       <c r="M6" t="n">
-        <v>8.946431300209669e-05</v>
+        <v>8.946431300209666e-05</v>
       </c>
       <c r="N6" t="n">
-        <v>5.900048756693419e-05</v>
+        <v>8.946431300209666e-05</v>
       </c>
       <c r="O6" t="n">
-        <v>9.552207536692732e-05</v>
+        <v>9.552207536692715e-05</v>
       </c>
       <c r="P6" t="n">
-        <v>9.68395343981755e-05</v>
+        <v>9.68395343981753e-05</v>
       </c>
       <c r="Q6" t="n">
-        <v>8.946431460821873e-05</v>
+        <v>8.94643146082187e-05</v>
       </c>
       <c r="R6" t="n">
-        <v>8.946431300209669e-05</v>
+        <v>8.946431300209666e-05</v>
       </c>
       <c r="S6" t="n">
-        <v>8.946431300209669e-05</v>
+        <v>8.946431300209666e-05</v>
       </c>
       <c r="T6" t="n">
-        <v>8.946431300209669e-05</v>
+        <v>8.946431300209666e-05</v>
       </c>
       <c r="U6" t="n">
-        <v>8.946431300209669e-05</v>
+        <v>8.946431300209666e-05</v>
       </c>
       <c r="V6" t="n">
-        <v>0.0001099984049080261</v>
+        <v>0.000109998404908026</v>
       </c>
       <c r="W6" t="n">
-        <v>8.946431300209669e-05</v>
+        <v>8.946431300209666e-05</v>
       </c>
       <c r="X6" t="n">
-        <v>8.946431300209669e-05</v>
+        <v>8.946431300209666e-05</v>
       </c>
       <c r="Y6" t="n">
-        <v>8.946431300209669e-05</v>
+        <v>8.946431300209666e-05</v>
       </c>
       <c r="Z6" t="n">
-        <v>7.844347727906734e-05</v>
+        <v>7.844347727906724e-05</v>
       </c>
       <c r="AA6" t="n">
-        <v>8.946431300209669e-05</v>
+        <v>8.946431300209666e-05</v>
       </c>
       <c r="AB6" t="n">
-        <v>8.946431300209669e-05</v>
+        <v>8.946431300209666e-05</v>
       </c>
     </row>
     <row r="7">
@@ -5658,85 +5658,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.001009733902463e-05</v>
+        <v>1.00100973390246e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>1.021570666581531e-05</v>
+        <v>1.021570666581529e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>1.03594162013539e-05</v>
+        <v>1.035941620135387e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>6.463003934853093e-06</v>
+        <v>6.463003934853071e-06</v>
       </c>
       <c r="F7" t="n">
-        <v>9.794760087255063e-06</v>
+        <v>9.794760087255041e-06</v>
       </c>
       <c r="G7" t="n">
-        <v>8.167703861176742e-06</v>
+        <v>8.167703861176771e-06</v>
       </c>
       <c r="H7" t="n">
-        <v>1.026680477025255e-05</v>
+        <v>1.026680477025253e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>8.675097546790912e-06</v>
+        <v>8.67509754679088e-06</v>
       </c>
       <c r="J7" t="n">
-        <v>8.218433275221914e-06</v>
+        <v>8.218433275221921e-06</v>
       </c>
       <c r="K7" t="n">
-        <v>6.261266311006073e-06</v>
+        <v>6.261266311006071e-06</v>
       </c>
       <c r="L7" t="n">
-        <v>8.478935797169856e-06</v>
+        <v>8.478935797169831e-06</v>
       </c>
       <c r="M7" t="n">
-        <v>8.120612224527734e-06</v>
+        <v>8.120612224527712e-06</v>
       </c>
       <c r="N7" t="n">
-        <v>1.037232126818872e-05</v>
+        <v>1.037232126818871e-05</v>
       </c>
       <c r="O7" t="n">
-        <v>9.933230278244799e-06</v>
+        <v>9.933230278244804e-06</v>
       </c>
       <c r="P7" t="n">
-        <v>1.057452496772092e-05</v>
+        <v>1.05745249677209e-05</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.028750150236435e-05</v>
+        <v>1.028750150236433e-05</v>
       </c>
       <c r="R7" t="n">
-        <v>9.998080401766335e-06</v>
+        <v>9.998080401766325e-06</v>
       </c>
       <c r="S7" t="n">
-        <v>6.296489066502355e-06</v>
+        <v>6.296489066502342e-06</v>
       </c>
       <c r="T7" t="n">
-        <v>1.038331686242362e-05</v>
+        <v>1.038331686242366e-05</v>
       </c>
       <c r="U7" t="n">
-        <v>7.832530581258242e-06</v>
+        <v>7.832530581258253e-06</v>
       </c>
       <c r="V7" t="n">
-        <v>1.014032129106651e-05</v>
+        <v>1.014032129106645e-05</v>
       </c>
       <c r="W7" t="n">
-        <v>5.892299399986324e-06</v>
+        <v>5.89229939998631e-06</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.480636616401511e-05</v>
+        <v>-1.480636616401509e-05</v>
       </c>
       <c r="Y7" t="n">
-        <v>-9.286619823274037e-07</v>
+        <v>-9.286619823274397e-07</v>
       </c>
       <c r="Z7" t="n">
-        <v>9.084634195888774e-06</v>
+        <v>9.08463419588876e-06</v>
       </c>
       <c r="AA7" t="n">
-        <v>6.161620310831422e-06</v>
+        <v>6.16162031083141e-06</v>
       </c>
       <c r="AB7" t="n">
-        <v>8.507133531027408e-06</v>
+        <v>8.507133531027407e-06</v>
       </c>
     </row>
     <row r="8">
@@ -5746,85 +5746,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.064545342405983e-05</v>
+        <v>1.064545342405982e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>1.07063858872793e-05</v>
+        <v>1.070638588727928e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>1.074739711311491e-05</v>
+        <v>1.07473971131149e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>7.207481053968142e-06</v>
+        <v>7.207481053968136e-06</v>
       </c>
       <c r="F8" t="n">
-        <v>1.058789612589818e-05</v>
+        <v>1.058789612589815e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>1.011711407618045e-05</v>
+        <v>1.011711407618046e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>1.072193733956341e-05</v>
+        <v>1.07219373395634e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>1.026932291204384e-05</v>
+        <v>1.026932291204383e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>1.012662779896254e-05</v>
+        <v>1.012662779896252e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>9.581215486278512e-06</v>
+        <v>9.581215486278486e-06</v>
       </c>
       <c r="L8" t="n">
-        <v>1.020883408754182e-05</v>
+        <v>1.020883408754183e-05</v>
       </c>
       <c r="M8" t="n">
-        <v>1.011282482218243e-05</v>
+        <v>1.011282482218244e-05</v>
       </c>
       <c r="N8" t="n">
-        <v>1.075060514951319e-05</v>
+        <v>1.075060514951317e-05</v>
       </c>
       <c r="O8" t="n">
         <v>1.06232014171815e-05</v>
       </c>
       <c r="P8" t="n">
-        <v>1.080724926154798e-05</v>
+        <v>1.0807249261548e-05</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.07266366093085e-05</v>
+        <v>1.072663660930848e-05</v>
       </c>
       <c r="R8" t="n">
-        <v>1.064536147448526e-05</v>
+        <v>1.064536147448524e-05</v>
       </c>
       <c r="S8" t="n">
-        <v>9.582427869405698e-06</v>
+        <v>9.582427869405681e-06</v>
       </c>
       <c r="T8" t="n">
-        <v>1.075426020491914e-05</v>
+        <v>1.075426020491915e-05</v>
       </c>
       <c r="U8" t="n">
-        <v>1.002352202088602e-05</v>
+        <v>1.002352202088601e-05</v>
       </c>
       <c r="V8" t="n">
-        <v>1.171096556198055e-05</v>
+        <v>1.171096556198057e-05</v>
       </c>
       <c r="W8" t="n">
-        <v>9.470888592180657e-06</v>
+        <v>9.470888592180649e-06</v>
       </c>
       <c r="X8" t="n">
-        <v>3.588960106772298e-06</v>
+        <v>3.588960106772291e-06</v>
       </c>
       <c r="Y8" t="n">
-        <v>7.526310423286599e-06</v>
+        <v>7.526310423286608e-06</v>
       </c>
       <c r="Z8" t="n">
         <v>1.038028629683267e-05</v>
       </c>
       <c r="AA8" t="n">
-        <v>9.548467869714192e-06</v>
+        <v>9.548467869714182e-06</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.022091888843053e-05</v>
+        <v>1.02209188884305e-05</v>
       </c>
     </row>
   </sheetData>
@@ -5993,61 +5993,61 @@
         <v>1.10729916700195e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>1.100308789796182e-05</v>
+        <v>1.100308789796181e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>1.125440609809035e-05</v>
+        <v>1.125440609809033e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>7.553297321457283e-06</v>
+        <v>7.553297321457287e-06</v>
       </c>
       <c r="F2" t="n">
-        <v>1.105909970988804e-05</v>
+        <v>1.105909970988802e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>1.108758205542183e-05</v>
+        <v>1.108758205542181e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>1.098318832860548e-05</v>
+        <v>1.098318832860547e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>1.133762684908953e-05</v>
+        <v>1.133762684908952e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>1.124257073243592e-05</v>
+        <v>1.12425707324359e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>1.204363740476015e-05</v>
+        <v>1.204363740476014e-05</v>
       </c>
       <c r="L2" t="n">
         <v>1.116314686023457e-05</v>
       </c>
       <c r="M2" t="n">
-        <v>1.134197488980478e-05</v>
+        <v>1.134197488980477e-05</v>
       </c>
       <c r="N2" t="n">
-        <v>1.095802834649461e-05</v>
+        <v>1.095802834649459e-05</v>
       </c>
       <c r="O2" t="n">
-        <v>1.104045080734085e-05</v>
+        <v>1.104045080734084e-05</v>
       </c>
       <c r="P2" t="n">
-        <v>1.094244511120557e-05</v>
+        <v>1.094244511120556e-05</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.103295986161987e-05</v>
+        <v>1.103295986161986e-05</v>
       </c>
       <c r="R2" t="n">
-        <v>1.106322565668205e-05</v>
+        <v>1.106322565668204e-05</v>
       </c>
       <c r="S2" t="n">
-        <v>1.146254986321217e-05</v>
+        <v>1.146254986321216e-05</v>
       </c>
       <c r="T2" t="n">
-        <v>1.103666033700356e-05</v>
+        <v>1.103666033700357e-05</v>
       </c>
       <c r="U2" t="n">
-        <v>1.149566025716269e-05</v>
+        <v>1.149566025716268e-05</v>
       </c>
       <c r="V2" t="n">
         <v>1.301252468954654e-05</v>
@@ -6056,19 +6056,19 @@
         <v>1.114853204895201e-05</v>
       </c>
       <c r="X2" t="n">
-        <v>1.560291378439323e-05</v>
+        <v>1.56029137843932e-05</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.232211575751697e-05</v>
+        <v>1.232211575751695e-05</v>
       </c>
       <c r="Z2" t="n">
         <v>1.107152049158852e-05</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.12960018914183e-05</v>
+        <v>1.129600189141831e-05</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.186868429225727e-05</v>
+        <v>1.186868429225726e-05</v>
       </c>
     </row>
     <row r="3">
@@ -6087,7 +6087,7 @@
         <v>1.091207941578236e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>7.462480859670975e-06</v>
+        <v>7.462480859670949e-06</v>
       </c>
       <c r="F3" t="n">
         <v>1.091207941578236e-05</v>
@@ -6102,7 +6102,7 @@
         <v>1.091207941578236e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>1.091565001303219e-05</v>
+        <v>1.091565001303217e-05</v>
       </c>
       <c r="K3" t="n">
         <v>1.091207941578236e-05</v>
@@ -6166,34 +6166,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8.185863395333861e-05</v>
+        <v>8.185863395333852e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>7.332906895403293e-05</v>
+        <v>7.332906895403286e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0001358355350563206</v>
+        <v>0.0001358355350563204</v>
       </c>
       <c r="E4" t="n">
-        <v>4.489574444468593e-05</v>
+        <v>4.489574444468586e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>8.528611569854735e-05</v>
+        <v>8.528611569854727e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>9.226888227988071e-05</v>
+        <v>9.226888227988089e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>6.809961867681201e-05</v>
+        <v>6.809961867681217e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0001572189569960177</v>
+        <v>0.0001572189569960175</v>
       </c>
       <c r="J4" t="n">
-        <v>0.000127907500280904</v>
+        <v>0.0001279075002809043</v>
       </c>
       <c r="K4" t="n">
-        <v>0.000325418283356612</v>
+        <v>0.0003254182833566118</v>
       </c>
       <c r="L4" t="n">
         <v>0.000115461777960868</v>
@@ -6202,31 +6202,31 @@
         <v>0.0001618201752147636</v>
       </c>
       <c r="N4" t="n">
-        <v>5.547092294784051e-05</v>
+        <v>5.547092294784037e-05</v>
       </c>
       <c r="O4" t="n">
-        <v>7.735930071512097e-05</v>
+        <v>7.735930071512082e-05</v>
       </c>
       <c r="P4" t="n">
-        <v>5.425842708688992e-05</v>
+        <v>5.425842708689002e-05</v>
       </c>
       <c r="Q4" t="n">
-        <v>7.761922162234238e-05</v>
+        <v>7.761922162234233e-05</v>
       </c>
       <c r="R4" t="n">
-        <v>8.575858258403054e-05</v>
+        <v>8.575858258403039e-05</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0001721028760082143</v>
+        <v>0.0001721028760082141</v>
       </c>
       <c r="T4" t="n">
-        <v>8.061658244092018e-05</v>
+        <v>8.061658244092011e-05</v>
       </c>
       <c r="U4" t="n">
         <v>0.0001851372252483572</v>
       </c>
       <c r="V4" t="n">
-        <v>0.0001650913902293645</v>
+        <v>0.0001650913902293647</v>
       </c>
       <c r="W4" t="n">
         <v>0.0001045555060138661</v>
@@ -6235,16 +6235,16 @@
         <v>0.001164150630636727</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.0004025058563105621</v>
+        <v>0.0004025058563105627</v>
       </c>
       <c r="Z4" t="n">
-        <v>8.564402977861632e-05</v>
+        <v>8.564402977861625e-05</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.0001391038985535256</v>
+        <v>0.0001391038985535257</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.0003030471099244802</v>
+        <v>0.0003030471099244799</v>
       </c>
     </row>
     <row r="5">
@@ -6254,82 +6254,82 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.675429487892456e-05</v>
+        <v>5.675429487892453e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>8.948686460312547e-05</v>
+        <v>8.94868646031254e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>8.948686460312547e-05</v>
+        <v>8.94868646031254e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>7.205773677540377e-05</v>
+        <v>7.20577367754036e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>6.185364668841082e-05</v>
+        <v>6.185364668841075e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>9.627417616830536e-05</v>
+        <v>9.627417616830537e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>8.948686460312547e-05</v>
+        <v>8.94868646031254e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>8.948686460312547e-05</v>
+        <v>8.94868646031254e-05</v>
       </c>
       <c r="J5" t="n">
         <v>8.940295590238266e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>8.948686460312547e-05</v>
+        <v>8.94868646031254e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>8.948686460312547e-05</v>
+        <v>8.94868646031254e-05</v>
       </c>
       <c r="M5" t="n">
-        <v>8.948686460313028e-05</v>
+        <v>8.948686460313021e-05</v>
       </c>
       <c r="N5" t="n">
-        <v>5.547092294784051e-05</v>
+        <v>6.41136470273446e-05</v>
       </c>
       <c r="O5" t="n">
-        <v>7.108642752923171e-05</v>
+        <v>7.108642752923169e-05</v>
       </c>
       <c r="P5" t="n">
-        <v>6.937723054220731e-05</v>
+        <v>6.937723054220715e-05</v>
       </c>
       <c r="Q5" t="n">
-        <v>5.032159784374345e-05</v>
+        <v>5.032159784374342e-05</v>
       </c>
       <c r="R5" t="n">
-        <v>8.948686460312547e-05</v>
+        <v>8.94868646031254e-05</v>
       </c>
       <c r="S5" t="n">
-        <v>8.948686460312547e-05</v>
+        <v>8.94868646031254e-05</v>
       </c>
       <c r="T5" t="n">
-        <v>8.948686460312547e-05</v>
+        <v>8.94868646031254e-05</v>
       </c>
       <c r="U5" t="n">
-        <v>7.353619838756498e-05</v>
+        <v>7.353619838756497e-05</v>
       </c>
       <c r="V5" t="n">
         <v>8.002776320460456e-05</v>
       </c>
       <c r="W5" t="n">
-        <v>8.949329749115417e-05</v>
+        <v>8.94932974911541e-05</v>
       </c>
       <c r="X5" t="n">
-        <v>5.332160289965906e-05</v>
+        <v>5.332160289965902e-05</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.0001220760176005505</v>
+        <v>0.0001220760176005503</v>
       </c>
       <c r="Z5" t="n">
-        <v>5.614627059144014e-05</v>
+        <v>5.614627059144012e-05</v>
       </c>
       <c r="AA5" t="n">
-        <v>8.948686460312547e-05</v>
+        <v>8.94868646031254e-05</v>
       </c>
       <c r="AB5" t="n">
         <v>0.0001236787707330273</v>
@@ -6342,85 +6342,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6.726704562772717e-05</v>
+        <v>6.726704562772713e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>8.442136726200984e-05</v>
+        <v>8.442136726200962e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>8.442136726200984e-05</v>
+        <v>8.442136726200962e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>8.046222008210708e-05</v>
+        <v>8.046222008210692e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>4.487597355762953e-05</v>
+        <v>4.487597355762944e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>8.442136762876805e-05</v>
+        <v>8.442136762876801e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>8.442136726200984e-05</v>
+        <v>8.442136726200962e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>8.442136726200984e-05</v>
+        <v>8.442136726200962e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>8.433745856126709e-05</v>
+        <v>8.433745856126696e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>8.442136726200984e-05</v>
+        <v>8.442136726200962e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>8.442136726200984e-05</v>
+        <v>8.442136726200962e-05</v>
       </c>
       <c r="M6" t="n">
-        <v>8.442136726200984e-05</v>
+        <v>8.442136726200962e-05</v>
       </c>
       <c r="N6" t="n">
-        <v>5.547092294784051e-05</v>
+        <v>8.442136726200962e-05</v>
       </c>
       <c r="O6" t="n">
-        <v>9.010628747836194e-05</v>
+        <v>9.010628747836188e-05</v>
       </c>
       <c r="P6" t="n">
-        <v>9.134266000875015e-05</v>
+        <v>9.134266000874989e-05</v>
       </c>
       <c r="Q6" t="n">
-        <v>8.442136762876805e-05</v>
+        <v>8.442136762876801e-05</v>
       </c>
       <c r="R6" t="n">
-        <v>8.442136726200984e-05</v>
+        <v>8.442136726200962e-05</v>
       </c>
       <c r="S6" t="n">
-        <v>8.442136726200984e-05</v>
+        <v>8.442136726200962e-05</v>
       </c>
       <c r="T6" t="n">
-        <v>8.442136726200984e-05</v>
+        <v>8.442136726200962e-05</v>
       </c>
       <c r="U6" t="n">
-        <v>8.442136726200984e-05</v>
+        <v>8.442136726200962e-05</v>
       </c>
       <c r="V6" t="n">
-        <v>0.0001036759835172511</v>
+        <v>0.000103675983517251</v>
       </c>
       <c r="W6" t="n">
-        <v>8.442136726200984e-05</v>
+        <v>8.442136726200962e-05</v>
       </c>
       <c r="X6" t="n">
-        <v>8.442136726200984e-05</v>
+        <v>8.442136726200962e-05</v>
       </c>
       <c r="Y6" t="n">
-        <v>8.442136726200984e-05</v>
+        <v>8.442136726200962e-05</v>
       </c>
       <c r="Z6" t="n">
-        <v>7.407883688397364e-05</v>
+        <v>7.407883688397357e-05</v>
       </c>
       <c r="AA6" t="n">
-        <v>8.442136726200984e-05</v>
+        <v>8.442136726200962e-05</v>
       </c>
       <c r="AB6" t="n">
-        <v>8.442136726200984e-05</v>
+        <v>8.442136726200962e-05</v>
       </c>
     </row>
     <row r="7">
@@ -6430,85 +6430,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9.669699283515076e-06</v>
+        <v>9.669699283515074e-06</v>
       </c>
       <c r="C7" t="n">
-        <v>1.009797661947938e-05</v>
+        <v>1.00979766194794e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>8.626861519976837e-06</v>
+        <v>8.626861519976827e-06</v>
       </c>
       <c r="E7" t="n">
-        <v>6.859000519475535e-06</v>
+        <v>6.859000519475511e-06</v>
       </c>
       <c r="F7" t="n">
-        <v>9.776659527005411e-06</v>
+        <v>9.776659527005396e-06</v>
       </c>
       <c r="G7" t="n">
-        <v>9.583664526770206e-06</v>
+        <v>9.583664526770165e-06</v>
       </c>
       <c r="H7" t="n">
-        <v>1.022053263454905e-05</v>
+        <v>1.022053263454904e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>8.144664355031456e-06</v>
+        <v>8.144664355031427e-06</v>
       </c>
       <c r="J7" t="n">
-        <v>8.705054595974692e-06</v>
+        <v>8.705054595974663e-06</v>
       </c>
       <c r="K7" t="n">
         <v>3.994061865899777e-06</v>
       </c>
       <c r="L7" t="n">
-        <v>9.144783211068568e-06</v>
+        <v>9.14478321106856e-06</v>
       </c>
       <c r="M7" t="n">
-        <v>8.124706822033051e-06</v>
+        <v>8.124706822033034e-06</v>
       </c>
       <c r="N7" t="n">
-        <v>1.03603997262789e-05</v>
+        <v>1.036039972627888e-05</v>
       </c>
       <c r="O7" t="n">
-        <v>9.862099118146463e-06</v>
+        <v>9.862099118146458e-06</v>
       </c>
       <c r="P7" t="n">
-        <v>1.044533702032083e-05</v>
+        <v>1.044533702032081e-05</v>
       </c>
       <c r="Q7" t="n">
-        <v>9.921350844374735e-06</v>
+        <v>9.921350844374725e-06</v>
       </c>
       <c r="R7" t="n">
-        <v>9.751470533353819e-06</v>
+        <v>9.751470533353807e-06</v>
       </c>
       <c r="S7" t="n">
-        <v>7.363274376161678e-06</v>
+        <v>7.36327437616168e-06</v>
       </c>
       <c r="T7" t="n">
         <v>9.902983937594776e-06</v>
       </c>
       <c r="U7" t="n">
-        <v>7.175248609744729e-06</v>
+        <v>7.175248609744718e-06</v>
       </c>
       <c r="V7" t="n">
-        <v>9.229288644303308e-06</v>
+        <v>9.229288644303306e-06</v>
       </c>
       <c r="W7" t="n">
-        <v>9.234057835752507e-06</v>
+        <v>9.234057835752501e-06</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.68714110510942e-05</v>
+        <v>-1.687141105109422e-05</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.32156060709279e-06</v>
+        <v>2.321560607092777e-06</v>
       </c>
       <c r="Z7" t="n">
-        <v>9.679868263084321e-06</v>
+        <v>9.679868263084313e-06</v>
       </c>
       <c r="AA7" t="n">
-        <v>8.365807242685922e-06</v>
+        <v>8.365807242685884e-06</v>
       </c>
       <c r="AB7" t="n">
-        <v>5.030039323895722e-06</v>
+        <v>5.030039323895715e-06</v>
       </c>
     </row>
     <row r="8">
@@ -6518,22 +6518,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.050770475060733e-05</v>
+        <v>1.050770475060732e-05</v>
       </c>
       <c r="C8" t="n">
         <v>1.063266853125229e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>1.021462467294151e-05</v>
+        <v>1.02146246729415e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>7.278711843490625e-06</v>
+        <v>7.278711843490633e-06</v>
       </c>
       <c r="F8" t="n">
-        <v>1.054248004212603e-05</v>
+        <v>1.054248004212602e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>1.048314904751421e-05</v>
+        <v>1.04831490475142e-05</v>
       </c>
       <c r="H8" t="n">
         <v>1.06685323393155e-05</v>
@@ -6545,16 +6545,16 @@
         <v>1.023674277292517e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>8.895917373149742e-06</v>
+        <v>8.895917373149755e-06</v>
       </c>
       <c r="L8" t="n">
-        <v>1.035902145505096e-05</v>
+        <v>1.035902145505095e-05</v>
       </c>
       <c r="M8" t="n">
-        <v>1.007371147681944e-05</v>
+        <v>1.007371147681943e-05</v>
       </c>
       <c r="N8" t="n">
-        <v>1.070701232967168e-05</v>
+        <v>1.070701232967167e-05</v>
       </c>
       <c r="O8" t="n">
         <v>1.056270642582784e-05</v>
@@ -6563,40 +6563,40 @@
         <v>1.073007583385081e-05</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.058217520436477e-05</v>
+        <v>1.058217520436475e-05</v>
       </c>
       <c r="R8" t="n">
-        <v>1.0535144916536e-05</v>
+        <v>1.053514491653602e-05</v>
       </c>
       <c r="S8" t="n">
-        <v>9.847832260814128e-06</v>
+        <v>9.847832260814118e-06</v>
       </c>
       <c r="T8" t="n">
-        <v>1.057751867863173e-05</v>
+        <v>1.057751867863172e-05</v>
       </c>
       <c r="U8" t="n">
-        <v>9.795390331842369e-06</v>
+        <v>9.795390331842368e-06</v>
       </c>
       <c r="V8" t="n">
         <v>1.151063665019094e-05</v>
       </c>
       <c r="W8" t="n">
-        <v>1.038502688250095e-05</v>
+        <v>1.038502688250094e-05</v>
       </c>
       <c r="X8" t="n">
-        <v>2.961337081233759e-06</v>
+        <v>2.961337081233718e-06</v>
       </c>
       <c r="Y8" t="n">
-        <v>8.413402323204127e-06</v>
+        <v>8.413402323204112e-06</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.051086049028697e-05</v>
+        <v>1.051086049028695e-05</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.013743993817147e-05</v>
+        <v>1.013743993817145e-05</v>
       </c>
       <c r="AB8" t="n">
-        <v>9.192337305499298e-06</v>
+        <v>9.19233730549928e-06</v>
       </c>
     </row>
   </sheetData>
@@ -6762,85 +6762,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.123224718311188e-05</v>
+        <v>3.123224718311186e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>1.789610050152325e-05</v>
+        <v>1.789610050152319e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>1.947863057259334e-05</v>
+        <v>1.947863057259336e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>1.730345510311156e-05</v>
+        <v>1.730345510311158e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>1.879104982910965e-05</v>
+        <v>1.879104982910963e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>2.170035900190735e-05</v>
+        <v>2.170035900190736e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>1.812087704366635e-05</v>
+        <v>1.812087704366629e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>1.85224394456946e-05</v>
+        <v>1.852243944569454e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>2.382794938335408e-05</v>
+        <v>2.382794938335406e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>1.831849149072785e-05</v>
+        <v>1.831849149072784e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>5.707769815205214e-05</v>
+        <v>5.707769815205215e-05</v>
       </c>
       <c r="M2" t="n">
-        <v>3.238047585974513e-05</v>
+        <v>3.238047585974509e-05</v>
       </c>
       <c r="N2" t="n">
-        <v>1.808511463967518e-05</v>
+        <v>1.808511463967523e-05</v>
       </c>
       <c r="O2" t="n">
-        <v>1.911242087505324e-05</v>
+        <v>1.91124208750532e-05</v>
       </c>
       <c r="P2" t="n">
-        <v>2.687130271637256e-05</v>
+        <v>2.687130271637255e-05</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.981305786114635e-05</v>
+        <v>1.981305786114631e-05</v>
       </c>
       <c r="R2" t="n">
-        <v>1.838253796599366e-05</v>
+        <v>1.838253796599361e-05</v>
       </c>
       <c r="S2" t="n">
-        <v>2.46177730642977e-05</v>
+        <v>2.461777306429764e-05</v>
       </c>
       <c r="T2" t="n">
-        <v>1.953744175683752e-05</v>
+        <v>1.953744175683746e-05</v>
       </c>
       <c r="U2" t="n">
-        <v>4.169589816887057e-05</v>
+        <v>4.169589816887061e-05</v>
       </c>
       <c r="V2" t="n">
-        <v>2.081250548744979e-05</v>
+        <v>2.081250548744981e-05</v>
       </c>
       <c r="W2" t="n">
-        <v>2.157709626983418e-05</v>
+        <v>2.157709626983414e-05</v>
       </c>
       <c r="X2" t="n">
-        <v>3.255548115774272e-05</v>
+        <v>3.255548115774273e-05</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.173751398422544e-05</v>
+        <v>2.173751398422539e-05</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.523985558878574e-05</v>
+        <v>2.52398555887857e-05</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.435627976432154e-05</v>
+        <v>2.435627976432151e-05</v>
       </c>
       <c r="AB2" t="n">
-        <v>3.470775617706441e-05</v>
+        <v>3.470775617706436e-05</v>
       </c>
     </row>
     <row r="3">
@@ -6850,85 +6850,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.777800072885086e-05</v>
+        <v>1.77780007288509e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>1.777800072885086e-05</v>
+        <v>1.77780007288509e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>1.777800072885086e-05</v>
+        <v>1.77780007288509e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>1.262760622736159e-05</v>
+        <v>1.26276062273616e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>1.777800072885086e-05</v>
+        <v>1.77780007288509e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>1.777800072885086e-05</v>
+        <v>1.77780007288509e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>1.777800072885086e-05</v>
+        <v>1.77780007288509e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>1.777800072885086e-05</v>
+        <v>1.77780007288509e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>1.767960931776303e-05</v>
+        <v>1.767960931776304e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>1.777800072885086e-05</v>
+        <v>1.77780007288509e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>1.777800072885086e-05</v>
+        <v>1.77780007288509e-05</v>
       </c>
       <c r="M3" t="n">
-        <v>1.777800072885086e-05</v>
+        <v>1.77780007288509e-05</v>
       </c>
       <c r="N3" t="n">
-        <v>1.777800072885086e-05</v>
+        <v>1.77780007288509e-05</v>
       </c>
       <c r="O3" t="n">
-        <v>1.777800072885086e-05</v>
+        <v>1.77780007288509e-05</v>
       </c>
       <c r="P3" t="n">
-        <v>1.777800072885086e-05</v>
+        <v>1.77780007288509e-05</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.777800072885086e-05</v>
+        <v>1.77780007288509e-05</v>
       </c>
       <c r="R3" t="n">
-        <v>1.777800072885086e-05</v>
+        <v>1.77780007288509e-05</v>
       </c>
       <c r="S3" t="n">
-        <v>1.777800072885086e-05</v>
+        <v>1.77780007288509e-05</v>
       </c>
       <c r="T3" t="n">
-        <v>1.777800072885086e-05</v>
+        <v>1.77780007288509e-05</v>
       </c>
       <c r="U3" t="n">
-        <v>1.777800072885086e-05</v>
+        <v>1.77780007288509e-05</v>
       </c>
       <c r="V3" t="n">
-        <v>1.809027209585075e-05</v>
+        <v>1.809027209585077e-05</v>
       </c>
       <c r="W3" t="n">
-        <v>1.777800072885086e-05</v>
+        <v>1.77780007288509e-05</v>
       </c>
       <c r="X3" t="n">
-        <v>1.777800072885086e-05</v>
+        <v>1.77780007288509e-05</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.777800072885086e-05</v>
+        <v>1.77780007288509e-05</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.777800072885086e-05</v>
+        <v>1.77780007288509e-05</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.777800072885086e-05</v>
+        <v>1.77780007288509e-05</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.777800072885086e-05</v>
+        <v>1.77780007288509e-05</v>
       </c>
     </row>
     <row r="4">
@@ -6938,85 +6938,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.003406281373079659</v>
+        <v>0.003406281373079662</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0001090825683266343</v>
+        <v>0.0001090825683266342</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0005537373217670848</v>
+        <v>0.0005537373217670844</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001290472297161667</v>
+        <v>0.001290472297161668</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0003592774500024099</v>
+        <v>0.0003592774500024096</v>
       </c>
       <c r="G4" t="n">
-        <v>0.00103651297649094</v>
+        <v>0.001036512976490941</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0001752493709121815</v>
+        <v>0.0001752493709121813</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0002840728697176291</v>
+        <v>0.000284072869717629</v>
       </c>
       <c r="J4" t="n">
-        <v>0.001648771309889275</v>
+        <v>0.001648771309889277</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0002262296794979551</v>
+        <v>0.000226229679497955</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01027315205824818</v>
+        <v>0.0102731520582482</v>
       </c>
       <c r="M4" t="n">
-        <v>0.003902950870225111</v>
+        <v>0.003902950870225121</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0001538822145996647</v>
+        <v>0.0001538822145996645</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0003974976468845993</v>
+        <v>0.0003974976468845982</v>
       </c>
       <c r="P4" t="n">
-        <v>0.002392575740913988</v>
+        <v>0.002392575740913984</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.0006215656128437262</v>
+        <v>0.0006215656128437264</v>
       </c>
       <c r="R4" t="n">
-        <v>0.0002468603680671078</v>
+        <v>0.0002468603680671073</v>
       </c>
       <c r="S4" t="n">
-        <v>0.00171211507298182</v>
+        <v>0.001712115072981824</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0005702399951254796</v>
+        <v>0.0005702399951254801</v>
       </c>
       <c r="U4" t="n">
-        <v>0.00633715925434251</v>
+        <v>0.006337159254342512</v>
       </c>
       <c r="V4" t="n">
-        <v>0.0007408151416384365</v>
+        <v>0.0007408151416384376</v>
       </c>
       <c r="W4" t="n">
-        <v>0.001101476439489155</v>
+        <v>0.001101476439489157</v>
       </c>
       <c r="X4" t="n">
-        <v>0.004192868473425545</v>
+        <v>0.004192868473425562</v>
       </c>
       <c r="Y4" t="n">
         <v>0.001132206154105313</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.001937289061071319</v>
+        <v>0.001937289061071317</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.001852601947961624</v>
+        <v>0.001852601947961626</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.005104551019904733</v>
+        <v>0.005104551019904731</v>
       </c>
     </row>
     <row r="5">
@@ -7026,52 +7026,52 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7.760121835521599e-05</v>
+        <v>7.760121835521612e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0001217140706394358</v>
+        <v>0.0001217140706394359</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0001217140706394358</v>
+        <v>0.0001217140706394359</v>
       </c>
       <c r="E5" t="n">
-        <v>9.822527804587895e-05</v>
+        <v>9.822527804587891e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>8.447348518339157e-05</v>
+        <v>8.447348518339159e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0001308611579291154</v>
+        <v>0.0001308611579291155</v>
       </c>
       <c r="H5" t="n">
         <v>0.0001217140706394358</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0001217140706394358</v>
+        <v>0.0001217140706394359</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0001216067455428048</v>
+        <v>0.0001216067455428049</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0001217140706394358</v>
+        <v>0.0001217140706394359</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0001217140706394358</v>
+        <v>0.0001217140706394359</v>
       </c>
       <c r="M5" t="n">
-        <v>0.000121714070639443</v>
+        <v>0.0001217140706394431</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0001538822145996647</v>
+        <v>8.751923019985819e-05</v>
       </c>
       <c r="O5" t="n">
-        <v>9.691626926158631e-05</v>
+        <v>9.691626926158635e-05</v>
       </c>
       <c r="P5" t="n">
-        <v>9.461282792327248e-05</v>
+        <v>9.461282792327247e-05</v>
       </c>
       <c r="Q5" t="n">
-        <v>6.893203605474851e-05</v>
+        <v>6.893203605474862e-05</v>
       </c>
       <c r="R5" t="n">
         <v>0.0001217140706394358</v>
@@ -7080,25 +7080,25 @@
         <v>0.0001217140706394358</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0001217140706394358</v>
+        <v>0.0001217140706394359</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0001001762730724928</v>
+        <v>0.000100176273072493</v>
       </c>
       <c r="V5" t="n">
         <v>0.0001089596425427113</v>
       </c>
       <c r="W5" t="n">
-        <v>0.0001217227400790721</v>
+        <v>0.0001217227400790723</v>
       </c>
       <c r="X5" t="n">
-        <v>7.297506662026541e-05</v>
+        <v>7.29750666202654e-05</v>
       </c>
       <c r="Y5" t="n">
         <v>0.0001655626663368419</v>
       </c>
       <c r="Z5" t="n">
-        <v>7.678179947655356e-05</v>
+        <v>7.678179947655373e-05</v>
       </c>
       <c r="AA5" t="n">
         <v>0.0001217140706394358</v>
@@ -7117,82 +7117,82 @@
         <v>0.000117580096109034</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0001478367466384703</v>
+        <v>0.0001478367466384704</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0001478367466384703</v>
+        <v>0.0001478367466384704</v>
       </c>
       <c r="E6" t="n">
         <v>0.0001408536250752125</v>
       </c>
       <c r="F6" t="n">
-        <v>7.808692637430636e-05</v>
+        <v>7.808692637430645e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0001478367335916493</v>
+        <v>0.0001478367335916494</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0001478367466384703</v>
+        <v>0.0001478367466384704</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0001478367466384703</v>
+        <v>0.0001478367466384704</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0001477294215418393</v>
+        <v>0.0001477294215418394</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0001478367466384703</v>
+        <v>0.0001478367466384704</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0001478367466384703</v>
+        <v>0.0001478367466384704</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0001478367466384703</v>
+        <v>0.0001478367466384704</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0001538822145996647</v>
+        <v>0.0001478367466384704</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0001578637436358307</v>
+        <v>0.0001578637436358308</v>
       </c>
       <c r="P6" t="n">
-        <v>0.0001600444462858125</v>
+        <v>0.0001600444462858124</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.0001478367335916493</v>
+        <v>0.0001478367335916494</v>
       </c>
       <c r="R6" t="n">
-        <v>0.0001478367466384703</v>
+        <v>0.0001478367466384704</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0001478367466384703</v>
+        <v>0.0001478367466384704</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0001478367466384703</v>
+        <v>0.0001478367466384704</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0001478367466384703</v>
+        <v>0.0001478367466384704</v>
       </c>
       <c r="V6" t="n">
-        <v>0.0001820620900190334</v>
+        <v>0.0001820620900190337</v>
       </c>
       <c r="W6" t="n">
-        <v>0.0001478367466384703</v>
+        <v>0.0001478367466384704</v>
       </c>
       <c r="X6" t="n">
-        <v>0.0001478367466384703</v>
+        <v>0.0001478367466384704</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.0001478367466384703</v>
+        <v>0.0001478367466384704</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.0001295946717148188</v>
+        <v>0.000129594671714819</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.0001478367466384703</v>
+        <v>0.0001478367466384704</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.0001478367466384703</v>
+        <v>0.0001478367466384704</v>
       </c>
     </row>
     <row r="7">
@@ -7202,28 +7202,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-6.296297166863298e-05</v>
+        <v>-6.296297166863308e-05</v>
       </c>
       <c r="C7" t="n">
         <v>1.63967423511006e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>7.128672589404934e-06</v>
+        <v>7.128672589404888e-06</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.533888710914363e-05</v>
+        <v>-1.533888710914353e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>1.118874474364369e-05</v>
+        <v>1.118874474364372e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>-6.242726771683229e-06</v>
+        <v>-6.242726771683357e-06</v>
       </c>
       <c r="H7" t="n">
-        <v>1.51002715749542e-05</v>
+        <v>1.510027157495422e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>1.273912988563806e-05</v>
+        <v>1.273912988563805e-05</v>
       </c>
       <c r="J7" t="n">
         <v>-1.934864700056192e-05</v>
@@ -7232,55 +7232,55 @@
         <v>1.391869692321013e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.0002152501315948646</v>
+        <v>-0.0002152501315948651</v>
       </c>
       <c r="M7" t="n">
-        <v>-6.811690792029294e-05</v>
+        <v>-6.811690792029293e-05</v>
       </c>
       <c r="N7" t="n">
         <v>1.528051998765286e-05</v>
       </c>
       <c r="O7" t="n">
-        <v>9.130516536688402e-06</v>
+        <v>9.130516536688428e-06</v>
       </c>
       <c r="P7" t="n">
-        <v>-3.712745055801851e-05</v>
+        <v>-3.712745055801854e-05</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.137393297968952e-06</v>
+        <v>5.137393297968939e-06</v>
       </c>
       <c r="R7" t="n">
-        <v>1.356591857620873e-05</v>
+        <v>1.356591857620869e-05</v>
       </c>
       <c r="S7" t="n">
-        <v>-2.348438398356292e-05</v>
+        <v>-2.348438398356295e-05</v>
       </c>
       <c r="T7" t="n">
         <v>6.791195386368196e-06</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0001244573084455397</v>
+        <v>-0.0001244573084455399</v>
       </c>
       <c r="V7" t="n">
-        <v>1.165104704203062e-06</v>
+        <v>1.165104704203098e-06</v>
       </c>
       <c r="W7" t="n">
-        <v>-5.337578838980414e-06</v>
+        <v>-5.337578838980443e-06</v>
       </c>
       <c r="X7" t="n">
-        <v>-6.955338514152142e-05</v>
+        <v>-6.955338514152154e-05</v>
       </c>
       <c r="Y7" t="n">
-        <v>-6.245427924540484e-06</v>
+        <v>-6.245427924540456e-06</v>
       </c>
       <c r="Z7" t="n">
         <v>-2.726319165193708e-05</v>
       </c>
       <c r="AA7" t="n">
-        <v>-2.170808908414559e-05</v>
+        <v>-2.170808908414557e-05</v>
       </c>
       <c r="AB7" t="n">
-        <v>-8.205360089383776e-05</v>
+        <v>-8.205360089383772e-05</v>
       </c>
     </row>
     <row r="8">
@@ -7290,49 +7290,49 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-5.505152563955256e-06</v>
+        <v>-5.505152563955337e-06</v>
       </c>
       <c r="C8" t="n">
         <v>1.726762353783753e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>1.463315233175027e-05</v>
+        <v>1.463315233175031e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>4.578611511075561e-06</v>
+        <v>4.578611511075557e-06</v>
       </c>
       <c r="F8" t="n">
-        <v>1.57929173571275e-05</v>
+        <v>1.579291735712746e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>1.077085143964774e-05</v>
+        <v>1.077085143964769e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>1.69025017452268e-05</v>
+        <v>1.690250174522679e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>1.622973715410412e-05</v>
+        <v>1.622973715410414e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>6.979974756464874e-06</v>
+        <v>6.97997475646483e-06</v>
       </c>
       <c r="K8" t="n">
-        <v>1.656249596028985e-05</v>
+        <v>1.656249596028983e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>-4.895084467183377e-05</v>
+        <v>-4.895084467183378e-05</v>
       </c>
       <c r="M8" t="n">
-        <v>-6.701981306447612e-06</v>
+        <v>-6.701981306447678e-06</v>
       </c>
       <c r="N8" t="n">
-        <v>1.694875294343119e-05</v>
+        <v>1.694875294343117e-05</v>
       </c>
       <c r="O8" t="n">
-        <v>1.517778800972236e-05</v>
+        <v>1.517778800972233e-05</v>
       </c>
       <c r="P8" t="n">
-        <v>1.889147407555565e-06</v>
+        <v>1.889147407555578e-06</v>
       </c>
       <c r="Q8" t="n">
         <v>1.406154119686931e-05</v>
@@ -7341,34 +7341,34 @@
         <v>1.646602716343205e-05</v>
       </c>
       <c r="S8" t="n">
-        <v>5.843256524731437e-06</v>
+        <v>5.843256524731414e-06</v>
       </c>
       <c r="T8" t="n">
-        <v>1.453841031313662e-05</v>
+        <v>1.453841031313666e-05</v>
       </c>
       <c r="U8" t="n">
-        <v>-2.302162078251262e-05</v>
+        <v>-2.302162078251265e-05</v>
       </c>
       <c r="V8" t="n">
         <v>1.311150038694195e-05</v>
       </c>
       <c r="W8" t="n">
-        <v>1.105943390148964e-05</v>
+        <v>1.105943390148962e-05</v>
       </c>
       <c r="X8" t="n">
-        <v>-7.180577721890351e-06</v>
+        <v>-7.180577721890377e-06</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.080677738880769e-05</v>
+        <v>1.080677738880772e-05</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.745969517763699e-06</v>
+        <v>4.745969517763733e-06</v>
       </c>
       <c r="AA8" t="n">
-        <v>6.389983064706139e-06</v>
+        <v>6.389983064706138e-06</v>
       </c>
       <c r="AB8" t="n">
-        <v>-1.071594070569654e-05</v>
+        <v>-1.071594070569649e-05</v>
       </c>
     </row>
   </sheetData>
@@ -7534,85 +7534,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.272310875462293e-05</v>
+        <v>1.272310875462294e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>1.269314621091392e-05</v>
+        <v>1.269314621091396e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>1.329193744412702e-05</v>
+        <v>1.329193744412708e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>8.851646625307304e-06</v>
+        <v>8.851646625307316e-06</v>
       </c>
       <c r="F2" t="n">
-        <v>1.271918177015518e-05</v>
+        <v>1.271918177015522e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>1.555553555883296e-05</v>
+        <v>1.5555535558833e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>1.268318891243712e-05</v>
+        <v>1.268318891243717e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>1.319992914262112e-05</v>
+        <v>1.319992914262116e-05</v>
       </c>
       <c r="J2" t="n">
         <v>1.459212304268648e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>1.489837566556037e-05</v>
+        <v>1.489837566556042e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>2.4683153665766e-05</v>
+        <v>2.468315366576605e-05</v>
       </c>
       <c r="M2" t="n">
-        <v>1.483216196681025e-05</v>
+        <v>1.483216196681023e-05</v>
       </c>
       <c r="N2" t="n">
-        <v>1.268202879776438e-05</v>
+        <v>1.26820287977644e-05</v>
       </c>
       <c r="O2" t="n">
-        <v>1.28882373809707e-05</v>
+        <v>1.288823738097075e-05</v>
       </c>
       <c r="P2" t="n">
-        <v>1.644172396154686e-05</v>
+        <v>1.64417239615469e-05</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.273026644243605e-05</v>
+        <v>1.273026644243607e-05</v>
       </c>
       <c r="R2" t="n">
-        <v>1.274912152721869e-05</v>
+        <v>1.274912152721873e-05</v>
       </c>
       <c r="S2" t="n">
-        <v>1.43051463899559e-05</v>
+        <v>1.430514638995595e-05</v>
       </c>
       <c r="T2" t="n">
-        <v>1.271072460558171e-05</v>
+        <v>1.27107246055817e-05</v>
       </c>
       <c r="U2" t="n">
         <v>1.626574255207422e-05</v>
       </c>
       <c r="V2" t="n">
-        <v>1.409004106881067e-05</v>
+        <v>1.409004106881065e-05</v>
       </c>
       <c r="W2" t="n">
-        <v>1.383476144361159e-05</v>
+        <v>1.383476144361163e-05</v>
       </c>
       <c r="X2" t="n">
-        <v>2.194920254200699e-05</v>
+        <v>2.194920254200703e-05</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.947363743020896e-05</v>
+        <v>1.947363743020895e-05</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.352878873429905e-05</v>
+        <v>1.352878873429908e-05</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.503205037200777e-05</v>
+        <v>1.503205037200781e-05</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.340076787478121e-05</v>
+        <v>2.340076787478124e-05</v>
       </c>
     </row>
     <row r="3">
@@ -7631,7 +7631,7 @@
         <v>1.264962790463889e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>8.503906768515559e-06</v>
+        <v>8.50390676851559e-06</v>
       </c>
       <c r="F3" t="n">
         <v>1.264962790463889e-05</v>
@@ -7646,7 +7646,7 @@
         <v>1.264962790463889e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>1.256829822223487e-05</v>
+        <v>1.256829822223488e-05</v>
       </c>
       <c r="K3" t="n">
         <v>1.264962790463889e-05</v>
@@ -7682,7 +7682,7 @@
         <v>1.264962790463889e-05</v>
       </c>
       <c r="V3" t="n">
-        <v>1.372918121782976e-05</v>
+        <v>1.372918121782977e-05</v>
       </c>
       <c r="W3" t="n">
         <v>1.264962790463889e-05</v>
@@ -7710,85 +7710,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.597113986199241e-05</v>
+        <v>6.59711398619924e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>6.963786387880147e-05</v>
+        <v>6.963786387880151e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0002171036503747755</v>
+        <v>0.0002171036503747757</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0001038807554330186</v>
+        <v>0.0001038807554330188</v>
       </c>
       <c r="F4" t="n">
-        <v>7.228389677915739e-05</v>
+        <v>7.228389677915746e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0006936392486009865</v>
+        <v>0.0006936392486009871</v>
       </c>
       <c r="H4" t="n">
-        <v>5.878624224528444e-05</v>
+        <v>5.87862422452845e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0001952555570574046</v>
+        <v>0.0001952555570574047</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0005199729202922653</v>
+        <v>0.0005199729202922658</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0005786486527647163</v>
+        <v>0.0005786486527647169</v>
       </c>
       <c r="L4" t="n">
-        <v>0.002779986874665247</v>
+        <v>0.00277998687466525</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0005861511607056647</v>
+        <v>0.0005861511607056642</v>
       </c>
       <c r="N4" t="n">
-        <v>5.516302837961726e-05</v>
+        <v>5.516302837961742e-05</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0001080717414311503</v>
+        <v>0.0001080717414311505</v>
       </c>
       <c r="P4" t="n">
-        <v>0.0009277828154604527</v>
+        <v>0.0009277828154604512</v>
       </c>
       <c r="Q4" t="n">
-        <v>7.547353668168523e-05</v>
+        <v>7.547353668168522e-05</v>
       </c>
       <c r="R4" t="n">
-        <v>7.573029683041513e-05</v>
+        <v>7.573029683041529e-05</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0004213198961785779</v>
+        <v>0.0004213198961785775</v>
       </c>
       <c r="T4" t="n">
-        <v>6.660766916959405e-05</v>
+        <v>6.660766916959401e-05</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0008860389441757918</v>
+        <v>0.0008860389441757916</v>
       </c>
       <c r="V4" t="n">
         <v>0.0001437881783790053</v>
       </c>
       <c r="W4" t="n">
-        <v>0.0003467692312083244</v>
+        <v>0.0003467692312083243</v>
       </c>
       <c r="X4" t="n">
-        <v>0.00238428094729454</v>
+        <v>0.002384280947294541</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.001755764616111718</v>
+        <v>0.001755764616111714</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.0002490509108818662</v>
+        <v>0.0002490509108818666</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.0006508732328974367</v>
+        <v>0.0006508732328974366</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.002955765440558875</v>
+        <v>0.002955765440558878</v>
       </c>
     </row>
     <row r="5">
@@ -7798,85 +7798,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.153486344608633e-05</v>
+        <v>6.153486344608648e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>9.714960472537252e-05</v>
+        <v>9.714960472537276e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>9.714960472537252e-05</v>
+        <v>9.714960472537276e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>7.818580556327959e-05</v>
+        <v>7.818580556327969e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>6.708322389923498e-05</v>
+        <v>6.708322389923504e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0001045345533381372</v>
+        <v>0.0001045345533381373</v>
       </c>
       <c r="H5" t="n">
-        <v>9.714960472537252e-05</v>
+        <v>9.714960472537276e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>9.714960472537252e-05</v>
+        <v>9.714960472537276e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>9.704799874372251e-05</v>
+        <v>9.704799874372258e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>9.714960472537252e-05</v>
+        <v>9.714960472537276e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>9.714960472537253e-05</v>
+        <v>9.714960472537278e-05</v>
       </c>
       <c r="M5" t="n">
-        <v>9.714960472536957e-05</v>
+        <v>9.714960472536982e-05</v>
       </c>
       <c r="N5" t="n">
-        <v>5.516302837961726e-05</v>
+        <v>6.954222201766852e-05</v>
       </c>
       <c r="O5" t="n">
-        <v>7.712897049684974e-05</v>
+        <v>7.712897049684987e-05</v>
       </c>
       <c r="P5" t="n">
-        <v>7.526927512304976e-05</v>
+        <v>7.526927512304995e-05</v>
       </c>
       <c r="Q5" t="n">
-        <v>5.453575391793843e-05</v>
+        <v>5.453575391793851e-05</v>
       </c>
       <c r="R5" t="n">
-        <v>9.714960472537252e-05</v>
+        <v>9.714960472537276e-05</v>
       </c>
       <c r="S5" t="n">
-        <v>9.714960472537252e-05</v>
+        <v>9.714960472537276e-05</v>
       </c>
       <c r="T5" t="n">
-        <v>9.714960472537252e-05</v>
+        <v>9.714960472537276e-05</v>
       </c>
       <c r="U5" t="n">
-        <v>7.977153289787414e-05</v>
+        <v>7.977153289787424e-05</v>
       </c>
       <c r="V5" t="n">
-        <v>8.676696973272984e-05</v>
+        <v>8.676696973272995e-05</v>
       </c>
       <c r="W5" t="n">
-        <v>9.715660404291182e-05</v>
+        <v>9.715660404291209e-05</v>
       </c>
       <c r="X5" t="n">
-        <v>5.779991572397327e-05</v>
+        <v>5.779991572397331e-05</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.0001325690986451264</v>
+        <v>0.0001325690986451265</v>
       </c>
       <c r="Z5" t="n">
-        <v>6.087330134224993e-05</v>
+        <v>6.087330134225009e-05</v>
       </c>
       <c r="AA5" t="n">
-        <v>9.714960472537252e-05</v>
+        <v>9.714960472537276e-05</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.000134352180048059</v>
+        <v>0.0001343521800480592</v>
       </c>
     </row>
     <row r="6">
@@ -7886,7 +7886,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8.090516547221269e-05</v>
+        <v>8.090516547221278e-05</v>
       </c>
       <c r="C6" t="n">
         <v>0.0001017635637784476</v>
@@ -7895,13 +7895,13 @@
         <v>0.0001017635637784476</v>
       </c>
       <c r="E6" t="n">
-        <v>9.694953044451723e-05</v>
+        <v>9.694953044451722e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>5.36792630291992e-05</v>
+        <v>5.367926302919927e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>0.000101763563668356</v>
+        <v>0.0001017635636683562</v>
       </c>
       <c r="H6" t="n">
         <v>0.0001017635637784476</v>
@@ -7910,7 +7910,7 @@
         <v>0.0001017635637784476</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0001016619577967973</v>
+        <v>0.0001016619577967974</v>
       </c>
       <c r="K6" t="n">
         <v>0.0001017635637784476</v>
@@ -7922,16 +7922,16 @@
         <v>0.0001017635637784476</v>
       </c>
       <c r="N6" t="n">
-        <v>5.516302837961726e-05</v>
+        <v>0.0001017635637784476</v>
       </c>
       <c r="O6" t="n">
-        <v>0.000108676009518933</v>
+        <v>0.0001086760095189331</v>
       </c>
       <c r="P6" t="n">
         <v>0.000110179347893736</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.000101763563668356</v>
+        <v>0.0001017635636683562</v>
       </c>
       <c r="R6" t="n">
         <v>0.0001017635637784476</v>
@@ -7958,7 +7958,7 @@
         <v>0.0001017635637784476</v>
       </c>
       <c r="Z6" t="n">
-        <v>8.91878043572217e-05</v>
+        <v>8.918780435722168e-05</v>
       </c>
       <c r="AA6" t="n">
         <v>0.0001017635637784476</v>
@@ -7974,85 +7974,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.182676700648769e-05</v>
+        <v>1.182676700648773e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>1.201484766444647e-05</v>
+        <v>1.201484766444649e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>8.508191716328265e-06</v>
+        <v>8.508191716328299e-06</v>
       </c>
       <c r="E7" t="n">
-        <v>6.343903795170738e-06</v>
+        <v>6.34390379517077e-06</v>
       </c>
       <c r="F7" t="n">
         <v>1.186718516465672e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>-5.013978674876822e-06</v>
+        <v>-5.01397867487684e-06</v>
       </c>
       <c r="H7" t="n">
-        <v>1.207815216210159e-05</v>
+        <v>1.207815216210156e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>9.053959525689973e-06</v>
+        <v>9.053959525689975e-06</v>
       </c>
       <c r="J7" t="n">
-        <v>2.139207139474574e-07</v>
+        <v>2.139207139474731e-07</v>
       </c>
       <c r="K7" t="n">
-        <v>-9.208427614417363e-07</v>
+        <v>-9.208427614417321e-07</v>
       </c>
       <c r="L7" t="n">
-        <v>-5.887365274964354e-05</v>
+        <v>-5.887365274964357e-05</v>
       </c>
       <c r="M7" t="n">
-        <v>-4.636005388769825e-07</v>
+        <v>-4.636005388769473e-07</v>
       </c>
       <c r="N7" t="n">
         <v>1.207815931384709e-05</v>
       </c>
       <c r="O7" t="n">
-        <v>1.084237189726571e-05</v>
+        <v>1.084237189726574e-05</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.03413982814654e-05</v>
+        <v>-1.034139828146536e-05</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.179590504351292e-05</v>
+        <v>1.179590504351298e-05</v>
       </c>
       <c r="R7" t="n">
-        <v>1.169171890803031e-05</v>
+        <v>1.169171890803036e-05</v>
       </c>
       <c r="S7" t="n">
-        <v>2.446686317049793e-06</v>
+        <v>2.446686317049809e-06</v>
       </c>
       <c r="T7" t="n">
-        <v>1.191316147394875e-05</v>
+        <v>1.191316147394876e-05</v>
       </c>
       <c r="U7" t="n">
-        <v>-9.133040863469679e-06</v>
+        <v>-9.133040863469684e-06</v>
       </c>
       <c r="V7" t="n">
         <v>1.107585805474101e-05</v>
       </c>
       <c r="W7" t="n">
-        <v>5.272696405623367e-06</v>
+        <v>5.272696405623353e-06</v>
       </c>
       <c r="X7" t="n">
-        <v>-4.225483310458628e-05</v>
+        <v>-4.225483310458627e-05</v>
       </c>
       <c r="Y7" t="n">
-        <v>-2.794208276865224e-05</v>
+        <v>-2.79420827686522e-05</v>
       </c>
       <c r="Z7" t="n">
-        <v>7.039909566531846e-06</v>
+        <v>7.039909566531869e-06</v>
       </c>
       <c r="AA7" t="n">
-        <v>-1.781892309587249e-06</v>
+        <v>-1.781892309587177e-06</v>
       </c>
       <c r="AB7" t="n">
-        <v>-5.069013354024722e-05</v>
+        <v>-5.069013354024718e-05</v>
       </c>
     </row>
     <row r="8">
@@ -8062,85 +8062,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.234870442366205e-05</v>
+        <v>1.234870442366206e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>1.240431917870178e-05</v>
+        <v>1.240431917870182e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>1.140757078047167e-05</v>
+        <v>1.140757078047172e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>7.868838388914353e-06</v>
+        <v>7.86883838891437e-06</v>
       </c>
       <c r="F8" t="n">
-        <v>1.236316782996624e-05</v>
+        <v>1.236316782996628e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>7.518538274579077e-06</v>
+        <v>7.518538274579115e-06</v>
       </c>
       <c r="H8" t="n">
-        <v>1.242316562839759e-05</v>
+        <v>1.242316562839755e-05</v>
       </c>
       <c r="I8" t="n">
         <v>1.156388857148418e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>8.970841905350579e-06</v>
+        <v>8.970841905350628e-06</v>
       </c>
       <c r="K8" t="n">
-        <v>8.723768265969679e-06</v>
+        <v>8.723768265969703e-06</v>
       </c>
       <c r="L8" t="n">
-        <v>-7.860166963103871e-06</v>
+        <v>-7.860166963103852e-06</v>
       </c>
       <c r="M8" t="n">
-        <v>8.865601235630991e-06</v>
+        <v>8.86560123563101e-06</v>
       </c>
       <c r="N8" t="n">
         <v>1.24220087677918e-05</v>
       </c>
       <c r="O8" t="n">
-        <v>1.20659301382327e-05</v>
+        <v>1.206593013823278e-05</v>
       </c>
       <c r="P8" t="n">
-        <v>5.980733778816318e-06</v>
+        <v>5.980733778816312e-06</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.234181981997035e-05</v>
+        <v>1.234181981997046e-05</v>
       </c>
       <c r="R8" t="n">
-        <v>1.231326988108696e-05</v>
+        <v>1.2313269881087e-05</v>
       </c>
       <c r="S8" t="n">
-        <v>9.662775452757313e-06</v>
+        <v>9.662775452757318e-06</v>
       </c>
       <c r="T8" t="n">
-        <v>1.237563003263842e-05</v>
+        <v>1.237563003263841e-05</v>
       </c>
       <c r="U8" t="n">
-        <v>6.354558845338239e-06</v>
+        <v>6.354558845338248e-06</v>
       </c>
       <c r="V8" t="n">
-        <v>1.288277057396607e-05</v>
+        <v>1.288277057396606e-05</v>
       </c>
       <c r="W8" t="n">
-        <v>1.047823410267366e-05</v>
+        <v>1.047823410267375e-05</v>
       </c>
       <c r="X8" t="n">
-        <v>-3.032502187325954e-06</v>
+        <v>-3.032502187325992e-06</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.004279715755019e-06</v>
+        <v>1.004279715754945e-06</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.09763490133488e-05</v>
+        <v>1.097634901334875e-05</v>
       </c>
       <c r="AA8" t="n">
-        <v>8.46566268400879e-06</v>
+        <v>8.465662684008824e-06</v>
       </c>
       <c r="AB8" t="n">
-        <v>-5.419025434485027e-06</v>
+        <v>-5.419025434485003e-06</v>
       </c>
     </row>
   </sheetData>
